--- a/app/template_knowledge/sources/영상편집DB.xlsx
+++ b/app/template_knowledge/sources/영상편집DB.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R576131c6b8b6403e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R016037fba0e6416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rfa4668d079244ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="Rcb4cf71566a44214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R23d6434092254068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="Rd5588dee259f4ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R241bfb6c422a445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R706ad47ef9b14d19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R85acde8afbde4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R9faeec7798c44953"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R17c462851164430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R95bbdf72f9994571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R87395bafb1874d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R8ab9419d8a5a4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R0a17b4958cc84099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R1428eea5ef8c4bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R16f82cb6d0444ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R7e74f51c363a40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="Ra76d2a1f66bb4f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="Rf10f84783210447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R17272ad391c340e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R5f2f7acb8f8441e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R622f108746d049cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R2ceb10cae35f4c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R6100602d2eb54910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="Rab55d6eb79934e2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31958,8 +31958,12 @@
       <x:c r="F7" s="47" t="str">
         <x:v>카페 추천 리뷰 릴스</x:v>
       </x:c>
-      <x:c r="G7" s="47"/>
-      <x:c r="H7" s="47"/>
+      <x:c r="G7" s="47" t="str">
+        <x:v>https://www.youtube.com/shorts/OWnLiuJU8Ks</x:v>
+      </x:c>
+      <x:c r="H7" s="47" t="str">
+        <x:v>OWnLiuJU8Ks</x:v>
+      </x:c>
       <x:c r="I7" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>

--- a/app/template_knowledge/sources/영상편집DB.xlsx
+++ b/app/template_knowledge/sources/영상편집DB.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R4651dc3642b1486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R6b681fbb4a2e4b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R561d980d27e24494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R8951591f35b14d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="Rfd4ead5a0ca247a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="Rf597362cdc9e4246"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="Rc5b11f33bb374417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R113f0cb8c6cb483a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R30be0a5f15b6459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="Ra7a056af11d14ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R09ebc56dece64c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R7426b7047afc407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R0cc8b2d00f4c4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R2032648c311c49f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R33393f5afa1243f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R2e1b16fa1d6845fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R5908d5be669743be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="Rba65ef4661e54f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R109d77a2b9e64612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="Rf0ea8f17fd0b49ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="Rd3df3d48fe764a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="Re9ef99df09b442b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="Rbfdc28e7f10b4a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rd5383b432b494061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R2f77975909b74c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R362a1cf81b04478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_SHOOTING_ELEMENTS" sheetId="14" r:id="R0a5b31abfd4445a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -364,7 +365,7 @@
     <x:numFmt numFmtId="177" formatCode="0.0"/>
     <x:numFmt numFmtId="178" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -427,8 +428,19 @@
       <x:color theme="10"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -500,8 +512,38 @@
         <x:fgColor rgb="FFFFF3C9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -532,13 +574,103 @@
         <x:color rgb="FFCAD6DB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="80">
+  <x:cellXfs count="115">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -775,6 +907,75 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -782,6 +983,24 @@
     <x:cellStyle name="하이퍼링크" xfId="2"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InformationalShootingElementsTable" displayName="InformationalShootingElementsTable" ref="A4:J8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="shooting_element_id"/>
+    <x:tableColumn id="2" name="guide_template_id"/>
+    <x:tableColumn id="3" name="challenge_id"/>
+    <x:tableColumn id="4" name="display_order"/>
+    <x:tableColumn id="5" name="title"/>
+    <x:tableColumn id="6" name="instruction"/>
+    <x:tableColumn id="7" name="minimum_recording_sec"/>
+    <x:tableColumn id="8" name="reference_segment_sequences"/>
+    <x:tableColumn id="9" name="validation_status"/>
+    <x:tableColumn id="10" name="template_status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35380,6 +35599,222 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="107" t="str">
+        <x:v>정보형 숏폼 촬영 요소</x:v>
+      </x:c>
+      <x:c r="B1" s="107"/>
+      <x:c r="C1" s="107"/>
+      <x:c r="D1" s="107"/>
+      <x:c r="E1" s="107"/>
+      <x:c r="F1" s="107"/>
+      <x:c r="G1" s="107"/>
+      <x:c r="H1" s="107"/>
+      <x:c r="I1" s="107"/>
+      <x:c r="J1" s="107"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="110" t="str">
+        <x:v>사용자에게는 최대 5개 요소만 제공하며, 내부 편집 컷은 shooting_element_id로 연결합니다.</x:v>
+      </x:c>
+      <x:c r="B2" s="110"/>
+      <x:c r="C2" s="110"/>
+      <x:c r="D2" s="110"/>
+      <x:c r="E2" s="110"/>
+      <x:c r="F2" s="110"/>
+      <x:c r="G2" s="110"/>
+      <x:c r="H2" s="110"/>
+      <x:c r="I2" s="110"/>
+      <x:c r="J2" s="110"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="112" t="str">
+        <x:v>shooting_element_id</x:v>
+      </x:c>
+      <x:c r="B4" s="113" t="str">
+        <x:v>guide_template_id</x:v>
+      </x:c>
+      <x:c r="C4" s="113" t="str">
+        <x:v>challenge_id</x:v>
+      </x:c>
+      <x:c r="D4" s="113" t="str">
+        <x:v>display_order</x:v>
+      </x:c>
+      <x:c r="E4" s="113" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="F4" s="113" t="str">
+        <x:v>instruction</x:v>
+      </x:c>
+      <x:c r="G4" s="113" t="str">
+        <x:v>minimum_recording_sec</x:v>
+      </x:c>
+      <x:c r="H4" s="113" t="str">
+        <x:v>reference_segment_sequences</x:v>
+      </x:c>
+      <x:c r="I4" s="113" t="str">
+        <x:v>validation_status</x:v>
+      </x:c>
+      <x:c r="J4" s="114" t="str">
+        <x:v>template_status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="98" t="str">
+        <x:v>ELEMENT_01</x:v>
+      </x:c>
+      <x:c r="B5" s="99" t="str">
+        <x:v>gt_cafe_recommendation_v2</x:v>
+      </x:c>
+      <x:c r="C5" s="99" t="str">
+        <x:v>cafe_recommendation_reels</x:v>
+      </x:c>
+      <x:c r="D5" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="99" t="str">
+        <x:v>제조 과정</x:v>
+      </x:c>
+      <x:c r="F5" s="99" t="str">
+        <x:v>준비와 추출 과정을 손동작이 보이게 길게 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G5" s="99" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H5" s="99" t="str">
+        <x:v>1,13,14,15,16,23</x:v>
+      </x:c>
+      <x:c r="I5" s="99" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J5" s="100" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="98" t="str">
+        <x:v>ELEMENT_02</x:v>
+      </x:c>
+      <x:c r="B6" s="99" t="str">
+        <x:v>gt_cafe_recommendation_v2</x:v>
+      </x:c>
+      <x:c r="C6" s="99" t="str">
+        <x:v>cafe_recommendation_reels</x:v>
+      </x:c>
+      <x:c r="D6" s="99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" s="99" t="str">
+        <x:v>대표 메뉴</x:v>
+      </x:c>
+      <x:c r="F6" s="99" t="str">
+        <x:v>음료와 디저트 전체·세부 모습을 여러 각도로 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G6" s="99" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H6" s="99" t="str">
+        <x:v>2,3,9,10,11,12,17,20,21</x:v>
+      </x:c>
+      <x:c r="I6" s="99" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J6" s="100" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="98" t="str">
+        <x:v>ELEMENT_03</x:v>
+      </x:c>
+      <x:c r="B7" s="99" t="str">
+        <x:v>gt_cafe_recommendation_v2</x:v>
+      </x:c>
+      <x:c r="C7" s="99" t="str">
+        <x:v>cafe_recommendation_reels</x:v>
+      </x:c>
+      <x:c r="D7" s="99" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="99" t="str">
+        <x:v>체험과 전망</x:v>
+      </x:c>
+      <x:c r="F7" s="99" t="str">
+        <x:v>컵을 든 모습과 매장 밖 전망을 각각 길게 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G7" s="99" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H7" s="99" t="str">
+        <x:v>4,5,6,7,8</x:v>
+      </x:c>
+      <x:c r="I7" s="99" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J7" s="100" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="101" t="str">
+        <x:v>ELEMENT_04</x:v>
+      </x:c>
+      <x:c r="B8" s="102" t="str">
+        <x:v>gt_cafe_recommendation_v2</x:v>
+      </x:c>
+      <x:c r="C8" s="102" t="str">
+        <x:v>cafe_recommendation_reels</x:v>
+      </x:c>
+      <x:c r="D8" s="102" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" s="102" t="str">
+        <x:v>매장 분위기</x:v>
+      </x:c>
+      <x:c r="F8" s="102" t="str">
+        <x:v>창과 인테리어가 보이도록 매장 공간을 천천히 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G8" s="102" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H8" s="102" t="str">
+        <x:v>18,19,22</x:v>
+      </x:c>
+      <x:c r="I8" s="102" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J8" s="103" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radb0586adf194d94"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14"/>
@@ -35614,6 +36049,7 @@
     <x:col min="7" max="7" width="30" customWidth="1"/>
     <x:col min="8" max="8" width="23.25" customWidth="1"/>
     <x:col min="9" max="9" width="24.1640625" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -35681,6 +36117,9 @@
       <x:c r="I4" s="1" t="str">
         <x:v>input_validation_status</x:v>
       </x:c>
+      <x:c r="J4" s="104" t="str">
+        <x:v>format_type</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" s="9" t="str">
@@ -35710,6 +36149,9 @@
       <x:c r="I5" s="9" t="str">
         <x:v>PASS</x:v>
       </x:c>
+      <x:c r="J5" s="63" t="str">
+        <x:v>밈</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="9" t="str">
@@ -35739,6 +36181,9 @@
       <x:c r="I6" s="9" t="str">
         <x:v>PASS</x:v>
       </x:c>
+      <x:c r="J6" s="63" t="str">
+        <x:v>챌린지</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" s="9" t="str">
@@ -35765,6 +36210,9 @@
       <x:c r="H7" s="9"/>
       <x:c r="I7" s="9" t="str">
         <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J7" s="63" t="str">
+        <x:v>정보형</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -35778,9 +36226,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="R2a5f6002b0d4479e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R705c2ea051e4455a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Raf6f7b73184e41e7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="R36632b385e214036"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R8af8ae4620e5467f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Ra0551073b25e4293"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -35813,6 +36261,7 @@
     <x:col min="23" max="23" width="28" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -35964,6 +36413,9 @@
       <x:c r="W4" s="64" t="str">
         <x:v>source_file_sha256</x:v>
       </x:c>
+      <x:c r="X4" s="105" t="str">
+        <x:v>shooting_element_id</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="78" customHeight="1">
       <x:c r="A5" s="65" t="str">
@@ -36035,6 +36487,7 @@
       <x:c r="W5" s="65" t="str">
         <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
       </x:c>
+      <x:c r="X5"/>
     </x:row>
     <x:row r="6" ht="78" customHeight="1">
       <x:c r="A6" s="65" t="str">
@@ -36106,6 +36559,7 @@
       <x:c r="W6" s="65" t="str">
         <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
       </x:c>
+      <x:c r="X6"/>
     </x:row>
     <x:row r="7" ht="78" customHeight="1">
       <x:c r="A7" s="65" t="str">
@@ -36177,6 +36631,7 @@
       <x:c r="W7" s="65" t="str">
         <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
       </x:c>
+      <x:c r="X7"/>
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="65" t="str">
@@ -36242,6 +36697,7 @@
       <x:c r="W8" s="65" t="str">
         <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
       </x:c>
+      <x:c r="X8"/>
     </x:row>
     <x:row r="9" ht="78" customHeight="1">
       <x:c r="A9" s="65" t="str">
@@ -36313,6 +36769,7 @@
       <x:c r="W9" s="65" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
+      <x:c r="X9"/>
     </x:row>
     <x:row r="10" ht="78" customHeight="1">
       <x:c r="A10" s="65" t="str">
@@ -36380,6 +36837,7 @@
       <x:c r="W10" s="65" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
+      <x:c r="X10"/>
     </x:row>
     <x:row r="11" ht="78" customHeight="1">
       <x:c r="A11" s="65" t="str">
@@ -36447,6 +36905,7 @@
       <x:c r="W11" s="65" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
+      <x:c r="X11"/>
     </x:row>
     <x:row r="12" ht="78" customHeight="1">
       <x:c r="A12" s="65" t="str">
@@ -36514,6 +36973,7 @@
       <x:c r="W12" s="65" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
+      <x:c r="X12"/>
     </x:row>
     <x:row r="13" ht="78" customHeight="1">
       <x:c r="A13" s="65" t="str">
@@ -36585,6 +37045,7 @@
       <x:c r="W13" s="65" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
+      <x:c r="X13"/>
     </x:row>
     <x:row r="14" ht="78" customHeight="1">
       <x:c r="A14" s="65" t="str">
@@ -36656,6 +37117,9 @@
       <x:c r="W14" s="65" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
       </x:c>
+      <x:c r="X14" t="str">
+        <x:v>ELEMENT_01</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="78" customHeight="1">
       <x:c r="A15" s="65" t="str">
@@ -36727,6 +37191,9 @@
       <x:c r="W15" s="65" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
       </x:c>
+      <x:c r="X15" t="str">
+        <x:v>ELEMENT_02</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="78" customHeight="1">
       <x:c r="A16" s="65" t="str">
@@ -36798,6 +37265,9 @@
       <x:c r="W16" s="65" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
       </x:c>
+      <x:c r="X16" t="str">
+        <x:v>ELEMENT_01</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="78" customHeight="1">
       <x:c r="A17" s="65" t="str">
@@ -36869,6 +37339,9 @@
       <x:c r="W17" s="65" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
       </x:c>
+      <x:c r="X17" t="str">
+        <x:v>ELEMENT_03</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="78" customHeight="1">
       <x:c r="A18" s="65" t="str">
@@ -36940,6 +37413,9 @@
       <x:c r="W18" s="65" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
       </x:c>
+      <x:c r="X18" t="str">
+        <x:v>ELEMENT_04</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="78" customHeight="1">
       <x:c r="A19" s="69" t="str">
@@ -37010,6 +37486,9 @@
       </x:c>
       <x:c r="W19" s="69" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
+      </x:c>
+      <x:c r="X19" t="str">
+        <x:v>ELEMENT_04</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="78" customHeight="1">

--- a/app/template_knowledge/sources/영상편집DB.xlsx
+++ b/app/template_knowledge/sources/영상편집DB.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R2032648c311c49f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R33393f5afa1243f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R2e1b16fa1d6845fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R5908d5be669743be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="Rba65ef4661e54f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R109d77a2b9e64612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="Rf0ea8f17fd0b49ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="Rd3df3d48fe764a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="Re9ef99df09b442b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="Rbfdc28e7f10b4a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rd5383b432b494061"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R2f77975909b74c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R362a1cf81b04478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_SHOOTING_ELEMENTS" sheetId="14" r:id="R0a5b31abfd4445a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="Rb02fb4e0f78d4299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R957d946270794ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rf1d1b013f79f4ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="Rbd03cdf5e5d140ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R218b49595aef4d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R95bacf32a9274c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R85d474222f534c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R2c79fb41fc184654"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R10d5e2be3fc240a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R8c064e9afc654f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rd34ca7ace9084291"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R85e023adb3054d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R135fee6015c14eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_SHOOTING_ELEMENTS" sheetId="14" r:id="Rd42a589e09694f51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1214,7 +1214,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="26" t="str">
-        <x:v>최초 제공 템플릿의 시트/열 구조를 고정합니다. 주술회전·오츠카레 썸머·카페 추천 리뷰의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:W 안에서 관리하고, 5프레임 분석은 action_pattern·timing_rule에 흡수합니다.</x:v>
+        <x:v>최초 제공 템플릿의 시트/열 구조를 고정합니다. 기존 3종과 동그리오 2종의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:X 안에서 관리합니다.</x:v>
       </x:c>
       <x:c r="B2" s="26"/>
       <x:c r="C2" s="26"/>
@@ -1508,16 +1508,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>실제 가이드 3종</x:v>
+        <x:v>실제 가이드 5종</x:v>
       </x:c>
       <x:c r="B24" s="8" t="str">
-        <x:v>주술회전 트랜지션 · 오츠카레 썸머 챌린지 · 카페 추천 리뷰 릴스를 실제 레코드로 등록</x:v>
+        <x:v>기존 3종과 동그리오(챌린지)·동그리오(매장 홍보)를 실제 레코드로 등록</x:v>
       </x:c>
       <x:c r="C24" s="8" t="str">
-        <x:v>02, 03, 12</x:v>
+        <x:v>02, 03, 03A, 12</x:v>
       </x:c>
       <x:c r="D24" s="8" t="str">
-        <x:v>12_SOURCE_GUIDES에 원문/분석 근거를 보존하고, 실행용 정밀 프레임 규칙은 03의 action_pattern·timing_rule에 직접 연결</x:v>
+        <x:v>같은 영상의 편집 구조를 공유하되 챌린지 촬영 컷과 정보형 촬영 요소를 분리</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -35590,6 +35590,7881 @@
         <x:v>VIDEO_ANALYSIS</x:v>
       </x:c>
     </x:row>
+    <x:row r="939">
+      <x:c r="A939" t="str">
+        <x:v>donggeurio_line_0001</x:v>
+      </x:c>
+      <x:c r="B939" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C939" t="n">
+        <x:v>935</x:v>
+      </x:c>
+      <x:c r="D939" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E939" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F939" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G939" t="str">
+        <x:v>## 1. 기본 정보</x:v>
+      </x:c>
+      <x:c r="H939" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I939" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J939" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K939" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940">
+      <x:c r="A940" t="str">
+        <x:v>donggeurio_line_0002</x:v>
+      </x:c>
+      <x:c r="B940" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C940" t="n">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="D940" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E940" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F940" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G940" t="str">
+        <x:v>- **가이드 템플릿 ID (`guide_template_id`)**: `gt_matcha_crepe_review_v1`</x:v>
+      </x:c>
+      <x:c r="H940" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I940" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J940" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K940" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941">
+      <x:c r="A941" t="str">
+        <x:v>donggeurio_line_0003</x:v>
+      </x:c>
+      <x:c r="B941" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C941" t="n">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="D941" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E941" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F941" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G941" t="str">
+        <x:v>- **챌린지 ID (`challenge_id`)**: `food_making_asmr`</x:v>
+      </x:c>
+      <x:c r="H941" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I941" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J941" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K941" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942">
+      <x:c r="A942" t="str">
+        <x:v>donggeurio_line_0004</x:v>
+      </x:c>
+      <x:c r="B942" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C942" t="n">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="D942" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E942" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F942" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G942" t="str">
+        <x:v>- **총 영상 길이**: `45,000ms` / 약 45초</x:v>
+      </x:c>
+      <x:c r="H942" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I942" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J942" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K942" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943">
+      <x:c r="A943" t="str">
+        <x:v>donggeurio_line_0005</x:v>
+      </x:c>
+      <x:c r="B943" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C943" t="n">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="D943" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E943" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F943" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G943" t="str">
+        <x:v>- **분석 단위**: 장면별 구간 및 ms 기준 정밀 타이밍</x:v>
+      </x:c>
+      <x:c r="H943" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I943" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J943" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K943" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944">
+      <x:c r="A944" t="str">
+        <x:v>donggeurio_line_0006</x:v>
+      </x:c>
+      <x:c r="B944" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C944" t="n">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="D944" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E944" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F944" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G944" t="str">
+        <x:v>- **템플릿 기준 시트**: `03_GUIDE_TEMPLATES`</x:v>
+      </x:c>
+      <x:c r="H944" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I944" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J944" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K944" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945">
+      <x:c r="A945" t="str">
+        <x:v>donggeurio_line_0007</x:v>
+      </x:c>
+      <x:c r="B945" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C945" t="n">
+        <x:v>941</x:v>
+      </x:c>
+      <x:c r="D945" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E945" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F945" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G945" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H945" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I945" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J945" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K945" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946">
+      <x:c r="A946" t="str">
+        <x:v>donggeurio_line_0008</x:v>
+      </x:c>
+      <x:c r="B946" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C946" t="n">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="D946" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E946" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F946" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G946" t="str">
+        <x:v>## 2. GUIDE_TEMPLATE 세그먼트 분석</x:v>
+      </x:c>
+      <x:c r="H946" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I946" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J946" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K946" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947">
+      <x:c r="A947" t="str">
+        <x:v>donggeurio_line_0009</x:v>
+      </x:c>
+      <x:c r="B947" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C947" t="n">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="D947" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E947" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F947" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G947" t="str">
+        <x:v>| 순번 (`guide_sequence_index`) | 구간 (`start_ms ~ end_ms`) | 장면 요약 (`scene_summary`) | 내러티브 역할 (`narrative_role`) | 액션 패턴 (`action_pattern`) | 타이밍 규칙 (`timing_rule`) | 자막·개인화 및 편집 규칙 |</x:v>
+      </x:c>
+      <x:c r="H947" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I947" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J947" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K947" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948">
+      <x:c r="A948" t="str">
+        <x:v>donggeurio_line_0010</x:v>
+      </x:c>
+      <x:c r="B948" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C948" t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="D948" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E948" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F948" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G948" t="str">
+        <x:v>| --- | --- | --- | --- | --- | --- | --- |</x:v>
+      </x:c>
+      <x:c r="H948" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I948" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J948" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K948" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949">
+      <x:c r="A949" t="str">
+        <x:v>donggeurio_line_0011</x:v>
+      </x:c>
+      <x:c r="B949" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C949" t="n">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="D949" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E949" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F949" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G949" t="str">
+        <x:v>| **1** | `0 ~ 2,500ms` | 완성된 크레페 등장 | `HOOK` / 결과물 선공개 | **0~500ms**: 완성된 크레페 2개를 든 손이 화면 중앙을 채우며 결과물을 즉시 노출한다. 시작 프레임부터 메뉴 형태가 식별 가능해야 한다.</x:v>
+      </x:c>
+      <x:c r="H949" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I949" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J949" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K949" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950">
+      <x:c r="A950" t="str">
+        <x:v>donggeurio_line_0012</x:v>
+      </x:c>
+      <x:c r="B950" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C950" t="n">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="D950" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E950" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F950" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G950" t="str">
+        <x:v>**1,500~2,000ms**: 상단 브륄레 코팅의 광택과 질감을 보여주기 위해 손목을 이용한 미세한 좌우 틸팅이 발생한다. 카메라보다 피사체 움직임을 중심으로 질감을 강조한다. | `0ms`부터 가장 시각적 임팩트가 높은 완성 결과물을 노출한다.</x:v>
+      </x:c>
+      <x:c r="H950" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I950" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J950" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K950" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951">
+      <x:c r="A951" t="str">
+        <x:v>donggeurio_line_0013</x:v>
+      </x:c>
+      <x:c r="B951" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C951" t="n">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="D951" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E951" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F951" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G951" t="str">
+        <x:v>`2,500ms` 부근에서 제조 공정 장면으로 **Hard Cut** 한다.</x:v>
+      </x:c>
+      <x:c r="H951" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I951" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J951" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K951" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952">
+      <x:c r="A952" t="str">
+        <x:v>donggeurio_line_0014</x:v>
+      </x:c>
+      <x:c r="B952" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C952" t="n">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="D952" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E952" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F952" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G952" t="str">
+        <x:v>HOOK에서는 결과물의 형태·색상·질감이 인지되기 전에 컷하지 않는다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H952" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I952" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J952" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K952" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953">
+      <x:c r="A953" t="str">
+        <x:v>donggeurio_line_0015</x:v>
+      </x:c>
+      <x:c r="B953" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C953" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="D953" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E953" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F953" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G953" t="str">
+        <x:v>`13,000원이지만 또 먹고 싶은 말차 크레페입니다`</x:v>
+      </x:c>
+      <x:c r="H953" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I953" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J953" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K953" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954">
+      <x:c r="A954" t="str">
+        <x:v>donggeurio_line_0016</x:v>
+      </x:c>
+      <x:c r="B954" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C954" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="D954" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E954" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F954" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G954" t="str">
+        <x:v>**`personalization_rule`**</x:v>
+      </x:c>
+      <x:c r="H954" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I954" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J954" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K954" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955">
+      <x:c r="A955" t="str">
+        <x:v>donggeurio_line_0017</x:v>
+      </x:c>
+      <x:c r="B955" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C955" t="n">
+        <x:v>951</x:v>
+      </x:c>
+      <x:c r="D955" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E955" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F955" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G955" t="str">
+        <x:v>가격과 핵심 메뉴명은 사용자 매장 데이터에 따라 치환한다.</x:v>
+      </x:c>
+      <x:c r="H955" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I955" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J955" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K955" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956">
+      <x:c r="A956" t="str">
+        <x:v>donggeurio_line_0018</x:v>
+      </x:c>
+      <x:c r="B956" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C956" t="n">
+        <x:v>952</x:v>
+      </x:c>
+      <x:c r="D956" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E956" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F956" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G956" t="str">
+        <x:v>`{{price}}이지만 또 먹고 싶은 {{menu}}입니다` |</x:v>
+      </x:c>
+      <x:c r="H956" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I956" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J956" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K956" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957">
+      <x:c r="A957" t="str">
+        <x:v>donggeurio_line_0019</x:v>
+      </x:c>
+      <x:c r="B957" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C957" t="n">
+        <x:v>953</x:v>
+      </x:c>
+      <x:c r="D957" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E957" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F957" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G957" t="str">
+        <x:v>| **2** | `2,500 ~ 8,500ms` | 말차 반죽 붓고 펴기 | `BUILD_UP` / 공정 시작 | **2,500~2,800ms**: 국자를 이용해 짙은 녹색 말차 반죽을 철판 중앙에 투하한다. 액체가 철판 표면으로 퍼지기 시작하는 순간이 주요 시각 피크다.</x:v>
+      </x:c>
+      <x:c r="H957" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I957" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J957" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K957" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958">
+      <x:c r="A958" t="str">
+        <x:v>donggeurio_line_0020</x:v>
+      </x:c>
+      <x:c r="B958" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C958" t="n">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="D958" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E958" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F958" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G958" t="str">
+        <x:v>**3,200~8,000ms**: T자형 스패출러를 이용해 반죽을 시계 방향으로 회전시키며 얇고 균일하게 펼친다. 카메라는 `Static`을 유지하고 피사체의 원형 운동을 강조한다. | `2,500ms`에서 이전 HOOK 장면과 **Hard Cut**한다.</x:v>
+      </x:c>
+      <x:c r="H958" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I958" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J958" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K958" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959">
+      <x:c r="A959" t="str">
+        <x:v>donggeurio_line_0021</x:v>
+      </x:c>
+      <x:c r="B959" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C959" t="n">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="D959" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E959" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F959" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G959" t="str">
+        <x:v>반죽이 철판 전체로 충분히 퍼지고 원형 형태가 완성되는 모션 종료점 부근인 `8,500ms`에서 다음 장면으로 전환한다.</x:v>
+      </x:c>
+      <x:c r="H959" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I959" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J959" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K959" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960">
+      <x:c r="A960" t="str">
+        <x:v>donggeurio_line_0022</x:v>
+      </x:c>
+      <x:c r="B960" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C960" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="D960" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E960" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F960" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G960" t="str">
+        <x:v>반죽 확산 동작 중간에 불필요한 컷을 넣지 않는다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H960" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I960" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J960" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K960" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961">
+      <x:c r="A961" t="str">
+        <x:v>donggeurio_line_0023</x:v>
+      </x:c>
+      <x:c r="B961" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C961" t="n">
+        <x:v>957</x:v>
+      </x:c>
+      <x:c r="D961" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E961" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F961" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G961" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H961" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I961" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J961" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K961" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962">
+      <x:c r="A962" t="str">
+        <x:v>donggeurio_line_0024</x:v>
+      </x:c>
+      <x:c r="B962" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C962" t="n">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="D962" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E962" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F962" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G962" t="str">
+        <x:v>**`supported_edit_elements`**</x:v>
+      </x:c>
+      <x:c r="H962" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I962" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J962" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K962" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963">
+      <x:c r="A963" t="str">
+        <x:v>donggeurio_line_0025</x:v>
+      </x:c>
+      <x:c r="B963" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C963" t="n">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="D963" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E963" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F963" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G963" t="str">
+        <x:v>`sfx`</x:v>
+      </x:c>
+      <x:c r="H963" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I963" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J963" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K963" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964">
+      <x:c r="A964" t="str">
+        <x:v>donggeurio_line_0026</x:v>
+      </x:c>
+      <x:c r="B964" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C964" t="n">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="D964" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E964" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F964" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G964" t="str">
+        <x:v>반죽이 철판에 닿고 익기 시작하는 실제 조리음을 강조한다. |</x:v>
+      </x:c>
+      <x:c r="H964" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I964" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J964" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K964" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965">
+      <x:c r="A965" t="str">
+        <x:v>donggeurio_line_0027</x:v>
+      </x:c>
+      <x:c r="B965" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C965" t="n">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="D965" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E965" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F965" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G965" t="str">
+        <x:v>| **3** | `8,500 ~ 15,200ms` | 크레페 굽기 및 접기 | `BUILD_UP` / 질감 강조 | **8,500~11,000ms**: 스패출러가 반죽 아래로 진입한 뒤 익은 반죽을 들어 올려 반으로 접는다. 접히는 순간의 가장자리 움직임과 증기·열감이 주요 시각 정보다.</x:v>
+      </x:c>
+      <x:c r="H965" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I965" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J965" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K965" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966">
+      <x:c r="A966" t="str">
+        <x:v>donggeurio_line_0028</x:v>
+      </x:c>
+      <x:c r="B966" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C966" t="n">
+        <x:v>962</x:v>
+      </x:c>
+      <x:c r="D966" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E966" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F966" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G966" t="str">
+        <x:v>**11,000~15,200ms**: 반원 형태의 반죽을 다시 접어 부채꼴 형태로 만든 후 다음 조리 위치 또는 철망으로 이동한다. | 반죽의 익은 표면, 색상 변화, 접히는 질감이 충분히 식별되도록 구간을 유지한다.</x:v>
+      </x:c>
+      <x:c r="H966" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I966" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J966" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K966" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967">
+      <x:c r="A967" t="str">
+        <x:v>donggeurio_line_0029</x:v>
+      </x:c>
+      <x:c r="B967" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C967" t="n">
+        <x:v>963</x:v>
+      </x:c>
+      <x:c r="D967" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E967" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F967" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G967" t="str">
+        <x:v>`15,200ms`에서 속재료·토핑 공정으로 **Hard Cut** 한다.</x:v>
+      </x:c>
+      <x:c r="H967" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I967" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J967" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K967" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968">
+      <x:c r="A968" t="str">
+        <x:v>donggeurio_line_0030</x:v>
+      </x:c>
+      <x:c r="B968" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C968" t="n">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="D968" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E968" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F968" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G968" t="str">
+        <x:v>모션이 완료되기 직전에 컷하지 않고 접기 동작이 완결된 이후 전환한다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H968" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I968" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J968" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K968" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969">
+      <x:c r="A969" t="str">
+        <x:v>donggeurio_line_0031</x:v>
+      </x:c>
+      <x:c r="B969" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C969" t="n">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="D969" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E969" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F969" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G969" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H969" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I969" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J969" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K969" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970">
+      <x:c r="A970" t="str">
+        <x:v>donggeurio_line_0032</x:v>
+      </x:c>
+      <x:c r="B970" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C970" t="n">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="D970" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E970" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F970" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G970" t="str">
+        <x:v>**`capability_conflict_note`**</x:v>
+      </x:c>
+      <x:c r="H970" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I970" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J970" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K970" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971">
+      <x:c r="A971" t="str">
+        <x:v>donggeurio_line_0033</x:v>
+      </x:c>
+      <x:c r="B971" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C971" t="n">
+        <x:v>967</x:v>
+      </x:c>
+      <x:c r="D971" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E971" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F971" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G971" t="str">
+        <x:v>원본 영상의 저작권 있는 BGM 또는 음원의 박자·멜로디를 그대로 복제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H971" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I971" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J971" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K971" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972">
+      <x:c r="A972" t="str">
+        <x:v>donggeurio_line_0034</x:v>
+      </x:c>
+      <x:c r="B972" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C972" t="n">
+        <x:v>968</x:v>
+      </x:c>
+      <x:c r="D972" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E972" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F972" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G972" t="str">
+        <x:v>컷 타이밍은 시각적 동작 피크를 기준으로 독립적으로 재구성한다. |</x:v>
+      </x:c>
+      <x:c r="H972" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I972" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J972" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K972" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973">
+      <x:c r="A973" t="str">
+        <x:v>donggeurio_line_0035</x:v>
+      </x:c>
+      <x:c r="B973" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C973" t="n">
+        <x:v>969</x:v>
+      </x:c>
+      <x:c r="D973" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E973" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F973" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G973" t="str">
+        <x:v>| **4** | `15,200 ~ 28,000ms` | 생크림 및 속재료 토핑 | `CORE_ACTION` / 내부 시각화 | **15,200~20,000ms**: 짤주머니에서 생크림을 지그재그 또는 연속 패턴으로 압출한다. 크림이 반죽 위에 층을 형성하는 과정을 연속적으로 보여준다.</x:v>
+      </x:c>
+      <x:c r="H973" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I973" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J973" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K973" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974">
+      <x:c r="A974" t="str">
+        <x:v>donggeurio_line_0036</x:v>
+      </x:c>
+      <x:c r="B974" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C974" t="n">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="D974" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E974" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F974" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G974" t="str">
+        <x:v>**20,500~27,000ms**: 핀셋·스푼 등을 이용해 베리류 또는 기타 토핑을 배치한다. 작업자의 손·도구와 재료 간 색상 및 질감 대비를 강조한다. | 크림 압출과 토핑 배치는 각각 하나의 완결된 작업 단위로 유지한다.</x:v>
+      </x:c>
+      <x:c r="H974" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I974" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J974" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K974" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975">
+      <x:c r="A975" t="str">
+        <x:v>donggeurio_line_0037</x:v>
+      </x:c>
+      <x:c r="B975" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C975" t="n">
+        <x:v>971</x:v>
+      </x:c>
+      <x:c r="D975" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E975" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F975" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G975" t="str">
+        <x:v>크림 → 토핑 순서를 유지하고, `28,000ms` 부근에서 포장·형태 완성 단계로 전환한다.</x:v>
+      </x:c>
+      <x:c r="H975" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I975" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J975" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K975" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976">
+      <x:c r="A976" t="str">
+        <x:v>donggeurio_line_0038</x:v>
+      </x:c>
+      <x:c r="B976" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C976" t="n">
+        <x:v>972</x:v>
+      </x:c>
+      <x:c r="D976" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E976" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F976" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G976" t="str">
+        <x:v>조리 과정의 이해를 방해하는 과도한 점프컷은 피한다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H976" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I976" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J976" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K976" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977">
+      <x:c r="A977" t="str">
+        <x:v>donggeurio_line_0039</x:v>
+      </x:c>
+      <x:c r="B977" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C977" t="n">
+        <x:v>973</x:v>
+      </x:c>
+      <x:c r="D977" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E977" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F977" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G977" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H977" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I977" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J977" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K977" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978">
+      <x:c r="A978" t="str">
+        <x:v>donggeurio_line_0040</x:v>
+      </x:c>
+      <x:c r="B978" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C978" t="n">
+        <x:v>974</x:v>
+      </x:c>
+      <x:c r="D978" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E978" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F978" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G978" t="str">
+        <x:v>**`personalization_rule`**</x:v>
+      </x:c>
+      <x:c r="H978" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I978" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J978" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K978" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979">
+      <x:c r="A979" t="str">
+        <x:v>donggeurio_line_0041</x:v>
+      </x:c>
+      <x:c r="B979" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C979" t="n">
+        <x:v>975</x:v>
+      </x:c>
+      <x:c r="D979" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E979" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F979" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G979" t="str">
+        <x:v>사용자 원본 영상의 길이가 긴 경우 토핑 반복 동작만 선택적으로 축약하거나 최대 약 `1.2x` 수준으로 속도 조절할 수 있다.</x:v>
+      </x:c>
+      <x:c r="H979" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I979" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J979" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K979" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980">
+      <x:c r="A980" t="str">
+        <x:v>donggeurio_line_0042</x:v>
+      </x:c>
+      <x:c r="B980" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C980" t="n">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="D980" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E980" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F980" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G980" t="str">
+        <x:v>단, 실제 토핑 종류나 제조 순서를 임의로 변경하지 않는다. |</x:v>
+      </x:c>
+      <x:c r="H980" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I980" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J980" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K980" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981">
+      <x:c r="A981" t="str">
+        <x:v>donggeurio_line_0043</x:v>
+      </x:c>
+      <x:c r="B981" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C981" t="n">
+        <x:v>977</x:v>
+      </x:c>
+      <x:c r="D981" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E981" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F981" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G981" t="str">
+        <x:v>| **5** | `28,000 ~ 38,000ms` | 형태 잡기 및 상단 평탄화 | `CLIMAX_PREP` / 마무리 준비 | **28,000~30,000ms**: 종이 포장지를 이용해 부채꼴 반죽을 감싸 콘 형태로 고정한다.</x:v>
+      </x:c>
+      <x:c r="H981" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I981" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J981" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K981" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982">
+      <x:c r="A982" t="str">
+        <x:v>donggeurio_line_0044</x:v>
+      </x:c>
+      <x:c r="B982" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C982" t="n">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="D982" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E982" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F982" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G982" t="str">
+        <x:v>**30,000~35,000ms**: 상단 빈 공간에 크림을 추가로 채운 후 스패출러를 이용해 표면을 평탄화한다.</x:v>
+      </x:c>
+      <x:c r="H982" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I982" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J982" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K982" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983">
+      <x:c r="A983" t="str">
+        <x:v>donggeurio_line_0045</x:v>
+      </x:c>
+      <x:c r="B983" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C983" t="n">
+        <x:v>979</x:v>
+      </x:c>
+      <x:c r="D983" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E983" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F983" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G983" t="str">
+        <x:v>**35,000~38,000ms**: 평탄화된 표면에 설탕 등을 고르게 뿌린다. 미세한 입자가 표면에 떨어지는 시각적 변화를 강조한다. | 후반부 하이라이트를 준비하는 장면이므로 화면의 시선을 크레페 상단으로 집중시킨다.</x:v>
+      </x:c>
+      <x:c r="H983" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I983" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J983" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K983" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984">
+      <x:c r="A984" t="str">
+        <x:v>donggeurio_line_0046</x:v>
+      </x:c>
+      <x:c r="B984" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C984" t="n">
+        <x:v>980</x:v>
+      </x:c>
+      <x:c r="D984" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E984" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F984" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G984" t="str">
+        <x:v>가능한 경우 타이트한 `Close-up` 구도를 사용한다.</x:v>
+      </x:c>
+      <x:c r="H984" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I984" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J984" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K984" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985">
+      <x:c r="A985" t="str">
+        <x:v>donggeurio_line_0047</x:v>
+      </x:c>
+      <x:c r="B985" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C985" t="n">
+        <x:v>981</x:v>
+      </x:c>
+      <x:c r="D985" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E985" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F985" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G985" t="str">
+        <x:v>설탕 도포가 완료되는 `38,000ms` 부근에서 토치 장면으로 연결한다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H985" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I985" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J985" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K985" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986">
+      <x:c r="A986" t="str">
+        <x:v>donggeurio_line_0048</x:v>
+      </x:c>
+      <x:c r="B986" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C986" t="n">
+        <x:v>982</x:v>
+      </x:c>
+      <x:c r="D986" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E986" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F986" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G986" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H986" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I986" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J986" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K986" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987">
+      <x:c r="A987" t="str">
+        <x:v>donggeurio_line_0049</x:v>
+      </x:c>
+      <x:c r="B987" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C987" t="n">
+        <x:v>983</x:v>
+      </x:c>
+      <x:c r="D987" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E987" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F987" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G987" t="str">
+        <x:v>**`source_preservation`**</x:v>
+      </x:c>
+      <x:c r="H987" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I987" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J987" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K987" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988">
+      <x:c r="A988" t="str">
+        <x:v>donggeurio_line_0050</x:v>
+      </x:c>
+      <x:c r="B988" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C988" t="n">
+        <x:v>984</x:v>
+      </x:c>
+      <x:c r="D988" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E988" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F988" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G988" t="str">
+        <x:v>평탄화·설탕 도포와 같이 조리 결과를 직접 변화시키는 핵심 동작은 지나치게 잘게 분할하지 않고 원본 동작 흐름을 보존한다. |</x:v>
+      </x:c>
+      <x:c r="H988" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I988" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J988" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K988" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989">
+      <x:c r="A989" t="str">
+        <x:v>donggeurio_line_0051</x:v>
+      </x:c>
+      <x:c r="B989" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C989" t="n">
+        <x:v>985</x:v>
+      </x:c>
+      <x:c r="D989" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E989" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F989" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G989" t="str">
+        <x:v>| **6** | `38,000 ~ 45,000ms` | 토치 브륄레 및 질감 강조 | `CLIMAX_OUTRO` / 하이라이트 및 종료 | **38,000~42,000ms**: 토치의 불꽃이 설탕 표면을 가열하면서 표면 색상이 점차 갈색으로 변화하고 캐러멜라이징이 발생한다. 기포·광택·그을림 변화가 가장 중요한 시각적 피크다.</x:v>
+      </x:c>
+      <x:c r="H989" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I989" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J989" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K989" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990">
+      <x:c r="A990" t="str">
+        <x:v>donggeurio_line_0052</x:v>
+      </x:c>
+      <x:c r="B990" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C990" t="n">
+        <x:v>986</x:v>
+      </x:c>
+      <x:c r="D990" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E990" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F990" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G990" t="str">
+        <x:v>**42,000~45,000ms**: 완성된 브륄레 표면과 크레페의 최종 질감을 근접 촬영으로 보여준다. 필요 시 도구로 표면을 가볍게 건드리는 장면을 활용해 바삭한 질감을 강조한다. | `38,000ms` 전후의 토치 점화 또는 불꽃이 표면에 처음 닿는 순간에 SFX를 매핑할 수 있다.</x:v>
+      </x:c>
+      <x:c r="H990" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I990" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J990" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K990" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991">
+      <x:c r="A991" t="str">
+        <x:v>donggeurio_line_0053</x:v>
+      </x:c>
+      <x:c r="B991" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C991" t="n">
+        <x:v>987</x:v>
+      </x:c>
+      <x:c r="D991" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E991" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F991" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G991" t="str">
+        <x:v>캐러멜라이징 진행 과정은 시각적 변화 자체가 핵심이므로 지나친 컷 분할 없이 연속 재생한다.</x:v>
+      </x:c>
+      <x:c r="H991" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I991" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J991" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K991" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992">
+      <x:c r="A992" t="str">
+        <x:v>donggeurio_line_0054</x:v>
+      </x:c>
+      <x:c r="B992" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C992" t="n">
+        <x:v>988</x:v>
+      </x:c>
+      <x:c r="D992" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E992" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F992" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G992" t="str">
+        <x:v>완성 질감을 충분히 노출한 뒤 **Cut-out** 또는 자연스러운 종료를 사용한다. | **`guide_on_screen_text`**</x:v>
+      </x:c>
+      <x:c r="H992" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I992" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J992" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K992" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993">
+      <x:c r="A993" t="str">
+        <x:v>donggeurio_line_0055</x:v>
+      </x:c>
+      <x:c r="B993" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C993" t="n">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="D993" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E993" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F993" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G993" t="str">
+        <x:v>없음</x:v>
+      </x:c>
+      <x:c r="H993" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I993" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J993" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K993" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994">
+      <x:c r="A994" t="str">
+        <x:v>donggeurio_line_0056</x:v>
+      </x:c>
+      <x:c r="B994" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C994" t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="D994" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E994" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F994" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G994" t="str">
+        <x:v>**`supported_edit_elements`**</x:v>
+      </x:c>
+      <x:c r="H994" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I994" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J994" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K994" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995">
+      <x:c r="A995" t="str">
+        <x:v>donggeurio_line_0057</x:v>
+      </x:c>
+      <x:c r="B995" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C995" t="n">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="D995" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E995" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F995" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G995" t="str">
+        <x:v>`video`, `sfx`, `color_grading`</x:v>
+      </x:c>
+      <x:c r="H995" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I995" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J995" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K995" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996">
+      <x:c r="A996" t="str">
+        <x:v>donggeurio_line_0058</x:v>
+      </x:c>
+      <x:c r="B996" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C996" t="n">
+        <x:v>992</x:v>
+      </x:c>
+      <x:c r="D996" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E996" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F996" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G996" t="str">
+        <x:v>색보정은 토치 불꽃과 브륄레 표면의 질감을 명확하게 만드는 범위에서만 적용한다. |</x:v>
+      </x:c>
+      <x:c r="H996" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I996" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J996" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K996" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997">
+      <x:c r="A997" t="str">
+        <x:v>donggeurio_line_0059</x:v>
+      </x:c>
+      <x:c r="B997" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C997" t="n">
+        <x:v>993</x:v>
+      </x:c>
+      <x:c r="D997" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E997" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F997" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G997" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H997" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I997" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J997" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K997" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998">
+      <x:c r="A998" t="str">
+        <x:v>donggeurio_line_0060</x:v>
+      </x:c>
+      <x:c r="B998" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C998" t="n">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="D998" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E998" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F998" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G998" t="str">
+        <x:v>## 3. `action_pattern` 작성 기준</x:v>
+      </x:c>
+      <x:c r="H998" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I998" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J998" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K998" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999">
+      <x:c r="A999" t="str">
+        <x:v>donggeurio_line_0061</x:v>
+      </x:c>
+      <x:c r="B999" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C999" t="n">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="D999" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E999" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F999" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G999" t="str">
+        <x:v>`03_GUIDE_TEMPLATES`에는 별도의 프레임 분석용 컬럼을 추가하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H999" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I999" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J999" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K999" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000">
+      <x:c r="A1000" t="str">
+        <x:v>donggeurio_line_0062</x:v>
+      </x:c>
+      <x:c r="B1000" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1000" t="n">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="D1000" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1000" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1000" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G1000" t="str">
+        <x:v>프레임 및 세부 동작 분석 결과는 각 세그먼트의 `action_pattern` 안에 다음 정보를 포함하는 형태로 기록한다.</x:v>
+      </x:c>
+      <x:c r="H1000" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1000" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1000" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1000" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="A1001" t="str">
+        <x:v>donggeurio_line_0063</x:v>
+      </x:c>
+      <x:c r="B1001" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1001" t="n">
+        <x:v>997</x:v>
+      </x:c>
+      <x:c r="D1001" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1001" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1001" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G1001" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1001" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1001" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1001" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1001" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002">
+      <x:c r="A1002" t="str">
+        <x:v>donggeurio_line_0064</x:v>
+      </x:c>
+      <x:c r="B1002" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1002" t="n">
+        <x:v>998</x:v>
+      </x:c>
+      <x:c r="D1002" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1002" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1002" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G1002" t="str">
+        <x:v>[시간 구간]</x:v>
+      </x:c>
+      <x:c r="H1002" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1002" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1002" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1002" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003">
+      <x:c r="A1003" t="str">
+        <x:v>donggeurio_line_0065</x:v>
+      </x:c>
+      <x:c r="B1003" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1003" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="D1003" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1003" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1003" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G1003" t="str">
+        <x:v>- 피사체 행동</x:v>
+      </x:c>
+      <x:c r="H1003" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1003" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1003" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1003" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004">
+      <x:c r="A1004" t="str">
+        <x:v>donggeurio_line_0066</x:v>
+      </x:c>
+      <x:c r="B1004" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1004" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D1004" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1004" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1004" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G1004" t="str">
+        <x:v>- 손 또는 도구의 움직임</x:v>
+      </x:c>
+      <x:c r="H1004" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1004" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1004" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1004" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005">
+      <x:c r="A1005" t="str">
+        <x:v>donggeurio_line_0067</x:v>
+      </x:c>
+      <x:c r="B1005" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1005" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="D1005" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1005" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1005" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G1005" t="str">
+        <x:v>- 메뉴·상품의 상태 변화</x:v>
+      </x:c>
+      <x:c r="H1005" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1005" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1005" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1005" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006">
+      <x:c r="A1006" t="str">
+        <x:v>donggeurio_line_0068</x:v>
+      </x:c>
+      <x:c r="B1006" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1006" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="D1006" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1006" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1006" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G1006" t="str">
+        <x:v>- 카메라 움직임</x:v>
+      </x:c>
+      <x:c r="H1006" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1006" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1006" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1006" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007">
+      <x:c r="A1007" t="str">
+        <x:v>donggeurio_line_0069</x:v>
+      </x:c>
+      <x:c r="B1007" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1007" t="n">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="D1007" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1007" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1007" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G1007" t="str">
+        <x:v>- 주요 시각 피크</x:v>
+      </x:c>
+      <x:c r="H1007" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1007" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1007" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1007" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008">
+      <x:c r="A1008" t="str">
+        <x:v>donggeurio_line_0070</x:v>
+      </x:c>
+      <x:c r="B1008" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1008" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="D1008" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1008" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1008" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G1008" t="str">
+        <x:v>- 컷 전 반드시 보존해야 하는 동작</x:v>
+      </x:c>
+      <x:c r="H1008" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1008" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1008" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1008" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009">
+      <x:c r="A1009" t="str">
+        <x:v>donggeurio_line_0071</x:v>
+      </x:c>
+      <x:c r="B1009" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1009" t="n">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="D1009" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1009" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1009" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G1009" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1009" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1009" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1009" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1009" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010">
+      <x:c r="A1010" t="str">
+        <x:v>donggeurio_line_0072</x:v>
+      </x:c>
+      <x:c r="B1010" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1010" t="n">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="D1010" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1010" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1010" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G1010" t="str">
+        <x:v>예시:</x:v>
+      </x:c>
+      <x:c r="H1010" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1010" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1010" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1010" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011">
+      <x:c r="A1011" t="str">
+        <x:v>donggeurio_line_0073</x:v>
+      </x:c>
+      <x:c r="B1011" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1011" t="n">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="D1011" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1011" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1011" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G1011" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1011" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1011" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1011" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1011" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012">
+      <x:c r="A1012" t="str">
+        <x:v>donggeurio_line_0074</x:v>
+      </x:c>
+      <x:c r="B1012" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1012" t="n">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="D1012" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1012" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1012" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G1012" t="str">
+        <x:v>[38000~42000ms]</x:v>
+      </x:c>
+      <x:c r="H1012" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1012" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1012" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1012" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013">
+      <x:c r="A1013" t="str">
+        <x:v>donggeurio_line_0075</x:v>
+      </x:c>
+      <x:c r="B1013" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1013" t="n">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="D1013" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1013" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1013" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G1013" t="str">
+        <x:v>토치 불꽃이 설탕 표면에 닿으며 캐러멜라이징 시작.</x:v>
+      </x:c>
+      <x:c r="H1013" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1013" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1013" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1013" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014">
+      <x:c r="A1014" t="str">
+        <x:v>donggeurio_line_0076</x:v>
+      </x:c>
+      <x:c r="B1014" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1014" t="n">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="D1014" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1014" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1014" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G1014" t="str">
+        <x:v>표면 색상이 연한 황색 → 갈색으로 변화하며 기포와 광택이 발생.</x:v>
+      </x:c>
+      <x:c r="H1014" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1014" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1014" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1014" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015">
+      <x:c r="A1015" t="str">
+        <x:v>donggeurio_line_0077</x:v>
+      </x:c>
+      <x:c r="B1015" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1015" t="n">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="D1015" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1015" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1015" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G1015" t="str">
+        <x:v>불꽃 최초 접촉 프레임과 표면 색 변화 시작 프레임을 핵심 모션 피크로 사용.</x:v>
+      </x:c>
+      <x:c r="H1015" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1015" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1015" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1015" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016">
+      <x:c r="A1016" t="str">
+        <x:v>donggeurio_line_0078</x:v>
+      </x:c>
+      <x:c r="B1016" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1016" t="n">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="D1016" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1016" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1016" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G1016" t="str">
+        <x:v>카메라는 Close-up Static을 유지.</x:v>
+      </x:c>
+      <x:c r="H1016" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1016" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1016" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1016" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017">
+      <x:c r="A1017" t="str">
+        <x:v>donggeurio_line_0079</x:v>
+      </x:c>
+      <x:c r="B1017" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1017" t="n">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="D1017" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1017" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1017" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G1017" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1017" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1017" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1017" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1017" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018">
+      <x:c r="A1018" t="str">
+        <x:v>donggeurio_line_0080</x:v>
+      </x:c>
+      <x:c r="B1018" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1018" t="n">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="D1018" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1018" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1018" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G1018" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1018" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1018" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1018" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1018" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019">
+      <x:c r="A1019" t="str">
+        <x:v>donggeurio_line_0081</x:v>
+      </x:c>
+      <x:c r="B1019" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1019" t="n">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="D1019" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1019" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1019" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G1019" t="str">
+        <x:v>## 4. `timing_rule` 작성 기준</x:v>
+      </x:c>
+      <x:c r="H1019" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1019" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1019" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1019" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020">
+      <x:c r="A1020" t="str">
+        <x:v>donggeurio_line_0082</x:v>
+      </x:c>
+      <x:c r="B1020" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1020" t="n">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="D1020" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1020" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1020" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G1020" t="str">
+        <x:v>`timing_rule`에는 단순히 구간의 시작·종료 시간만 기록하지 않고, 실제 편집 Agent가 판단에 사용할 수 있는 **편집 의사결정 규칙**을 기록한다.</x:v>
+      </x:c>
+      <x:c r="H1020" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1020" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1020" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1020" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021">
+      <x:c r="A1021" t="str">
+        <x:v>donggeurio_line_0083</x:v>
+      </x:c>
+      <x:c r="B1021" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1021" t="n">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="D1021" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1021" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1021" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G1021" t="str">
+        <x:v>주요 기록 대상은 다음과 같다.</x:v>
+      </x:c>
+      <x:c r="H1021" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1021" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1021" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1021" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022">
+      <x:c r="A1022" t="str">
+        <x:v>donggeurio_line_0084</x:v>
+      </x:c>
+      <x:c r="B1022" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1022" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="D1022" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1022" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1022" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G1022" t="str">
+        <x:v>- 컷 시작 조건</x:v>
+      </x:c>
+      <x:c r="H1022" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1022" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1022" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1022" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023">
+      <x:c r="A1023" t="str">
+        <x:v>donggeurio_line_0085</x:v>
+      </x:c>
+      <x:c r="B1023" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1023" t="n">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="D1023" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1023" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1023" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G1023" t="str">
+        <x:v>- 컷 종료 조건</x:v>
+      </x:c>
+      <x:c r="H1023" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1023" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1023" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1023" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024">
+      <x:c r="A1024" t="str">
+        <x:v>donggeurio_line_0086</x:v>
+      </x:c>
+      <x:c r="B1024" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1024" t="n">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="D1024" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1024" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1024" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G1024" t="str">
+        <x:v>- 동작의 Peak 시점</x:v>
+      </x:c>
+      <x:c r="H1024" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1024" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1024" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1024" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025">
+      <x:c r="A1025" t="str">
+        <x:v>donggeurio_line_0087</x:v>
+      </x:c>
+      <x:c r="B1025" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1025" t="n">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="D1025" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1025" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1025" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G1025" t="str">
+        <x:v>- Hard Cut 여부</x:v>
+      </x:c>
+      <x:c r="H1025" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1025" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1025" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1025" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026">
+      <x:c r="A1026" t="str">
+        <x:v>donggeurio_line_0088</x:v>
+      </x:c>
+      <x:c r="B1026" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1026" t="n">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="D1026" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1026" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1026" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G1026" t="str">
+        <x:v>- Long Take 유지 여부</x:v>
+      </x:c>
+      <x:c r="H1026" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1026" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1026" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1026" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027">
+      <x:c r="A1027" t="str">
+        <x:v>donggeurio_line_0089</x:v>
+      </x:c>
+      <x:c r="B1027" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1027" t="n">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="D1027" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1027" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1027" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G1027" t="str">
+        <x:v>- 모션 완료 후 컷 여부</x:v>
+      </x:c>
+      <x:c r="H1027" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1027" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1027" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1027" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028">
+      <x:c r="A1028" t="str">
+        <x:v>donggeurio_line_0090</x:v>
+      </x:c>
+      <x:c r="B1028" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1028" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="D1028" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1028" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1028" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G1028" t="str">
+        <x:v>- SFX 삽입 시점</x:v>
+      </x:c>
+      <x:c r="H1028" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1028" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1028" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1028" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029">
+      <x:c r="A1029" t="str">
+        <x:v>donggeurio_line_0091</x:v>
+      </x:c>
+      <x:c r="B1029" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1029" t="n">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="D1029" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1029" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1029" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G1029" t="str">
+        <x:v>- 속도 조절 가능 구간</x:v>
+      </x:c>
+      <x:c r="H1029" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1029" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1029" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1029" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030">
+      <x:c r="A1030" t="str">
+        <x:v>donggeurio_line_0092</x:v>
+      </x:c>
+      <x:c r="B1030" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1030" t="n">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="D1030" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1030" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1030" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G1030" t="str">
+        <x:v>- 카메라 구도 유지 조건</x:v>
+      </x:c>
+      <x:c r="H1030" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1030" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1030" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1030" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031">
+      <x:c r="A1031" t="str">
+        <x:v>donggeurio_line_0093</x:v>
+      </x:c>
+      <x:c r="B1031" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1031" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="D1031" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1031" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1031" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G1031" t="str">
+        <x:v>예시:</x:v>
+      </x:c>
+      <x:c r="H1031" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1031" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1031" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1031" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032">
+      <x:c r="A1032" t="str">
+        <x:v>donggeurio_line_0094</x:v>
+      </x:c>
+      <x:c r="B1032" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1032" t="n">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="D1032" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1032" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1032" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G1032" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1032" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1032" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1032" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1032" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033">
+      <x:c r="A1033" t="str">
+        <x:v>donggeurio_line_0095</x:v>
+      </x:c>
+      <x:c r="B1033" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1033" t="n">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="D1033" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1033" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1033" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G1033" t="str">
+        <x:v>38000ms 전후 토치 불꽃 최초 접촉 지점에서 SFX 동기화.</x:v>
+      </x:c>
+      <x:c r="H1033" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1033" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1033" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1033" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034">
+      <x:c r="A1034" t="str">
+        <x:v>donggeurio_line_0096</x:v>
+      </x:c>
+      <x:c r="B1034" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1034" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="D1034" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1034" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1034" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G1034" t="str">
+        <x:v>캐러멜라이징에 따른 색상 변화가 시작된 이후에는 중간 컷을 금지하고</x:v>
+      </x:c>
+      <x:c r="H1034" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1034" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1034" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1034" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035">
+      <x:c r="A1035" t="str">
+        <x:v>donggeurio_line_0097</x:v>
+      </x:c>
+      <x:c r="B1035" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1035" t="n">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="D1035" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1035" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1035" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G1035" t="str">
+        <x:v>표면 갈변이 충분히 인지될 때까지 연속 재생.</x:v>
+      </x:c>
+      <x:c r="H1035" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1035" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1035" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1035" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036">
+      <x:c r="A1036" t="str">
+        <x:v>donggeurio_line_0098</x:v>
+      </x:c>
+      <x:c r="B1036" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1036" t="n">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="D1036" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1036" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1036" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G1036" t="str">
+        <x:v>완성 질감 노출 이후 영상 종료.</x:v>
+      </x:c>
+      <x:c r="H1036" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1036" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1036" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1036" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037">
+      <x:c r="A1037" t="str">
+        <x:v>donggeurio_line_0099</x:v>
+      </x:c>
+      <x:c r="B1037" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1037" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="D1037" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1037" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1037" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G1037" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1037" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1037" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1037" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1037" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038">
+      <x:c r="A1038" t="str">
+        <x:v>donggeurio_line_0100</x:v>
+      </x:c>
+      <x:c r="B1038" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1038" t="n">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="D1038" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1038" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1038" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G1038" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1038" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1038" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1038" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1038" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039">
+      <x:c r="A1039" t="str">
+        <x:v>donggeurio_line_0101</x:v>
+      </x:c>
+      <x:c r="B1039" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1039" t="n">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="D1039" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1039" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1039" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G1039" t="str">
+        <x:v>## 5. 자막 생성 원칙</x:v>
+      </x:c>
+      <x:c r="H1039" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1039" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1039" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1039" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040">
+      <x:c r="A1040" t="str">
+        <x:v>donggeurio_line_0102</x:v>
+      </x:c>
+      <x:c r="B1040" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1040" t="n">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="D1040" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1040" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1040" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G1040" t="str">
+        <x:v>레퍼런스 영상의 실제 자막 문구는 새로운 사용자 영상에 **고정 템플릿 값으로 재사용하지 않는다.**</x:v>
+      </x:c>
+      <x:c r="H1040" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1040" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1040" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1040" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041">
+      <x:c r="A1041" t="str">
+        <x:v>donggeurio_line_0103</x:v>
+      </x:c>
+      <x:c r="B1041" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1041" t="n">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="D1041" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1041" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1041" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G1041" t="str">
+        <x:v>`guide_on_screen_text`는 레퍼런스 분석 및 자막 역할 파악을 위한 근거로 사용할 수 있지만, 실제 사용자 영상 편집 시에는 LLM이 다음 정보를 바탕으로 새로운 자막을 생성한다.</x:v>
+      </x:c>
+      <x:c r="H1041" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1041" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1041" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1041" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042">
+      <x:c r="A1042" t="str">
+        <x:v>donggeurio_line_0104</x:v>
+      </x:c>
+      <x:c r="B1042" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1042" t="n">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="D1042" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1042" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1042" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G1042" t="str">
+        <x:v>- 실제 촬영된 메뉴·상품</x:v>
+      </x:c>
+      <x:c r="H1042" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1042" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1042" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1042" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043">
+      <x:c r="A1043" t="str">
+        <x:v>donggeurio_line_0105</x:v>
+      </x:c>
+      <x:c r="B1043" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1043" t="n">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="D1043" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1043" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1043" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G1043" t="str">
+        <x:v>- 홍보 목적</x:v>
+      </x:c>
+      <x:c r="H1043" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1043" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1043" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1043" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044">
+      <x:c r="A1044" t="str">
+        <x:v>donggeurio_line_0106</x:v>
+      </x:c>
+      <x:c r="B1044" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1044" t="n">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="D1044" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1044" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1044" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G1044" t="str">
+        <x:v>- 매장 정보</x:v>
+      </x:c>
+      <x:c r="H1044" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1044" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1044" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1044" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045">
+      <x:c r="A1045" t="str">
+        <x:v>donggeurio_line_0107</x:v>
+      </x:c>
+      <x:c r="B1045" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1045" t="n">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="D1045" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1045" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1045" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G1045" t="str">
+        <x:v>- 영상 내 장면 내용</x:v>
+      </x:c>
+      <x:c r="H1045" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1045" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1045" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1045" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046">
+      <x:c r="A1046" t="str">
+        <x:v>donggeurio_line_0108</x:v>
+      </x:c>
+      <x:c r="B1046" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1046" t="n">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="D1046" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1046" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1046" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G1046" t="str">
+        <x:v>- 해당 장면의 `narrative_role`</x:v>
+      </x:c>
+      <x:c r="H1046" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1046" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1046" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1046" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047">
+      <x:c r="A1047" t="str">
+        <x:v>donggeurio_line_0109</x:v>
+      </x:c>
+      <x:c r="B1047" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1047" t="n">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="D1047" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1047" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1047" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G1047" t="str">
+        <x:v>- 템플릿에서 정의한 자막 스타일·길이·위치·타이밍 패턴</x:v>
+      </x:c>
+      <x:c r="H1047" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1047" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1047" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1047" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048">
+      <x:c r="A1048" t="str">
+        <x:v>donggeurio_line_0110</x:v>
+      </x:c>
+      <x:c r="B1048" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1048" t="n">
+        <x:v>1044</x:v>
+      </x:c>
+      <x:c r="D1048" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1048" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1048" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G1048" t="str">
+        <x:v>따라서 다음과 같은 문구:</x:v>
+      </x:c>
+      <x:c r="H1048" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1048" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1048" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1048" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1049">
+      <x:c r="A1049" t="str">
+        <x:v>donggeurio_line_0111</x:v>
+      </x:c>
+      <x:c r="B1049" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1049" t="n">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="D1049" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1049" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1049" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G1049" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1049" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1049" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1049" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1049" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1050">
+      <x:c r="A1050" t="str">
+        <x:v>donggeurio_line_0112</x:v>
+      </x:c>
+      <x:c r="B1050" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1050" t="n">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="D1050" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1050" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1050" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G1050" t="str">
+        <x:v>13,000원이지만 또 먹고 싶은 말차 크레페입니다</x:v>
+      </x:c>
+      <x:c r="H1050" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1050" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1050" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1050" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1051">
+      <x:c r="A1051" t="str">
+        <x:v>donggeurio_line_0113</x:v>
+      </x:c>
+      <x:c r="B1051" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1051" t="n">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="D1051" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1051" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1051" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G1051" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1051" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1051" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1051" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1051" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1052">
+      <x:c r="A1052" t="str">
+        <x:v>donggeurio_line_0114</x:v>
+      </x:c>
+      <x:c r="B1052" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1052" t="n">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="D1052" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1052" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1052" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G1052" t="str">
+        <x:v>는 그대로 재사용하는 고정 문구가 아니라 다음과 같은 **자막 의도 및 구조**로 활용한다.</x:v>
+      </x:c>
+      <x:c r="H1052" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1052" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1052" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1052" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1053">
+      <x:c r="A1053" t="str">
+        <x:v>donggeurio_line_0115</x:v>
+      </x:c>
+      <x:c r="B1053" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1053" t="n">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="D1053" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1053" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1053" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G1053" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1053" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1053" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1053" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1053" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1054">
+      <x:c r="A1054" t="str">
+        <x:v>donggeurio_line_0116</x:v>
+      </x:c>
+      <x:c r="B1054" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1054" t="n">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="D1054" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1054" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1054" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G1054" t="str">
+        <x:v>[가격 또는 특징] + [재방문/추천 의도] + [핵심 메뉴명]</x:v>
+      </x:c>
+      <x:c r="H1054" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1054" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1054" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1054" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1055">
+      <x:c r="A1055" t="str">
+        <x:v>donggeurio_line_0117</x:v>
+      </x:c>
+      <x:c r="B1055" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1055" t="n">
+        <x:v>1051</x:v>
+      </x:c>
+      <x:c r="D1055" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1055" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1055" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G1055" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1055" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1055" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1055" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1055" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1056">
+      <x:c r="A1056" t="str">
+        <x:v>donggeurio_line_0118</x:v>
+      </x:c>
+      <x:c r="B1056" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1056" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="D1056" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1056" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1056" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G1056" t="str">
+        <x:v>사용자 영상에서는 예를 들어 다음 슬롯을 기반으로 새 문장을 생성할 수 있다.</x:v>
+      </x:c>
+      <x:c r="H1056" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1056" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1056" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1056" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1057">
+      <x:c r="A1057" t="str">
+        <x:v>donggeurio_line_0119</x:v>
+      </x:c>
+      <x:c r="B1057" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1057" t="n">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="D1057" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1057" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1057" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G1057" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1057" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1057" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1057" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1057" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1058">
+      <x:c r="A1058" t="str">
+        <x:v>donggeurio_line_0120</x:v>
+      </x:c>
+      <x:c r="B1058" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1058" t="n">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="D1058" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1058" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1058" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G1058" t="str">
+        <x:v>{{price}}</x:v>
+      </x:c>
+      <x:c r="H1058" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1058" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1058" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1058" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1059">
+      <x:c r="A1059" t="str">
+        <x:v>donggeurio_line_0121</x:v>
+      </x:c>
+      <x:c r="B1059" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1059" t="n">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="D1059" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1059" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1059" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G1059" t="str">
+        <x:v>{{menu}}</x:v>
+      </x:c>
+      <x:c r="H1059" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1059" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1059" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1059" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1060">
+      <x:c r="A1060" t="str">
+        <x:v>donggeurio_line_0122</x:v>
+      </x:c>
+      <x:c r="B1060" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1060" t="n">
+        <x:v>1056</x:v>
+      </x:c>
+      <x:c r="D1060" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1060" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1060" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G1060" t="str">
+        <x:v>{{promo.primary}}</x:v>
+      </x:c>
+      <x:c r="H1060" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1060" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1060" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1060" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1061">
+      <x:c r="A1061" t="str">
+        <x:v>donggeurio_line_0123</x:v>
+      </x:c>
+      <x:c r="B1061" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1061" t="n">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="D1061" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1061" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1061" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G1061" t="str">
+        <x:v>{{store.name}}</x:v>
+      </x:c>
+      <x:c r="H1061" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1061" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1061" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1061" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1062">
+      <x:c r="A1062" t="str">
+        <x:v>donggeurio_line_0124</x:v>
+      </x:c>
+      <x:c r="B1062" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1062" t="n">
+        <x:v>1058</x:v>
+      </x:c>
+      <x:c r="D1062" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1062" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1062" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G1062" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1062" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1062" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1062" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1062" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1063">
+      <x:c r="A1063" t="str">
+        <x:v>donggeurio_line_0125</x:v>
+      </x:c>
+      <x:c r="B1063" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1063" t="n">
+        <x:v>1059</x:v>
+      </x:c>
+      <x:c r="D1063" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1063" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1063" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G1063" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1063" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1063" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1063" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1063" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1064">
+      <x:c r="A1064" t="str">
+        <x:v>donggeurio_line_0126</x:v>
+      </x:c>
+      <x:c r="B1064" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1064" t="n">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="D1064" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1064" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1064" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G1064" t="str">
+        <x:v>## 6. 개인화 규칙</x:v>
+      </x:c>
+      <x:c r="H1064" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1064" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1064" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1064" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1065">
+      <x:c r="A1065" t="str">
+        <x:v>donggeurio_line_0127</x:v>
+      </x:c>
+      <x:c r="B1065" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1065" t="n">
+        <x:v>1061</x:v>
+      </x:c>
+      <x:c r="D1065" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1065" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1065" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G1065" t="str">
+        <x:v>`personalization_rule`에는 실제 사용자 영상에서 변경 가능한 항목만 정의한다.</x:v>
+      </x:c>
+      <x:c r="H1065" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1065" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1065" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1065" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1066">
+      <x:c r="A1066" t="str">
+        <x:v>donggeurio_line_0128</x:v>
+      </x:c>
+      <x:c r="B1066" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1066" t="n">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="D1066" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1066" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1066" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G1066" t="str">
+        <x:v>### 변경 가능</x:v>
+      </x:c>
+      <x:c r="H1066" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1066" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1066" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1066" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1067">
+      <x:c r="A1067" t="str">
+        <x:v>donggeurio_line_0129</x:v>
+      </x:c>
+      <x:c r="B1067" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1067" t="n">
+        <x:v>1063</x:v>
+      </x:c>
+      <x:c r="D1067" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1067" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1067" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G1067" t="str">
+        <x:v>- 메뉴명</x:v>
+      </x:c>
+      <x:c r="H1067" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1067" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1067" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1067" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1068">
+      <x:c r="A1068" t="str">
+        <x:v>donggeurio_line_0130</x:v>
+      </x:c>
+      <x:c r="B1068" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1068" t="n">
+        <x:v>1064</x:v>
+      </x:c>
+      <x:c r="D1068" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1068" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1068" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G1068" t="str">
+        <x:v>- 가격</x:v>
+      </x:c>
+      <x:c r="H1068" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1068" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1068" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1068" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1069">
+      <x:c r="A1069" t="str">
+        <x:v>donggeurio_line_0131</x:v>
+      </x:c>
+      <x:c r="B1069" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1069" t="n">
+        <x:v>1065</x:v>
+      </x:c>
+      <x:c r="D1069" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1069" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1069" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G1069" t="str">
+        <x:v>- 프로모션 핵심 포인트</x:v>
+      </x:c>
+      <x:c r="H1069" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1069" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1069" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1069" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1070">
+      <x:c r="A1070" t="str">
+        <x:v>donggeurio_line_0132</x:v>
+      </x:c>
+      <x:c r="B1070" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1070" t="n">
+        <x:v>1066</x:v>
+      </x:c>
+      <x:c r="D1070" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1070" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1070" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G1070" t="str">
+        <x:v>- 자막 문구</x:v>
+      </x:c>
+      <x:c r="H1070" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1070" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1070" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1070" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1071">
+      <x:c r="A1071" t="str">
+        <x:v>donggeurio_line_0133</x:v>
+      </x:c>
+      <x:c r="B1071" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1071" t="n">
+        <x:v>1067</x:v>
+      </x:c>
+      <x:c r="D1071" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1071" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1071" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G1071" t="str">
+        <x:v>- 일부 반복 동작의 길이</x:v>
+      </x:c>
+      <x:c r="H1071" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1071" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1071" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1071" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1072">
+      <x:c r="A1072" t="str">
+        <x:v>donggeurio_line_0134</x:v>
+      </x:c>
+      <x:c r="B1072" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1072" t="n">
+        <x:v>1068</x:v>
+      </x:c>
+      <x:c r="D1072" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1072" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1072" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G1072" t="str">
+        <x:v>- 제한적인 재생 속도 조정</x:v>
+      </x:c>
+      <x:c r="H1072" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1072" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1072" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1072" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1073">
+      <x:c r="A1073" t="str">
+        <x:v>donggeurio_line_0135</x:v>
+      </x:c>
+      <x:c r="B1073" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1073" t="n">
+        <x:v>1069</x:v>
+      </x:c>
+      <x:c r="D1073" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1073" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1073" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G1073" t="str">
+        <x:v>- SFX 적용</x:v>
+      </x:c>
+      <x:c r="H1073" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1073" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1073" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1073" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1074">
+      <x:c r="A1074" t="str">
+        <x:v>donggeurio_line_0136</x:v>
+      </x:c>
+      <x:c r="B1074" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1074" t="n">
+        <x:v>1070</x:v>
+      </x:c>
+      <x:c r="D1074" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1074" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1074" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G1074" t="str">
+        <x:v>- 자막 위치·크기·표시 타이밍</x:v>
+      </x:c>
+      <x:c r="H1074" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1074" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1074" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1074" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1075">
+      <x:c r="A1075" t="str">
+        <x:v>donggeurio_line_0137</x:v>
+      </x:c>
+      <x:c r="B1075" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1075" t="n">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="D1075" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1075" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1075" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G1075" t="str">
+        <x:v>- 지원 범위 내 색보정</x:v>
+      </x:c>
+      <x:c r="H1075" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1075" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1075" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1075" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1076">
+      <x:c r="A1076" t="str">
+        <x:v>donggeurio_line_0138</x:v>
+      </x:c>
+      <x:c r="B1076" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1076" t="n">
+        <x:v>1072</x:v>
+      </x:c>
+      <x:c r="D1076" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1076" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1076" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G1076" t="str">
+        <x:v>### 변경 불가 또는 제한</x:v>
+      </x:c>
+      <x:c r="H1076" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1076" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1076" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1076" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1077">
+      <x:c r="A1077" t="str">
+        <x:v>donggeurio_line_0139</x:v>
+      </x:c>
+      <x:c r="B1077" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1077" t="n">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="D1077" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1077" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1077" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G1077" t="str">
+        <x:v>- 실제 촬영되지 않은 메뉴 추가</x:v>
+      </x:c>
+      <x:c r="H1077" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1077" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1077" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1077" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1078">
+      <x:c r="A1078" t="str">
+        <x:v>donggeurio_line_0140</x:v>
+      </x:c>
+      <x:c r="B1078" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1078" t="n">
+        <x:v>1074</x:v>
+      </x:c>
+      <x:c r="D1078" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1078" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1078" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G1078" t="str">
+        <x:v>- 장면 순서 임의 변경</x:v>
+      </x:c>
+      <x:c r="H1078" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1078" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1078" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1078" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1079">
+      <x:c r="A1079" t="str">
+        <x:v>donggeurio_line_0141</x:v>
+      </x:c>
+      <x:c r="B1079" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1079" t="n">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="D1079" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1079" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1079" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G1079" t="str">
+        <x:v>- 존재하지 않는 제조 과정 생성</x:v>
+      </x:c>
+      <x:c r="H1079" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1079" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1079" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1079" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1080">
+      <x:c r="A1080" t="str">
+        <x:v>donggeurio_line_0142</x:v>
+      </x:c>
+      <x:c r="B1080" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1080" t="n">
+        <x:v>1076</x:v>
+      </x:c>
+      <x:c r="D1080" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1080" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1080" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G1080" t="str">
+        <x:v>- 원본 영상에 없는 사진 또는 이미지를 영상에 삽입</x:v>
+      </x:c>
+      <x:c r="H1080" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1080" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1080" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1080" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1081">
+      <x:c r="A1081" t="str">
+        <x:v>donggeurio_line_0143</x:v>
+      </x:c>
+      <x:c r="B1081" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1081" t="n">
+        <x:v>1077</x:v>
+      </x:c>
+      <x:c r="D1081" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1081" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1081" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G1081" t="str">
+        <x:v>- 레퍼런스 영상의 자막 문구 그대로 복제</x:v>
+      </x:c>
+      <x:c r="H1081" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1081" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1081" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1081" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1082">
+      <x:c r="A1082" t="str">
+        <x:v>donggeurio_line_0144</x:v>
+      </x:c>
+      <x:c r="B1082" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1082" t="n">
+        <x:v>1078</x:v>
+      </x:c>
+      <x:c r="D1082" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1082" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1082" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G1082" t="str">
+        <x:v>- 원본 저작권 BGM 복제</x:v>
+      </x:c>
+      <x:c r="H1082" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1082" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1082" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1082" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1083">
+      <x:c r="A1083" t="str">
+        <x:v>donggeurio_line_0145</x:v>
+      </x:c>
+      <x:c r="B1083" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1083" t="n">
+        <x:v>1079</x:v>
+      </x:c>
+      <x:c r="D1083" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1083" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1083" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G1083" t="str">
+        <x:v>- 플랫폼 UI 또는 레퍼런스의 고유 그래픽 요소 복제</x:v>
+      </x:c>
+      <x:c r="H1083" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1083" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1083" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1083" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1084">
+      <x:c r="A1084" t="str">
+        <x:v>donggeurio_line_0146</x:v>
+      </x:c>
+      <x:c r="B1084" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1084" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="D1084" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1084" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1084" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G1084" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1084" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1084" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1084" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1084" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1085">
+      <x:c r="A1085" t="str">
+        <x:v>donggeurio_line_0147</x:v>
+      </x:c>
+      <x:c r="B1085" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1085" t="n">
+        <x:v>1081</x:v>
+      </x:c>
+      <x:c r="D1085" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1085" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1085" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G1085" t="str">
+        <x:v>## 7. 편집 구조 요약</x:v>
+      </x:c>
+      <x:c r="H1085" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1085" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1085" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1085" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1086">
+      <x:c r="A1086" t="str">
+        <x:v>donggeurio_line_0148</x:v>
+      </x:c>
+      <x:c r="B1086" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1086" t="n">
+        <x:v>1082</x:v>
+      </x:c>
+      <x:c r="D1086" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1086" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1086" t="n">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G1086" t="str">
+        <x:v>전체 영상의 편집 구조는 다음과 같이 정리할 수 있다.</x:v>
+      </x:c>
+      <x:c r="H1086" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1086" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1086" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1086" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1087">
+      <x:c r="A1087" t="str">
+        <x:v>donggeurio_line_0149</x:v>
+      </x:c>
+      <x:c r="B1087" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1087" t="n">
+        <x:v>1083</x:v>
+      </x:c>
+      <x:c r="D1087" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1087" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1087" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G1087" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1087" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1087" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1087" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1087" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1088">
+      <x:c r="A1088" t="str">
+        <x:v>donggeurio_line_0150</x:v>
+      </x:c>
+      <x:c r="B1088" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1088" t="n">
+        <x:v>1084</x:v>
+      </x:c>
+      <x:c r="D1088" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1088" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1088" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G1088" t="str">
+        <x:v>HOOK</x:v>
+      </x:c>
+      <x:c r="H1088" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1088" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1088" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1088" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1089">
+      <x:c r="A1089" t="str">
+        <x:v>donggeurio_line_0151</x:v>
+      </x:c>
+      <x:c r="B1089" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1089" t="n">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="D1089" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1089" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1089" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="G1089" t="str">
+        <x:v>완성 결과물 선공개</x:v>
+      </x:c>
+      <x:c r="H1089" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1089" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1089" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1089" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1090">
+      <x:c r="A1090" t="str">
+        <x:v>donggeurio_line_0152</x:v>
+      </x:c>
+      <x:c r="B1090" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1090" t="n">
+        <x:v>1086</x:v>
+      </x:c>
+      <x:c r="D1090" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1090" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1090" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G1090" t="str">
+        <x:v>↓</x:v>
+      </x:c>
+      <x:c r="H1090" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1090" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1090" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1090" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1091">
+      <x:c r="A1091" t="str">
+        <x:v>donggeurio_line_0153</x:v>
+      </x:c>
+      <x:c r="B1091" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1091" t="n">
+        <x:v>1087</x:v>
+      </x:c>
+      <x:c r="D1091" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1091" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1091" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G1091" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="H1091" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1091" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1091" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1091" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1092">
+      <x:c r="A1092" t="str">
+        <x:v>donggeurio_line_0154</x:v>
+      </x:c>
+      <x:c r="B1092" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1092" t="n">
+        <x:v>1088</x:v>
+      </x:c>
+      <x:c r="D1092" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1092" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1092" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G1092" t="str">
+        <x:v>반죽 투입 및 펼치기</x:v>
+      </x:c>
+      <x:c r="H1092" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1092" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1092" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1092" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1093">
+      <x:c r="A1093" t="str">
+        <x:v>donggeurio_line_0155</x:v>
+      </x:c>
+      <x:c r="B1093" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1093" t="n">
+        <x:v>1089</x:v>
+      </x:c>
+      <x:c r="D1093" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1093" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1093" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G1093" t="str">
+        <x:v>↓</x:v>
+      </x:c>
+      <x:c r="H1093" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1093" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1093" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1093" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1094">
+      <x:c r="A1094" t="str">
+        <x:v>donggeurio_line_0156</x:v>
+      </x:c>
+      <x:c r="B1094" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1094" t="n">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="D1094" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1094" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1094" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G1094" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="H1094" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1094" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1094" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1094" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1095">
+      <x:c r="A1095" t="str">
+        <x:v>donggeurio_line_0157</x:v>
+      </x:c>
+      <x:c r="B1095" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1095" t="n">
+        <x:v>1091</x:v>
+      </x:c>
+      <x:c r="D1095" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1095" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1095" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G1095" t="str">
+        <x:v>굽기 및 접기</x:v>
+      </x:c>
+      <x:c r="H1095" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1095" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1095" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1095" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1096">
+      <x:c r="A1096" t="str">
+        <x:v>donggeurio_line_0158</x:v>
+      </x:c>
+      <x:c r="B1096" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1096" t="n">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="D1096" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1096" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1096" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G1096" t="str">
+        <x:v>↓</x:v>
+      </x:c>
+      <x:c r="H1096" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1096" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1096" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1096" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1097">
+      <x:c r="A1097" t="str">
+        <x:v>donggeurio_line_0159</x:v>
+      </x:c>
+      <x:c r="B1097" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1097" t="n">
+        <x:v>1093</x:v>
+      </x:c>
+      <x:c r="D1097" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1097" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1097" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G1097" t="str">
+        <x:v>CORE_ACTION</x:v>
+      </x:c>
+      <x:c r="H1097" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1097" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1097" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1097" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1098">
+      <x:c r="A1098" t="str">
+        <x:v>donggeurio_line_0160</x:v>
+      </x:c>
+      <x:c r="B1098" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1098" t="n">
+        <x:v>1094</x:v>
+      </x:c>
+      <x:c r="D1098" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1098" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1098" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G1098" t="str">
+        <x:v>크림 및 속재료 토핑</x:v>
+      </x:c>
+      <x:c r="H1098" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1098" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1098" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1098" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1099">
+      <x:c r="A1099" t="str">
+        <x:v>donggeurio_line_0161</x:v>
+      </x:c>
+      <x:c r="B1099" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1099" t="n">
+        <x:v>1095</x:v>
+      </x:c>
+      <x:c r="D1099" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1099" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1099" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G1099" t="str">
+        <x:v>↓</x:v>
+      </x:c>
+      <x:c r="H1099" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1099" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1099" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1099" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1100">
+      <x:c r="A1100" t="str">
+        <x:v>donggeurio_line_0162</x:v>
+      </x:c>
+      <x:c r="B1100" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1100" t="n">
+        <x:v>1096</x:v>
+      </x:c>
+      <x:c r="D1100" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1100" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1100" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G1100" t="str">
+        <x:v>CLIMAX_PREP</x:v>
+      </x:c>
+      <x:c r="H1100" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1100" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1100" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1100" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1101">
+      <x:c r="A1101" t="str">
+        <x:v>donggeurio_line_0163</x:v>
+      </x:c>
+      <x:c r="B1101" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1101" t="n">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="D1101" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1101" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1101" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G1101" t="str">
+        <x:v>포장 및 표면 마무리</x:v>
+      </x:c>
+      <x:c r="H1101" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1101" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1101" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1101" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1102">
+      <x:c r="A1102" t="str">
+        <x:v>donggeurio_line_0164</x:v>
+      </x:c>
+      <x:c r="B1102" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1102" t="n">
+        <x:v>1098</x:v>
+      </x:c>
+      <x:c r="D1102" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1102" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1102" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G1102" t="str">
+        <x:v>↓</x:v>
+      </x:c>
+      <x:c r="H1102" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1102" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1102" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1102" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1103">
+      <x:c r="A1103" t="str">
+        <x:v>donggeurio_line_0165</x:v>
+      </x:c>
+      <x:c r="B1103" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1103" t="n">
+        <x:v>1099</x:v>
+      </x:c>
+      <x:c r="D1103" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1103" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1103" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G1103" t="str">
+        <x:v>CLIMAX_OUTRO</x:v>
+      </x:c>
+      <x:c r="H1103" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1103" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1103" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1103" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1104">
+      <x:c r="A1104" t="str">
+        <x:v>donggeurio_line_0166</x:v>
+      </x:c>
+      <x:c r="B1104" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1104" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="D1104" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1104" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1104" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G1104" t="str">
+        <x:v>토치 브륄레 및 최종 질감 공개</x:v>
+      </x:c>
+      <x:c r="H1104" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1104" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1104" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1104" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1105">
+      <x:c r="A1105" t="str">
+        <x:v>donggeurio_line_0167</x:v>
+      </x:c>
+      <x:c r="B1105" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1105" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="D1105" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1105" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1105" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G1105" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1105" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1105" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1105" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1105" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1106">
+      <x:c r="A1106" t="str">
+        <x:v>donggeurio_line_0168</x:v>
+      </x:c>
+      <x:c r="B1106" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1106" t="n">
+        <x:v>1102</x:v>
+      </x:c>
+      <x:c r="D1106" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1106" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1106" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G1106" t="str">
+        <x:v>핵심 편집 문법은 다음과 같다.</x:v>
+      </x:c>
+      <x:c r="H1106" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1106" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1106" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1106" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1107">
+      <x:c r="A1107" t="str">
+        <x:v>donggeurio_line_0169</x:v>
+      </x:c>
+      <x:c r="B1107" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1107" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="D1107" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1107" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1107" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G1107" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1107" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1107" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1107" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1107" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1108">
+      <x:c r="A1108" t="str">
+        <x:v>donggeurio_line_0170</x:v>
+      </x:c>
+      <x:c r="B1108" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1108" t="n">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="D1108" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1108" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1108" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G1108" t="str">
+        <x:v>결과물 선공개</x:v>
+      </x:c>
+      <x:c r="H1108" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1108" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1108" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1108" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1109">
+      <x:c r="A1109" t="str">
+        <x:v>donggeurio_line_0171</x:v>
+      </x:c>
+      <x:c r="B1109" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1109" t="n">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="D1109" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1109" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1109" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G1109" t="str">
+        <x:v>→ 제조 과정 순차 전개</x:v>
+      </x:c>
+      <x:c r="H1109" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1109" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1109" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1109" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1110">
+      <x:c r="A1110" t="str">
+        <x:v>donggeurio_line_0172</x:v>
+      </x:c>
+      <x:c r="B1110" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1110" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="D1110" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1110" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1110" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G1110" t="str">
+        <x:v>→ 질감이 강한 행동을 길게 보존</x:v>
+      </x:c>
+      <x:c r="H1110" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1110" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1110" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1110" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1111">
+      <x:c r="A1111" t="str">
+        <x:v>donggeurio_line_0173</x:v>
+      </x:c>
+      <x:c r="B1111" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1111" t="n">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="D1111" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1111" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1111" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G1111" t="str">
+        <x:v>→ 조리 단계 사이에서 Hard Cut</x:v>
+      </x:c>
+      <x:c r="H1111" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1111" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1111" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1111" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1112">
+      <x:c r="A1112" t="str">
+        <x:v>donggeurio_line_0174</x:v>
+      </x:c>
+      <x:c r="B1112" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1112" t="n">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="D1112" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1112" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1112" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G1112" t="str">
+        <x:v>→ 최종 브륄레 변화 과정을 하이라이트로 배치</x:v>
+      </x:c>
+      <x:c r="H1112" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1112" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1112" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1112" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1113">
+      <x:c r="A1113" t="str">
+        <x:v>donggeurio_line_0175</x:v>
+      </x:c>
+      <x:c r="B1113" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1113" t="n">
+        <x:v>1109</x:v>
+      </x:c>
+      <x:c r="D1113" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1113" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1113" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G1113" t="str">
+        <x:v>→ 완성 질감으로 종료</x:v>
+      </x:c>
+      <x:c r="H1113" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1113" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1113" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1113" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1114">
+      <x:c r="A1114" t="str">
+        <x:v>donggeurio_line_0176</x:v>
+      </x:c>
+      <x:c r="B1114" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1114" t="n">
+        <x:v>1110</x:v>
+      </x:c>
+      <x:c r="D1114" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1114" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1114" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G1114" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1114" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1114" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1114" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1114" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1115">
+      <x:c r="A1115" t="str">
+        <x:v>donggeurio_line_0177</x:v>
+      </x:c>
+      <x:c r="B1115" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1115" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="D1115" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1115" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1115" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G1115" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1115" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1115" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1115" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1115" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1116">
+      <x:c r="A1116" t="str">
+        <x:v>donggeurio_line_0178</x:v>
+      </x:c>
+      <x:c r="B1116" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1116" t="n">
+        <x:v>1112</x:v>
+      </x:c>
+      <x:c r="D1116" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1116" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1116" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G1116" t="str">
+        <x:v>## 8. DB 스키마 적용 시 핵심 고려사항</x:v>
+      </x:c>
+      <x:c r="H1116" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1116" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1116" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1116" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1117">
+      <x:c r="A1117" t="str">
+        <x:v>donggeurio_line_0179</x:v>
+      </x:c>
+      <x:c r="B1117" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1117" t="n">
+        <x:v>1113</x:v>
+      </x:c>
+      <x:c r="D1117" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1117" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1117" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G1117" t="str">
+        <x:v>1. **기존 스키마 유지**</x:v>
+      </x:c>
+      <x:c r="H1117" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1117" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1117" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1117" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1118">
+      <x:c r="A1118" t="str">
+        <x:v>donggeurio_line_0180</x:v>
+      </x:c>
+      <x:c r="B1118" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1118" t="n">
+        <x:v>1114</x:v>
+      </x:c>
+      <x:c r="D1118" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1118" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1118" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G1118" t="str">
+        <x:v>- `03_GUIDE_TEMPLATES`의 기존 컬럼 구조를 변경하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H1118" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1118" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1118" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1118" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1119">
+      <x:c r="A1119" t="str">
+        <x:v>donggeurio_line_0181</x:v>
+      </x:c>
+      <x:c r="B1119" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1119" t="n">
+        <x:v>1115</x:v>
+      </x:c>
+      <x:c r="D1119" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1119" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1119" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G1119" t="str">
+        <x:v>- 프레임 분석용 신규 시트 또는 신규 컬럼을 추가하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H1119" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1119" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1119" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1119" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1120">
+      <x:c r="A1120" t="str">
+        <x:v>donggeurio_line_0182</x:v>
+      </x:c>
+      <x:c r="B1120" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1120" t="n">
+        <x:v>1116</x:v>
+      </x:c>
+      <x:c r="D1120" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1120" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1120" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G1120" t="str">
+        <x:v>2. **정밀 분석의 `action_pattern` 흡수**</x:v>
+      </x:c>
+      <x:c r="H1120" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1120" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1120" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1120" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1121">
+      <x:c r="A1121" t="str">
+        <x:v>donggeurio_line_0183</x:v>
+      </x:c>
+      <x:c r="B1121" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1121" t="n">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="D1121" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1121" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1121" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G1121" t="str">
+        <x:v>- 피사체 행동</x:v>
+      </x:c>
+      <x:c r="H1121" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1121" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1121" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1121" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1122">
+      <x:c r="A1122" t="str">
+        <x:v>donggeurio_line_0184</x:v>
+      </x:c>
+      <x:c r="B1122" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1122" t="n">
+        <x:v>1118</x:v>
+      </x:c>
+      <x:c r="D1122" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1122" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1122" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G1122" t="str">
+        <x:v>- 카메라</x:v>
+      </x:c>
+      <x:c r="H1122" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1122" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1122" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1122" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1123">
+      <x:c r="A1123" t="str">
+        <x:v>donggeurio_line_0185</x:v>
+      </x:c>
+      <x:c r="B1123" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1123" t="n">
+        <x:v>1119</x:v>
+      </x:c>
+      <x:c r="D1123" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1123" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1123" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G1123" t="str">
+        <x:v>- 도구</x:v>
+      </x:c>
+      <x:c r="H1123" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1123" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1123" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1123" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1124">
+      <x:c r="A1124" t="str">
+        <x:v>donggeurio_line_0186</x:v>
+      </x:c>
+      <x:c r="B1124" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1124" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="D1124" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1124" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1124" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G1124" t="str">
+        <x:v>- 상품 상태 변화</x:v>
+      </x:c>
+      <x:c r="H1124" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1124" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1124" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1124" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1125">
+      <x:c r="A1125" t="str">
+        <x:v>donggeurio_line_0187</x:v>
+      </x:c>
+      <x:c r="B1125" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1125" t="n">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="D1125" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1125" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1125" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G1125" t="str">
+        <x:v>- 시각 Peak</x:v>
+      </x:c>
+      <x:c r="H1125" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1125" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1125" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1125" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1126">
+      <x:c r="A1126" t="str">
+        <x:v>donggeurio_line_0188</x:v>
+      </x:c>
+      <x:c r="B1126" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1126" t="n">
+        <x:v>1122</x:v>
+      </x:c>
+      <x:c r="D1126" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1126" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1126" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G1126" t="str">
+        <x:v>- 세부 ms 타이밍</x:v>
+      </x:c>
+      <x:c r="H1126" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1126" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1126" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1126" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1127">
+      <x:c r="A1127" t="str">
+        <x:v>donggeurio_line_0189</x:v>
+      </x:c>
+      <x:c r="B1127" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1127" t="n">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="D1127" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1127" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1127" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G1127" t="str">
+        <x:v>을 `action_pattern` 내부에 함께 기록한다.</x:v>
+      </x:c>
+      <x:c r="H1127" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1127" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1127" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1127" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1128">
+      <x:c r="A1128" t="str">
+        <x:v>donggeurio_line_0190</x:v>
+      </x:c>
+      <x:c r="B1128" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1128" t="n">
+        <x:v>1124</x:v>
+      </x:c>
+      <x:c r="D1128" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1128" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1128" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G1128" t="str">
+        <x:v>3. **편집 판단은 `timing_rule`에 기록**</x:v>
+      </x:c>
+      <x:c r="H1128" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1128" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1128" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1128" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1129">
+      <x:c r="A1129" t="str">
+        <x:v>donggeurio_line_0191</x:v>
+      </x:c>
+      <x:c r="B1129" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1129" t="n">
+        <x:v>1125</x:v>
+      </x:c>
+      <x:c r="D1129" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1129" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1129" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G1129" t="str">
+        <x:v>- 단순 시간 정보가 아니라 실제 편집 Agent가 실행 가능한 규칙 형태로 정의한다.</x:v>
+      </x:c>
+      <x:c r="H1129" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1129" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1129" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1129" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1130">
+      <x:c r="A1130" t="str">
+        <x:v>donggeurio_line_0192</x:v>
+      </x:c>
+      <x:c r="B1130" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1130" t="n">
+        <x:v>1126</x:v>
+      </x:c>
+      <x:c r="D1130" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1130" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1130" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G1130" t="str">
+        <x:v>4. **장면 순서 유지**</x:v>
+      </x:c>
+      <x:c r="H1130" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1130" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1130" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1130" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1131">
+      <x:c r="A1131" t="str">
+        <x:v>donggeurio_line_0193</x:v>
+      </x:c>
+      <x:c r="B1131" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1131" t="n">
+        <x:v>1127</x:v>
+      </x:c>
+      <x:c r="D1131" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1131" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1131" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G1131" t="str">
+        <x:v>- 원본 가이드가 가진 제조 및 내러티브 흐름을 유지한다.</x:v>
+      </x:c>
+      <x:c r="H1131" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1131" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1131" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1131" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1132">
+      <x:c r="A1132" t="str">
+        <x:v>donggeurio_line_0194</x:v>
+      </x:c>
+      <x:c r="B1132" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1132" t="n">
+        <x:v>1128</x:v>
+      </x:c>
+      <x:c r="D1132" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1132" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1132" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G1132" t="str">
+        <x:v>- 개인화를 이유로 장면을 임의 재배열하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H1132" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1132" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1132" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1132" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1133">
+      <x:c r="A1133" t="str">
+        <x:v>donggeurio_line_0195</x:v>
+      </x:c>
+      <x:c r="B1133" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1133" t="n">
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="D1133" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1133" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1133" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G1133" t="str">
+        <x:v>5. **레퍼런스 자막 고정 재사용 금지**</x:v>
+      </x:c>
+      <x:c r="H1133" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1133" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1133" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1133" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1134">
+      <x:c r="A1134" t="str">
+        <x:v>donggeurio_line_0196</x:v>
+      </x:c>
+      <x:c r="B1134" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1134" t="n">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="D1134" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1134" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1134" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G1134" t="str">
+        <x:v>- 실제 자막 문구는 분석 근거로만 보존한다.</x:v>
+      </x:c>
+      <x:c r="H1134" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1134" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1134" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1134" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1135">
+      <x:c r="A1135" t="str">
+        <x:v>donggeurio_line_0197</x:v>
+      </x:c>
+      <x:c r="B1135" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1135" t="n">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="D1135" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1135" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1135" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G1135" t="str">
+        <x:v>- 새 사용자 영상의 자막은 LLM이 실제 영상 내용과 홍보 목적에 맞춰 새로 생성한다.</x:v>
+      </x:c>
+      <x:c r="H1135" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1135" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1135" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1135" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1136">
+      <x:c r="A1136" t="str">
+        <x:v>donggeurio_line_0198</x:v>
+      </x:c>
+      <x:c r="B1136" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1136" t="n">
+        <x:v>1132</x:v>
+      </x:c>
+      <x:c r="D1136" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1136" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1136" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G1136" t="str">
+        <x:v>6. **지원 편집 기능 내에서만 개인화**</x:v>
+      </x:c>
+      <x:c r="H1136" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1136" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1136" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1136" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1137">
+      <x:c r="A1137" t="str">
+        <x:v>donggeurio_line_0199</x:v>
+      </x:c>
+      <x:c r="B1137" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1137" t="n">
+        <x:v>1133</x:v>
+      </x:c>
+      <x:c r="D1137" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1137" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1137" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G1137" t="str">
+        <x:v>- `caption`</x:v>
+      </x:c>
+      <x:c r="H1137" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1137" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1137" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1137" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1138">
+      <x:c r="A1138" t="str">
+        <x:v>donggeurio_line_0200</x:v>
+      </x:c>
+      <x:c r="B1138" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1138" t="n">
+        <x:v>1134</x:v>
+      </x:c>
+      <x:c r="D1138" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1138" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1138" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G1138" t="str">
+        <x:v>- `text_2d`</x:v>
+      </x:c>
+      <x:c r="H1138" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1138" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1138" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1138" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1139">
+      <x:c r="A1139" t="str">
+        <x:v>donggeurio_line_0201</x:v>
+      </x:c>
+      <x:c r="B1139" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1139" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="D1139" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1139" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1139" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G1139" t="str">
+        <x:v>- `sfx`</x:v>
+      </x:c>
+      <x:c r="H1139" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1139" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1139" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1139" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1140">
+      <x:c r="A1140" t="str">
+        <x:v>donggeurio_line_0202</x:v>
+      </x:c>
+      <x:c r="B1140" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1140" t="n">
+        <x:v>1136</x:v>
+      </x:c>
+      <x:c r="D1140" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1140" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1140" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G1140" t="str">
+        <x:v>- `color_grading`</x:v>
+      </x:c>
+      <x:c r="H1140" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1140" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1140" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1140" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1141">
+      <x:c r="A1141" t="str">
+        <x:v>donggeurio_line_0203</x:v>
+      </x:c>
+      <x:c r="B1141" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1141" t="n">
+        <x:v>1137</x:v>
+      </x:c>
+      <x:c r="D1141" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1141" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1141" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G1141" t="str">
+        <x:v>- 영상 컷 및 trim</x:v>
+      </x:c>
+      <x:c r="H1141" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1141" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1141" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1141" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1142">
+      <x:c r="A1142" t="str">
+        <x:v>donggeurio_line_0204</x:v>
+      </x:c>
+      <x:c r="B1142" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1142" t="n">
+        <x:v>1138</x:v>
+      </x:c>
+      <x:c r="D1142" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1142" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1142" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G1142" t="str">
+        <x:v>- 지원 범위 내 속도 조정</x:v>
+      </x:c>
+      <x:c r="H1142" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1142" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1142" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1142" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1143">
+      <x:c r="A1143" t="str">
+        <x:v>donggeurio_line_0205</x:v>
+      </x:c>
+      <x:c r="B1143" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1143" t="n">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c r="D1143" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1143" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1143" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G1143" t="str">
+        <x:v>7. **원본 BGM 및 고유 표현 복제 금지**</x:v>
+      </x:c>
+      <x:c r="H1143" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1143" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1143" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1143" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1144">
+      <x:c r="A1144" t="str">
+        <x:v>donggeurio_line_0206</x:v>
+      </x:c>
+      <x:c r="B1144" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1144" t="n">
+        <x:v>1140</x:v>
+      </x:c>
+      <x:c r="D1144" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1144" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1144" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G1144" t="str">
+        <x:v>- 레퍼런스의 저작권 음원, 플랫폼 UI, 고유 그래픽을 템플릿화하지 않는다.</x:v>
+      </x:c>
+      <x:c r="H1144" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1144" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1144" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1144" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1145">
+      <x:c r="A1145" t="str">
+        <x:v>donggeurio_line_0207</x:v>
+      </x:c>
+      <x:c r="B1145" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1145" t="n">
+        <x:v>1141</x:v>
+      </x:c>
+      <x:c r="D1145" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1145" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1145" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G1145" t="str">
+        <x:v>---</x:v>
+      </x:c>
+      <x:c r="H1145" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1145" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1145" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1145" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1146">
+      <x:c r="A1146" t="str">
+        <x:v>donggeurio_line_0208</x:v>
+      </x:c>
+      <x:c r="B1146" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1146" t="n">
+        <x:v>1142</x:v>
+      </x:c>
+      <x:c r="D1146" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1146" t="str">
+        <x:v>HEADING</x:v>
+      </x:c>
+      <x:c r="F1146" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G1146" t="str">
+        <x:v>## 9. 최종 템플릿 해석</x:v>
+      </x:c>
+      <x:c r="H1146" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1146" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1146" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1146" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1147">
+      <x:c r="A1147" t="str">
+        <x:v>donggeurio_line_0209</x:v>
+      </x:c>
+      <x:c r="B1147" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1147" t="n">
+        <x:v>1143</x:v>
+      </x:c>
+      <x:c r="D1147" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1147" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1147" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G1147" t="str">
+        <x:v>이 가마쿠라 말차 크레페 영상의 핵심은 단순한 음식 리뷰가 아니라,</x:v>
+      </x:c>
+      <x:c r="H1147" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1147" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1147" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1147" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1148">
+      <x:c r="A1148" t="str">
+        <x:v>donggeurio_line_0210</x:v>
+      </x:c>
+      <x:c r="B1148" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1148" t="n">
+        <x:v>1144</x:v>
+      </x:c>
+      <x:c r="D1148" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1148" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1148" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G1148" t="str">
+        <x:v>&gt; **완성 결과물을 먼저 보여준 뒤 실제 제조 공정의 시각적 만족감을 순차적으로 축적하고, 토치 브륄레라는 가장 강한 질감 변화로 영상을 마무리하는 `PROCESS → TEXTURE → CLIMAX`형 숏폼 편집 템플릿**</x:v>
+      </x:c>
+      <x:c r="H1148" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1148" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1148" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1148" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1149">
+      <x:c r="A1149" t="str">
+        <x:v>donggeurio_line_0211</x:v>
+      </x:c>
+      <x:c r="B1149" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1149" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="D1149" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1149" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1149" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G1149" t="str">
+        <x:v>&gt;</x:v>
+      </x:c>
+      <x:c r="H1149" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1149" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1149" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1149" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1150">
+      <x:c r="A1150" t="str">
+        <x:v>donggeurio_line_0212</x:v>
+      </x:c>
+      <x:c r="B1150" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1150" t="n">
+        <x:v>1146</x:v>
+      </x:c>
+      <x:c r="D1150" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1150" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1150" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G1150" t="str">
+        <x:v>으로 정의할 수 있다.</x:v>
+      </x:c>
+      <x:c r="H1150" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1150" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1150" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1150" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1151">
+      <x:c r="A1151" t="str">
+        <x:v>donggeurio_line_0213</x:v>
+      </x:c>
+      <x:c r="B1151" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1151" t="n">
+        <x:v>1147</x:v>
+      </x:c>
+      <x:c r="D1151" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1151" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1151" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G1151" t="str">
+        <x:v>따라서 `gt_matcha_crepe_review_v1`을 다른 매장에 적용할 경우에도 **말차 크레페라는 특정 메뉴 자체를 복제하는 것이 아니라**, 다음 편집 구조를 재사용하는 것이 핵심이다.</x:v>
+      </x:c>
+      <x:c r="H1151" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1151" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1151" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1151" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1152">
+      <x:c r="A1152" t="str">
+        <x:v>donggeurio_line_0214</x:v>
+      </x:c>
+      <x:c r="B1152" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1152" t="n">
+        <x:v>1148</x:v>
+      </x:c>
+      <x:c r="D1152" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1152" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1152" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G1152" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1152" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1152" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1152" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1152" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1153">
+      <x:c r="A1153" t="str">
+        <x:v>donggeurio_line_0215</x:v>
+      </x:c>
+      <x:c r="B1153" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1153" t="n">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="D1153" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1153" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1153" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G1153" t="str">
+        <x:v>1. 완성 메뉴 선공개</x:v>
+      </x:c>
+      <x:c r="H1153" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1153" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1153" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1153" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1154">
+      <x:c r="A1154" t="str">
+        <x:v>donggeurio_line_0216</x:v>
+      </x:c>
+      <x:c r="B1154" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1154" t="n">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="D1154" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1154" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1154" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G1154" t="str">
+        <x:v>2. 첫 번째 제조 행동</x:v>
+      </x:c>
+      <x:c r="H1154" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1154" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1154" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1154" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1155">
+      <x:c r="A1155" t="str">
+        <x:v>donggeurio_line_0217</x:v>
+      </x:c>
+      <x:c r="B1155" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1155" t="n">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="D1155" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1155" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1155" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G1155" t="str">
+        <x:v>3. 형태 또는 상태 변화</x:v>
+      </x:c>
+      <x:c r="H1155" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1155" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1155" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1155" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1156">
+      <x:c r="A1156" t="str">
+        <x:v>donggeurio_line_0218</x:v>
+      </x:c>
+      <x:c r="B1156" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1156" t="n">
+        <x:v>1152</x:v>
+      </x:c>
+      <x:c r="D1156" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1156" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1156" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G1156" t="str">
+        <x:v>4. 핵심 재료 추가</x:v>
+      </x:c>
+      <x:c r="H1156" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1156" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1156" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1156" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1157">
+      <x:c r="A1157" t="str">
+        <x:v>donggeurio_line_0219</x:v>
+      </x:c>
+      <x:c r="B1157" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1157" t="n">
+        <x:v>1153</x:v>
+      </x:c>
+      <x:c r="D1157" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1157" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1157" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G1157" t="str">
+        <x:v>5. 최종 형태 완성</x:v>
+      </x:c>
+      <x:c r="H1157" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1157" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1157" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1157" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1158">
+      <x:c r="A1158" t="str">
+        <x:v>donggeurio_line_0220</x:v>
+      </x:c>
+      <x:c r="B1158" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1158" t="n">
+        <x:v>1154</x:v>
+      </x:c>
+      <x:c r="D1158" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1158" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1158" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G1158" t="str">
+        <x:v>6. 가장 강한 시각·질감 변화</x:v>
+      </x:c>
+      <x:c r="H1158" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1158" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1158" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1158" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1159">
+      <x:c r="A1159" t="str">
+        <x:v>donggeurio_line_0221</x:v>
+      </x:c>
+      <x:c r="B1159" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1159" t="n">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="D1159" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1159" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1159" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G1159" t="str">
+        <x:v>7. 완성 결과물로 종료</x:v>
+      </x:c>
+      <x:c r="H1159" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1159" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1159" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1159" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1160">
+      <x:c r="A1160" t="str">
+        <x:v>donggeurio_line_0222</x:v>
+      </x:c>
+      <x:c r="B1160" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1160" t="n">
+        <x:v>1156</x:v>
+      </x:c>
+      <x:c r="D1160" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1160" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1160" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G1160" t="str">
+        <x:v>```</x:v>
+      </x:c>
+      <x:c r="H1160" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1160" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1160" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1160" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1161">
+      <x:c r="A1161" t="str">
+        <x:v>donggeurio_line_0223</x:v>
+      </x:c>
+      <x:c r="B1161" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1161" t="n">
+        <x:v>1157</x:v>
+      </x:c>
+      <x:c r="D1161" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1161" t="str">
+        <x:v>ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F1161" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G1161" t="str">
+        <x:v>이 구조를 유지하면서 실제 사용자가 촬영한 메뉴와 제조 행동에 맞게 `action_pattern`, 자막, 세부 컷 길이 및 편집 요소를 개인화한다.</x:v>
+      </x:c>
+      <x:c r="H1161" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1161" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1161" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1161" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1162">
+      <x:c r="A1162" t="str">
+        <x:v>donggeurio_challenge_difficulty</x:v>
+      </x:c>
+      <x:c r="B1162" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1162" t="n">
+        <x:v>1158</x:v>
+      </x:c>
+      <x:c r="D1162" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E1162" t="str">
+        <x:v>CLASSIFICATION</x:v>
+      </x:c>
+      <x:c r="F1162" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G1162" t="str">
+        <x:v>촬영 난이도 ★★: 6개 공정 컷을 순서대로 촬영</x:v>
+      </x:c>
+      <x:c r="H1162" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1162" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1162" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K1162" t="str">
+        <x:v>GENERATED_SUMMARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1163">
+      <x:c r="A1163" t="str">
+        <x:v>donggeurio_store_difficulty</x:v>
+      </x:c>
+      <x:c r="B1163" t="str">
+        <x:v>gemini_donggeurio_report_20260828</x:v>
+      </x:c>
+      <x:c r="C1163" t="n">
+        <x:v>1159</x:v>
+      </x:c>
+      <x:c r="D1163" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="E1163" t="str">
+        <x:v>CLASSIFICATION</x:v>
+      </x:c>
+      <x:c r="F1163" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G1163" t="str">
+        <x:v>촬영 난이도 ★★: 5개 촬영 요소에서 6개 편집 구간을 재구성</x:v>
+      </x:c>
+      <x:c r="H1163" t="str">
+        <x:v>동그리오_Gemini_분석보고서.md</x:v>
+      </x:c>
+      <x:c r="I1163" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="J1163" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="K1163" t="str">
+        <x:v>GENERATED_SUMMARY</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:K1"/>
@@ -35803,6 +43678,166 @@
         <x:v>ACTIVE</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>ELEMENT_01</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>완성 메뉴</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>완성 메뉴의 전체 모습과 표면 질감을 가까이 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>ELEMENT_02</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>반죽 조리</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>반죽을 붓고 고르게 펴는 손과 도구를 길게 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>ELEMENT_03</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>굽기와 접기</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>익은 메뉴를 들어 올려 접고 옮기는 과정을 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>ELEMENT_04</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>토핑과 포장</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>재료를 올리고 포장해 형태를 잡는 전 과정을 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G12" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>4,5</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>ELEMENT_05</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>토치와 질감</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>토치로 표면이 변하고 완성 질감이 보이게 촬영하세요.</x:v>
+      </x:c>
+      <x:c r="G13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -35810,7 +43845,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radb0586adf194d94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebb7d37d377e4cf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35835,7 +43870,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="26" t="str">
-        <x:v>실제 등록 가이드 3종의 exact 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 총 213개의 5프레임 분석 근거는 별도 시트 없이 03_GUIDE_TEMPLATES action_pattern·timing_rule에 흡수되어 있습니다.</x:v>
+        <x:v>실제 등록 가이드 5종의 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 동그리오 2종은 동일한 6구간 분석을 서비스 유형별 촬영 계약으로 분리합니다.</x:v>
       </x:c>
       <x:c r="B2" s="26"/>
       <x:c r="C2" s="26"/>
@@ -35866,7 +43901,7 @@
         <x:v>챌린지 입력</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
         <x:v>중복 제거 후 누적된 챌린지 수</x:v>
@@ -35880,7 +43915,7 @@
         <x:v>전체 가이드 템플릿 구간</x:v>
       </x:c>
       <x:c r="B6" s="5" t="n">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
         <x:v>버전 이력을 포함한 03_GUIDE_TEMPLATES 전체 데이터 행</x:v>
@@ -36215,6 +44250,70 @@
         <x:v>정보형</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>gemini_report_20260828</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>동그리오(챌린지)</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>동그리오 챌린지</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>https://www.youtube.com/shorts/6duJ3WOzeuQ</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>6duJ3WOzeuQ</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>밈</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>gemini_report_20260828</x:v>
+      </x:c>
+      <x:c r="B9" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>동그리오(매장 홍보)</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>동그리오 매장 홍보</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>https://www.youtube.com/shorts/6duJ3WOzeuQ</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>6duJ3WOzeuQ</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>정보형</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
@@ -36226,9 +44325,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="R36632b385e214036"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R8af8ae4620e5467f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Ra0551073b25e4293"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="Rd233a7df584e49b9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R2d7585e520234367"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Raae56f80e2d84a18"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -42306,6 +50405,882 @@
       </x:c>
       <x:c r="W87" s="69" t="str">
         <x:v>70A521B50E58B1355992AC47AEB7C36E7C98174A9826BEE007A464FD20ECA140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>gts_donggeurio_challenge_v1_01</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F88" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G88" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="H88" t="str">
+        <x:v>완성 메뉴 선공개</x:v>
+      </x:c>
+      <x:c r="I88" t="str">
+        <x:v>HOOK</x:v>
+      </x:c>
+      <x:c r="J88" t="str">
+        <x:v>[0~500ms] 완성 메뉴가 시작 프레임부터 식별되도록 중앙에 노출한다. [1500~2000ms] 손목의 미세 좌우 틸팅으로 표면 광택과 질감을 강조한다. 카메라는 고정하고 피사체 움직임을 사용한다.</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
+        <x:v>0ms부터 가장 시각적 임팩트가 높은 결과물을 노출한다. 형태·색상·질감이 인지된 뒤 2500ms 부근에서 제조 공정으로 Hard Cut한다.</x:v>
+      </x:c>
+      <x:c r="L88" t="str">
+        <x:v>{{price}}이지만 또 먹고 싶은 {{menu}}입니다</x:v>
+      </x:c>
+      <x:c r="M88" t="str">
+        <x:v>price,menu,promo.primary,store.name</x:v>
+      </x:c>
+      <x:c r="N88" t="str">
+        <x:v>가격·메뉴명·홍보 포인트는 검증된 매장 정보와 실제 촬영 메뉴로 치환한다. 레퍼런스 문구는 구조만 참고하고 그대로 복제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="O88" t="str">
+        <x:v>video,caption,text_2d,hard_cut</x:v>
+      </x:c>
+      <x:c r="P88" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q88" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R88" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S88" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T88" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U88" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V88" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W88" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>gts_donggeurio_challenge_v1_02</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D89" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E89" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F89" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="H89" t="str">
+        <x:v>반죽 붓고 펴기</x:v>
+      </x:c>
+      <x:c r="I89" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="J89" t="str">
+        <x:v>[2500~2800ms] 반죽이 조리판 중앙에 닿아 퍼지기 시작하는 순간을 보존한다. [3200~8000ms] 도구로 원형을 만들며 균일하게 펼치는 연속 동작을 Static 구도로 보여준다.</x:v>
+      </x:c>
+      <x:c r="K89" t="str">
+        <x:v>2500ms에서 Hard Cut한다. 반죽 확산 중간에는 컷하지 않고 원형 형태가 완성되는 모션 종료점인 8500ms 부근에서 전환한다.</x:v>
+      </x:c>
+      <x:c r="L89" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M89" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N89" t="str">
+        <x:v>실제 촬영된 첫 제조 행동으로 치환하되 제조 순서와 동작 완료 시점은 유지한다.</x:v>
+      </x:c>
+      <x:c r="O89" t="str">
+        <x:v>video,sfx,hard_cut</x:v>
+      </x:c>
+      <x:c r="P89" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q89" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R89" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S89" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T89" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U89" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V89" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W89" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>gts_donggeurio_challenge_v1_03</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D90" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E90" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F90" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>15200</x:v>
+      </x:c>
+      <x:c r="H90" t="str">
+        <x:v>굽기 및 접기</x:v>
+      </x:c>
+      <x:c r="I90" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>[8500~11000ms] 도구가 반죽 아래로 진입해 익은 반죽을 들어 올리고 접는 가장자리 움직임을 보존한다. [11000~15200ms] 형태를 다시 접고 다음 위치로 옮기는 동작을 완결한다.</x:v>
+      </x:c>
+      <x:c r="K90" t="str">
+        <x:v>익은 표면과 형태 변화가 식별되도록 유지한다. 접기 동작 완료 뒤 15200ms에서 토핑 공정으로 Hard Cut한다. 저작권 BGM 박자는 복제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L90" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M90" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N90" t="str">
+        <x:v>실제 메뉴의 상태 변화 동작으로 치환하되 존재하지 않는 공정은 생성하지 않고 실제 동작 완료 후 컷한다.</x:v>
+      </x:c>
+      <x:c r="O90" t="str">
+        <x:v>video,hard_cut</x:v>
+      </x:c>
+      <x:c r="P90" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q90" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R90" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S90" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T90" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U90" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V90" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W90" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>gts_donggeurio_challenge_v1_04</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D91" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E91" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F91" t="n">
+        <x:v>15200</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="H91" t="str">
+        <x:v>크림과 속재료 토핑</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>CORE_ACTION</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>[15200~20000ms] 크림 또는 핵심 재료가 층을 이루는 연속 과정을 보여준다. [20500~27000ms] 도구로 토핑을 배치하며 손·도구·재료의 색과 질감 대비를 강조한다.</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>재료 추가 순서를 유지하고 각 작업을 완결된 단위로 보존한다. 긴 반복 동작만 선택적으로 축약하거나 최대 1.2x로 조절하고 28000ms 부근에서 전환한다.</x:v>
+      </x:c>
+      <x:c r="L91" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M91" t="str">
+        <x:v>menu,promo.primary</x:v>
+      </x:c>
+      <x:c r="N91" t="str">
+        <x:v>실제 촬영 재료와 순서를 따른다. 반복만 축약할 수 있고 토핑 종류나 제조 순서는 바꾸지 않는다.</x:v>
+      </x:c>
+      <x:c r="O91" t="str">
+        <x:v>video,sfx,hard_cut,speed</x:v>
+      </x:c>
+      <x:c r="P91" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q91" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R91" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S91" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T91" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U91" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V91" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W91" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>gts_donggeurio_challenge_v1_05</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D92" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E92" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F92" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>38000</x:v>
+      </x:c>
+      <x:c r="H92" t="str">
+        <x:v>포장과 표면 마무리</x:v>
+      </x:c>
+      <x:c r="I92" t="str">
+        <x:v>CLIMAX_PREP</x:v>
+      </x:c>
+      <x:c r="J92" t="str">
+        <x:v>[28000~30000ms] 포장으로 형태를 고정한다. [30000~35000ms] 상단을 채우고 표면을 평탄화한다. [35000~38000ms] 마무리 재료가 떨어지는 미세 변화를 Close-up으로 강조한다.</x:v>
+      </x:c>
+      <x:c r="K92" t="str">
+        <x:v>후반 하이라이트를 준비하므로 시선을 메뉴 상단에 집중시킨다. 핵심 형태 변화는 잘게 분할하지 않고 마무리 재료 도포 완료 뒤 38000ms에 전환한다.</x:v>
+      </x:c>
+      <x:c r="L92" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M92" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N92" t="str">
+        <x:v>실제 메뉴의 포장·마무리 동작으로 치환하며 결과를 직접 바꾸는 핵심 동작 흐름은 보존한다.</x:v>
+      </x:c>
+      <x:c r="O92" t="str">
+        <x:v>video,sfx,hard_cut</x:v>
+      </x:c>
+      <x:c r="P92" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q92" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R92" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S92" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T92" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U92" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V92" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W92" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>gts_donggeurio_challenge_v1_06</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E93" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F93" t="n">
+        <x:v>38000</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="H93" t="str">
+        <x:v>토치와 완성 질감</x:v>
+      </x:c>
+      <x:c r="I93" t="str">
+        <x:v>CLIMAX_OUTRO</x:v>
+      </x:c>
+      <x:c r="J93" t="str">
+        <x:v>[38000~42000ms] 토치 불꽃이 표면에 닿아 색이 갈색으로 변하고 기포·광택이 생기는 시각 피크를 Close-up Static으로 보존한다. [42000~45000ms] 완성 표면과 최종 질감을 근접 촬영한다.</x:v>
+      </x:c>
+      <x:c r="K93" t="str">
+        <x:v>토치 최초 접촉 지점에 SFX를 동기화할 수 있다. 색 변화가 시작된 뒤 중간 컷을 금지하고 갈변이 인지될 때까지 연속 재생한 뒤 Cut-out 또는 자연스럽게 종료한다.</x:v>
+      </x:c>
+      <x:c r="L93" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M93" t="str">
+        <x:v>menu,promo.primary</x:v>
+      </x:c>
+      <x:c r="N93" t="str">
+        <x:v>실제 촬영된 가장 강한 질감 변화로 치환한다. 지원 범위 안에서 색보정하되 없는 동작이나 메뉴는 생성하지 않는다.</x:v>
+      </x:c>
+      <x:c r="O93" t="str">
+        <x:v>video,sfx,color_grading,hard_cut</x:v>
+      </x:c>
+      <x:c r="P93" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q93" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R93" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S93" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T93" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U93" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V93" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W93" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>gts_donggeurio_store_v1_01</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>완성 메뉴 선공개</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>HOOK</x:v>
+      </x:c>
+      <x:c r="J94" t="str">
+        <x:v>[0~500ms] 완성 메뉴가 시작 프레임부터 식별되도록 중앙에 노출한다. [1500~2000ms] 손목의 미세 좌우 틸팅으로 표면 광택과 질감을 강조한다. 카메라는 고정하고 피사체 움직임을 사용한다.</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>0ms부터 가장 시각적 임팩트가 높은 결과물을 노출한다. 형태·색상·질감이 인지된 뒤 2500ms 부근에서 제조 공정으로 Hard Cut한다.</x:v>
+      </x:c>
+      <x:c r="L94" t="str">
+        <x:v>{{price}}이지만 또 먹고 싶은 {{menu}}입니다</x:v>
+      </x:c>
+      <x:c r="M94" t="str">
+        <x:v>price,menu,promo.primary,store.name</x:v>
+      </x:c>
+      <x:c r="N94" t="str">
+        <x:v>가격·메뉴명·홍보 포인트는 검증된 매장 정보와 실제 촬영 메뉴로 치환한다. 레퍼런스 문구는 구조만 참고하고 그대로 복제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="O94" t="str">
+        <x:v>video,caption,text_2d,hard_cut</x:v>
+      </x:c>
+      <x:c r="P94" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q94" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R94" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S94" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T94" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U94" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V94" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W94" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X94" t="str">
+        <x:v>ELEMENT_01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>gts_donggeurio_store_v1_02</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F95" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>반죽 붓고 펴기</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="J95" t="str">
+        <x:v>[2500~2800ms] 반죽이 조리판 중앙에 닿아 퍼지기 시작하는 순간을 보존한다. [3200~8000ms] 도구로 원형을 만들며 균일하게 펼치는 연속 동작을 Static 구도로 보여준다.</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>2500ms에서 Hard Cut한다. 반죽 확산 중간에는 컷하지 않고 원형 형태가 완성되는 모션 종료점인 8500ms 부근에서 전환한다.</x:v>
+      </x:c>
+      <x:c r="L95" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M95" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N95" t="str">
+        <x:v>실제 촬영된 첫 제조 행동으로 치환하되 제조 순서와 동작 완료 시점은 유지한다.</x:v>
+      </x:c>
+      <x:c r="O95" t="str">
+        <x:v>video,sfx,hard_cut</x:v>
+      </x:c>
+      <x:c r="P95" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q95" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R95" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S95" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T95" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U95" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V95" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W95" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X95" t="str">
+        <x:v>ELEMENT_02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>gts_donggeurio_store_v1_03</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E96" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F96" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>15200</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>굽기 및 접기</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>BUILD_UP</x:v>
+      </x:c>
+      <x:c r="J96" t="str">
+        <x:v>[8500~11000ms] 도구가 반죽 아래로 진입해 익은 반죽을 들어 올리고 접는 가장자리 움직임을 보존한다. [11000~15200ms] 형태를 다시 접고 다음 위치로 옮기는 동작을 완결한다.</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>익은 표면과 형태 변화가 식별되도록 유지한다. 접기 동작 완료 뒤 15200ms에서 토핑 공정으로 Hard Cut한다. 저작권 BGM 박자는 복제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="L96" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M96" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N96" t="str">
+        <x:v>실제 메뉴의 상태 변화 동작으로 치환하되 존재하지 않는 공정은 생성하지 않고 실제 동작 완료 후 컷한다.</x:v>
+      </x:c>
+      <x:c r="O96" t="str">
+        <x:v>video,hard_cut</x:v>
+      </x:c>
+      <x:c r="P96" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q96" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R96" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S96" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T96" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U96" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V96" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W96" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X96" t="str">
+        <x:v>ELEMENT_03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>gts_donggeurio_store_v1_04</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E97" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F97" t="n">
+        <x:v>15200</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>크림과 속재료 토핑</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>CORE_ACTION</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>[15200~20000ms] 크림 또는 핵심 재료가 층을 이루는 연속 과정을 보여준다. [20500~27000ms] 도구로 토핑을 배치하며 손·도구·재료의 색과 질감 대비를 강조한다.</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>재료 추가 순서를 유지하고 각 작업을 완결된 단위로 보존한다. 긴 반복 동작만 선택적으로 축약하거나 최대 1.2x로 조절하고 28000ms 부근에서 전환한다.</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M97" t="str">
+        <x:v>menu,promo.primary</x:v>
+      </x:c>
+      <x:c r="N97" t="str">
+        <x:v>실제 촬영 재료와 순서를 따른다. 반복만 축약할 수 있고 토핑 종류나 제조 순서는 바꾸지 않는다.</x:v>
+      </x:c>
+      <x:c r="O97" t="str">
+        <x:v>video,sfx,hard_cut,speed</x:v>
+      </x:c>
+      <x:c r="P97" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q97" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R97" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S97" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T97" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U97" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V97" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W97" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X97" t="str">
+        <x:v>ELEMENT_04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>gts_donggeurio_store_v1_05</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E98" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F98" t="n">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>38000</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>포장과 표면 마무리</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>CLIMAX_PREP</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>[28000~30000ms] 포장으로 형태를 고정한다. [30000~35000ms] 상단을 채우고 표면을 평탄화한다. [35000~38000ms] 마무리 재료가 떨어지는 미세 변화를 Close-up으로 강조한다.</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>후반 하이라이트를 준비하므로 시선을 메뉴 상단에 집중시킨다. 핵심 형태 변화는 잘게 분할하지 않고 마무리 재료 도포 완료 뒤 38000ms에 전환한다.</x:v>
+      </x:c>
+      <x:c r="L98" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M98" t="str">
+        <x:v>menu</x:v>
+      </x:c>
+      <x:c r="N98" t="str">
+        <x:v>실제 메뉴의 포장·마무리 동작으로 치환하며 결과를 직접 바꾸는 핵심 동작 흐름은 보존한다.</x:v>
+      </x:c>
+      <x:c r="O98" t="str">
+        <x:v>video,sfx,hard_cut</x:v>
+      </x:c>
+      <x:c r="P98" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q98" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R98" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S98" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T98" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U98" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V98" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W98" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X98" t="str">
+        <x:v>ELEMENT_05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>gts_donggeurio_store_v1_06</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>gt_donggeurio_store_promotion_v1</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>donggeurio_store_promotion</x:v>
+      </x:c>
+      <x:c r="D99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E99" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F99" t="n">
+        <x:v>38000</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>토치와 완성 질감</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>CLIMAX_OUTRO</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>[38000~42000ms] 토치 불꽃이 표면에 닿아 색이 갈색으로 변하고 기포·광택이 생기는 시각 피크를 Close-up Static으로 보존한다. [42000~45000ms] 완성 표면과 최종 질감을 근접 촬영한다.</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>토치 최초 접촉 지점에 SFX를 동기화할 수 있다. 색 변화가 시작된 뒤 중간 컷을 금지하고 갈변이 인지될 때까지 연속 재생한 뒤 Cut-out 또는 자연스럽게 종료한다.</x:v>
+      </x:c>
+      <x:c r="L99" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="M99" t="str">
+        <x:v>menu,promo.primary</x:v>
+      </x:c>
+      <x:c r="N99" t="str">
+        <x:v>실제 촬영된 가장 강한 질감 변화로 치환한다. 지원 범위 안에서 색보정하되 없는 동작이나 메뉴는 생성하지 않는다.</x:v>
+      </x:c>
+      <x:c r="O99" t="str">
+        <x:v>video,sfx,color_grading,hard_cut</x:v>
+      </x:c>
+      <x:c r="P99" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q99" t="n">
+        <x:v>46262.18894675926</x:v>
+      </x:c>
+      <x:c r="R99" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S99" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T99" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$939:$G$1163</x:v>
+      </x:c>
+      <x:c r="U99" t="str">
+        <x:v>GEMINI_ANALYSIS_REPORT; EXECUTION_RULES_EMBEDDED_IN_ACTION_PATTERN_TIMING_RULE</x:v>
+      </x:c>
+      <x:c r="V99" t="str">
+        <x:v>REFERENCE_BGM_AND_PLATFORM_UI_EXCLUDED; CAPTIONS_REGENERATED_FROM_ACTUAL_FOOTAGE</x:v>
+      </x:c>
+      <x:c r="W99" t="str">
+        <x:v>A72F8CCF4EB1B758A13394041A1B59B3B8C84FFC776ECFE2D217FD688CEBDED7</x:v>
+      </x:c>
+      <x:c r="X99" t="str">
+        <x:v>ELEMENT_05</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/template_knowledge/sources/영상편집DB.xlsx
+++ b/app/template_knowledge/sources/영상편집DB.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R457d46e0091b4f7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R1b75e9a3ea38480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R25d335b7020b41d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R04f7d9cc4e664e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R274557fdb13543bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R3ce23ae9300744ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R696449c80e624539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="Ra344ed7808d34229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="Raddf62cf79ea418e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R112e96942e894201"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R316d4dee8fd741c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R96c9cb0ce0c44fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R8b6fff9d59b247d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R2559efaf5987480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R723ce5923351474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rb7fe763e7bd64973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R9e0a4e0e15734cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R5efd6aef886f4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R0fcb1d9fe35340d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R2300e1cb26c44df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R657d1f5689cb45d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R362a401d4c654592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="Ree13d59270e84394"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rbd47d9c6a19349cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="Rf769d156e8204fa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R4f30a5f5a4c54b63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -959,7 +959,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>최초 제공 템플릿의 시트·열 구조를 유지합니다. 현재 승인된 두 가이드의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:W 안에서 관리하고, 5프레임 분석은 action_pattern·timing_rule에 흡수합니다.</x:v>
+        <x:v>최초 제공 템플릿의 시트·열 구조를 유지합니다. 현재 승인된 세 가이드의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:W 안에서 관리하고, 프레임 분석은 action_pattern·timing_rule에 흡수합니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -1253,16 +1253,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>실제 가이드 2종</x:v>
+        <x:v>실제 가이드 3종</x:v>
       </x:c>
       <x:c r="B24" s="8" t="str">
-        <x:v>주술회전 트랜지션 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
+        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
       </x:c>
       <x:c r="C24" s="8" t="str">
         <x:v>02, 03, 12</x:v>
       </x:c>
       <x:c r="D24" s="8" t="str">
-        <x:v>12_SOURCE_GUIDES에 두 가이드의 원문·분석 근거를 보존하고 실행 규칙에 연결</x:v>
+        <x:v>12_SOURCE_GUIDES에 세 가이드의 원문·분석 근거를 보존하고 실행 규칙에 연결</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26296,368 +26296,984 @@
       </x:c>
     </x:row>
     <x:row r="679" ht="18" customHeight="1">
-      <x:c r="A679"/>
-      <x:c r="B679"/>
-      <x:c r="C679"/>
-      <x:c r="D679"/>
-      <x:c r="E679"/>
-      <x:c r="F679"/>
-      <x:c r="G679"/>
-      <x:c r="H679"/>
-      <x:c r="I679"/>
-      <x:c r="J679"/>
-      <x:c r="K679"/>
+      <x:c r="A679" t="str">
+        <x:v>jujutsu20260830_line_0001</x:v>
+      </x:c>
+      <x:c r="B679" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C679" t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="D679" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E679" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F679" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G679" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/Aa-CGr9-c8E; 14초, 8컷, 4개 SETUP/REVEAL 매치컷 쌍, confidence=0.98, 촬영 난이도 ★★.</x:v>
+      </x:c>
+      <x:c r="H679" t="str">
+        <x:v>주술회전_1프레임분석.json</x:v>
+      </x:c>
+      <x:c r="I679" t="str">
+        <x:v>6868F640E082BDCFE1616CAF43F36267706D571358838896B5CDC74CC6646F31</x:v>
+      </x:c>
+      <x:c r="J679" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K679" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="680" ht="18" customHeight="1">
-      <x:c r="A680"/>
-      <x:c r="B680"/>
-      <x:c r="C680"/>
-      <x:c r="D680"/>
-      <x:c r="E680"/>
-      <x:c r="F680"/>
-      <x:c r="G680"/>
-      <x:c r="H680"/>
-      <x:c r="I680"/>
-      <x:c r="J680"/>
-      <x:c r="K680"/>
+      <x:c r="A680" t="str">
+        <x:v>jujutsu20260830_line_0002</x:v>
+      </x:c>
+      <x:c r="B680" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C680" t="n">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="D680" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E680" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F680" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G680" t="str">
+        <x:v>- S01 0-1500ms HOOK_SETUP: 인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="H680" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I680" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J680" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K680" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="681" ht="18" customHeight="1">
-      <x:c r="A681"/>
-      <x:c r="B681"/>
-      <x:c r="C681"/>
-      <x:c r="D681"/>
-      <x:c r="E681"/>
-      <x:c r="F681"/>
-      <x:c r="G681"/>
-      <x:c r="H681"/>
-      <x:c r="I681"/>
-      <x:c r="J681"/>
-      <x:c r="K681"/>
+      <x:c r="A681" t="str">
+        <x:v>jujutsu20260830_line_0003</x:v>
+      </x:c>
+      <x:c r="B681" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C681" t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="D681" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E681" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F681" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G681" t="str">
+        <x:v>- S02 1500-3500ms MAGIC_REVEAL: S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
+      </x:c>
+      <x:c r="H681" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I681" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J681" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K681" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="682" ht="18" customHeight="1">
-      <x:c r="A682"/>
-      <x:c r="B682"/>
-      <x:c r="C682"/>
-      <x:c r="D682"/>
-      <x:c r="E682"/>
-      <x:c r="F682"/>
-      <x:c r="G682"/>
-      <x:c r="H682"/>
-      <x:c r="I682"/>
-      <x:c r="J682"/>
-      <x:c r="K682"/>
+      <x:c r="A682" t="str">
+        <x:v>jujutsu20260830_line_0004</x:v>
+      </x:c>
+      <x:c r="B682" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C682" t="n">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="D682" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E682" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F682" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G682" t="str">
+        <x:v>- S03 3500-5000ms SETUP: 인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
+      </x:c>
+      <x:c r="H682" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I682" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J682" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K682" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="683" ht="18" customHeight="1">
-      <x:c r="A683"/>
-      <x:c r="B683"/>
-      <x:c r="C683"/>
-      <x:c r="D683"/>
-      <x:c r="E683"/>
-      <x:c r="F683"/>
-      <x:c r="G683"/>
-      <x:c r="H683"/>
-      <x:c r="I683"/>
-      <x:c r="J683"/>
-      <x:c r="K683"/>
+      <x:c r="A683" t="str">
+        <x:v>jujutsu20260830_line_0005</x:v>
+      </x:c>
+      <x:c r="B683" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C683" t="n">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c r="D683" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E683" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F683" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G683" t="str">
+        <x:v>- S04 5000-7000ms MAGIC_REVEAL: S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
+      </x:c>
+      <x:c r="H683" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I683" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J683" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K683" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="684" ht="18" customHeight="1">
-      <x:c r="A684"/>
-      <x:c r="B684"/>
-      <x:c r="C684"/>
-      <x:c r="D684"/>
-      <x:c r="E684"/>
-      <x:c r="F684"/>
-      <x:c r="G684"/>
-      <x:c r="H684"/>
-      <x:c r="I684"/>
-      <x:c r="J684"/>
-      <x:c r="K684"/>
+      <x:c r="A684" t="str">
+        <x:v>jujutsu20260830_line_0006</x:v>
+      </x:c>
+      <x:c r="B684" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C684" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="D684" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E684" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F684" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G684" t="str">
+        <x:v>- S05 7000-8500ms SETUP: 인물 A가 다시 등장해 케이크 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="H684" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I684" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J684" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K684" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="685" ht="18" customHeight="1">
-      <x:c r="A685"/>
-      <x:c r="B685"/>
-      <x:c r="C685"/>
-      <x:c r="D685"/>
-      <x:c r="E685"/>
-      <x:c r="F685"/>
-      <x:c r="G685"/>
-      <x:c r="H685"/>
-      <x:c r="I685"/>
-      <x:c r="J685"/>
-      <x:c r="K685"/>
+      <x:c r="A685" t="str">
+        <x:v>jujutsu20260830_line_0007</x:v>
+      </x:c>
+      <x:c r="B685" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C685" t="n">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="D685" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E685" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F685" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G685" t="str">
+        <x:v>- S06 8500-10500ms MAGIC_REVEAL: S05와 동일 포즈·구도에서 인물 A가 실제 케이크 접시를 든 상태로 시작</x:v>
+      </x:c>
+      <x:c r="H685" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I685" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J685" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K685" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="686" ht="18" customHeight="1">
-      <x:c r="A686"/>
-      <x:c r="B686"/>
-      <x:c r="C686"/>
-      <x:c r="D686"/>
-      <x:c r="E686"/>
-      <x:c r="F686"/>
-      <x:c r="G686"/>
-      <x:c r="H686"/>
-      <x:c r="I686"/>
-      <x:c r="J686"/>
-      <x:c r="K686"/>
+      <x:c r="A686" t="str">
+        <x:v>jujutsu20260830_line_0008</x:v>
+      </x:c>
+      <x:c r="B686" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C686" t="n">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="D686" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E686" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F686" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G686" t="str">
+        <x:v>- S07 10500-12000ms SETUP: 인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
+      </x:c>
+      <x:c r="H686" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I686" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J686" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K686" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="687" ht="18" customHeight="1">
-      <x:c r="A687"/>
-      <x:c r="B687"/>
-      <x:c r="C687"/>
-      <x:c r="D687"/>
-      <x:c r="E687"/>
-      <x:c r="F687"/>
-      <x:c r="G687"/>
-      <x:c r="H687"/>
-      <x:c r="I687"/>
-      <x:c r="J687"/>
-      <x:c r="K687"/>
+      <x:c r="A687" t="str">
+        <x:v>jujutsu20260830_line_0009</x:v>
+      </x:c>
+      <x:c r="B687" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C687" t="n">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="D687" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E687" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F687" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G687" t="str">
+        <x:v>- S08 12000-14000ms MAGIC_REVEAL: S07과 동일 포즈·구도에서 실제 빵 접시가 나타난 상태로 전환해 아웃트로 유지</x:v>
+      </x:c>
+      <x:c r="H687" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I687" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J687" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K687" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="688" ht="18" customHeight="1">
-      <x:c r="A688"/>
-      <x:c r="B688"/>
-      <x:c r="C688"/>
-      <x:c r="D688"/>
-      <x:c r="E688"/>
-      <x:c r="F688"/>
-      <x:c r="G688"/>
-      <x:c r="H688"/>
-      <x:c r="I688"/>
-      <x:c r="J688"/>
-      <x:c r="K688"/>
+      <x:c r="A688" t="str">
+        <x:v>jujutsu20260830_line_0010</x:v>
+      </x:c>
+      <x:c r="B688" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C688" t="n">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="D688" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E688" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F688" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G688" t="str">
+        <x:v>- reveal_sfx_markers_ms: 1500, 5000, 8500, 12000; 모든 MAGIC_REVEAL 첫 프레임을 타격점에 정렬.</x:v>
+      </x:c>
+      <x:c r="H688" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I688" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J688" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K688" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="689" ht="18" customHeight="1">
-      <x:c r="A689"/>
-      <x:c r="B689"/>
-      <x:c r="C689"/>
-      <x:c r="D689"/>
-      <x:c r="E689"/>
-      <x:c r="F689"/>
-      <x:c r="G689"/>
-      <x:c r="H689"/>
-      <x:c r="I689"/>
-      <x:c r="J689"/>
-      <x:c r="K689"/>
+      <x:c r="A689" t="str">
+        <x:v>jujutsu20260830_line_0011</x:v>
+      </x:c>
+      <x:c r="B689" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C689" t="n">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="D689" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E689" t="str">
+        <x:v>MATCH_RULE</x:v>
+      </x:c>
+      <x:c r="F689" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G689" t="str">
+        <x:v>- 각 SETUP/REVEAL 쌍은 동일 인물·카메라·배경·포즈를 유지하고 SETUP에는 아이템이 없어야 하며 REVEAL에는 명확히 보여야 함.</x:v>
+      </x:c>
+      <x:c r="H689" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I689" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J689" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K689" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="690" ht="18" customHeight="1">
-      <x:c r="A690"/>
-      <x:c r="B690"/>
-      <x:c r="C690"/>
-      <x:c r="D690"/>
-      <x:c r="E690"/>
-      <x:c r="F690"/>
-      <x:c r="G690"/>
-      <x:c r="H690"/>
-      <x:c r="I690"/>
-      <x:c r="J690"/>
-      <x:c r="K690"/>
+      <x:c r="A690" t="str">
+        <x:v>jujutsu20260830_line_0012</x:v>
+      </x:c>
+      <x:c r="B690" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C690" t="n">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="D690" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E690" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F690" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G690" t="str">
+        <x:v>- 별도 자막·애니메이션 오버레이 없음. 플랫폼 UI와 레퍼런스 오디오는 편집 요소로 복제하지 않음.</x:v>
+      </x:c>
+      <x:c r="H690" t="str">
+        <x:v>주술회전_1프레임분석.json</x:v>
+      </x:c>
+      <x:c r="I690" t="str">
+        <x:v>6868F640E082BDCFE1616CAF43F36267706D571358838896B5CDC74CC6646F31</x:v>
+      </x:c>
+      <x:c r="J690" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K690" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="691" ht="18" customHeight="1">
-      <x:c r="A691"/>
-      <x:c r="B691"/>
-      <x:c r="C691"/>
-      <x:c r="D691"/>
-      <x:c r="E691"/>
-      <x:c r="F691"/>
-      <x:c r="G691"/>
-      <x:c r="H691"/>
-      <x:c r="I691"/>
-      <x:c r="J691"/>
-      <x:c r="K691"/>
+      <x:c r="A691" t="str">
+        <x:v>jujutsu20260830_line_0013</x:v>
+      </x:c>
+      <x:c r="B691" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C691" t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="D691" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E691" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F691" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G691" t="str">
+        <x:v>- hard_fail: 카메라 이동, 배경/인물 불일치, SETUP 아이템 노출, REVEAL 아이템 미노출, SFX 비동기, 경계 디졸브/페이드.</x:v>
+      </x:c>
+      <x:c r="H691" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I691" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J691" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K691" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="692" ht="18" customHeight="1">
-      <x:c r="A692"/>
-      <x:c r="B692"/>
-      <x:c r="C692"/>
-      <x:c r="D692"/>
-      <x:c r="E692"/>
-      <x:c r="F692"/>
-      <x:c r="G692"/>
-      <x:c r="H692"/>
-      <x:c r="I692"/>
-      <x:c r="J692"/>
-      <x:c r="K692"/>
+      <x:c r="A692" t="str">
+        <x:v>jujutsu20260830_line_0014</x:v>
+      </x:c>
+      <x:c r="B692" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C692" t="n">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="D692" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E692" t="str">
+        <x:v>PROVENANCE</x:v>
+      </x:c>
+      <x:c r="F692" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G692" t="str">
+        <x:v>- 포즈/배경 정렬 점수·안정 구간 탐색·대체 테이크·미세 crop/translation 복구를 추가하되 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="H692" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I692" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J692" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K692" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="693" ht="18" customHeight="1">
-      <x:c r="A693"/>
-      <x:c r="B693"/>
-      <x:c r="C693"/>
-      <x:c r="D693"/>
-      <x:c r="E693"/>
-      <x:c r="F693"/>
-      <x:c r="G693"/>
-      <x:c r="H693"/>
-      <x:c r="I693"/>
-      <x:c r="J693"/>
-      <x:c r="K693"/>
+      <x:c r="A693" t="str">
+        <x:v>donggeurio20260830_line_0001</x:v>
+      </x:c>
+      <x:c r="B693" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C693" t="n">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="D693" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E693" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F693" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G693" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/iWyRoIJheV4; 실측 12.067초, 7컷 웜톤 카페 브이로그, shooting_difficulty: ★★, confidence=0.95.</x:v>
+      </x:c>
+      <x:c r="H693" t="str">
+        <x:v>동그리오_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I693" t="str">
+        <x:v>F8C3D8926CE141C84DF9C8077E82B5ABB6A90162A4E8BAF689277EDA85400A71</x:v>
+      </x:c>
+      <x:c r="J693" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K693" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="694" ht="18" customHeight="1">
-      <x:c r="A694"/>
-      <x:c r="B694"/>
-      <x:c r="C694"/>
-      <x:c r="D694"/>
-      <x:c r="E694"/>
-      <x:c r="F694"/>
-      <x:c r="G694"/>
-      <x:c r="H694"/>
-      <x:c r="I694"/>
-      <x:c r="J694"/>
-      <x:c r="K694"/>
+      <x:c r="A694" t="str">
+        <x:v>donggeurio20260830_line_0002</x:v>
+      </x:c>
+      <x:c r="B694" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C694" t="n">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="D694" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E694" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F694" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G694" t="str">
+        <x:v>- S01 0-1033ms HOOK: 안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
+      </x:c>
+      <x:c r="H694" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I694" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J694" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K694" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="695" ht="18" customHeight="1">
-      <x:c r="A695"/>
-      <x:c r="B695"/>
-      <x:c r="C695"/>
-      <x:c r="D695"/>
-      <x:c r="E695"/>
-      <x:c r="F695"/>
-      <x:c r="G695"/>
-      <x:c r="H695"/>
-      <x:c r="I695"/>
-      <x:c r="J695"/>
-      <x:c r="K695"/>
+      <x:c r="A695" t="str">
+        <x:v>donggeurio20260830_line_0003</x:v>
+      </x:c>
+      <x:c r="B695" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C695" t="n">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="D695" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E695" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F695" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G695" t="str">
+        <x:v>- S02 1033-3767ms REVEAL: 메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
+      </x:c>
+      <x:c r="H695" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I695" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J695" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K695" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="696" ht="18" customHeight="1">
-      <x:c r="A696"/>
-      <x:c r="B696"/>
-      <x:c r="C696"/>
-      <x:c r="D696"/>
-      <x:c r="E696"/>
-      <x:c r="F696"/>
-      <x:c r="G696"/>
-      <x:c r="H696"/>
-      <x:c r="I696"/>
-      <x:c r="J696"/>
-      <x:c r="K696"/>
+      <x:c r="A696" t="str">
+        <x:v>donggeurio20260830_line_0004</x:v>
+      </x:c>
+      <x:c r="B696" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C696" t="n">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="D696" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E696" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F696" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G696" t="str">
+        <x:v>- S03 3767-4700ms AMBIENCE: 조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
+      </x:c>
+      <x:c r="H696" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I696" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J696" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K696" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="697" ht="18" customHeight="1">
-      <x:c r="A697"/>
-      <x:c r="B697"/>
-      <x:c r="C697"/>
-      <x:c r="D697"/>
-      <x:c r="E697"/>
-      <x:c r="F697"/>
-      <x:c r="G697"/>
-      <x:c r="H697"/>
-      <x:c r="I697"/>
-      <x:c r="J697"/>
-      <x:c r="K697"/>
+      <x:c r="A697" t="str">
+        <x:v>donggeurio20260830_line_0005</x:v>
+      </x:c>
+      <x:c r="B697" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C697" t="n">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="D697" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E697" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F697" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G697" t="str">
+        <x:v>- S04 4700-7000ms ACTION: 손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
+      </x:c>
+      <x:c r="H697" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I697" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J697" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K697" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="698" ht="18" customHeight="1">
-      <x:c r="A698"/>
-      <x:c r="B698"/>
-      <x:c r="C698"/>
-      <x:c r="D698"/>
-      <x:c r="E698"/>
-      <x:c r="F698"/>
-      <x:c r="G698"/>
-      <x:c r="H698"/>
-      <x:c r="I698"/>
-      <x:c r="J698"/>
-      <x:c r="K698"/>
+      <x:c r="A698" t="str">
+        <x:v>donggeurio20260830_line_0006</x:v>
+      </x:c>
+      <x:c r="B698" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C698" t="n">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="D698" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E698" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F698" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G698" t="str">
+        <x:v>- S05 7000-8333ms ACTION_HIGHLIGHT: 포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
+      </x:c>
+      <x:c r="H698" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I698" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J698" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K698" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="699" ht="18" customHeight="1">
-      <x:c r="A699"/>
-      <x:c r="B699"/>
-      <x:c r="C699"/>
-      <x:c r="D699"/>
-      <x:c r="E699"/>
-      <x:c r="F699"/>
-      <x:c r="G699"/>
-      <x:c r="H699"/>
-      <x:c r="I699"/>
-      <x:c r="J699"/>
-      <x:c r="K699"/>
+      <x:c r="A699" t="str">
+        <x:v>donggeurio20260830_line_0007</x:v>
+      </x:c>
+      <x:c r="B699" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C699" t="n">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="D699" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E699" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F699" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G699" t="str">
+        <x:v>- S06 8333-9633ms LOCATION: 매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
+      </x:c>
+      <x:c r="H699" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I699" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J699" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K699" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="700" ht="18" customHeight="1">
-      <x:c r="A700"/>
-      <x:c r="B700"/>
-      <x:c r="C700"/>
-      <x:c r="D700"/>
-      <x:c r="E700"/>
-      <x:c r="F700"/>
-      <x:c r="G700"/>
-      <x:c r="H700"/>
-      <x:c r="I700"/>
-      <x:c r="J700"/>
-      <x:c r="K700"/>
+      <x:c r="A700" t="str">
+        <x:v>donggeurio20260830_line_0008</x:v>
+      </x:c>
+      <x:c r="B700" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C700" t="n">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="D700" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E700" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F700" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G700" t="str">
+        <x:v>- S07 9633-12067ms OUTRO: 비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
+      </x:c>
+      <x:c r="H700" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I700" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J700" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K700" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="701" ht="18" customHeight="1">
-      <x:c r="A701"/>
-      <x:c r="B701"/>
-      <x:c r="C701"/>
-      <x:c r="D701"/>
-      <x:c r="E701"/>
-      <x:c r="F701"/>
-      <x:c r="G701"/>
-      <x:c r="H701"/>
-      <x:c r="I701"/>
-      <x:c r="J701"/>
-      <x:c r="K701"/>
+      <x:c r="A701" t="str">
+        <x:v>donggeurio20260830_line_0009</x:v>
+      </x:c>
+      <x:c r="B701" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C701" t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="D701" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E701" t="str">
+        <x:v>TIMELINE</x:v>
+      </x:c>
+      <x:c r="F701" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G701" t="str">
+        <x:v>- measured_boundaries_ms: 0,1033,3767,4700,7000,8333,9633,12067. 실행 시간축은 MP4 실측 경계를, 의미 라벨은 분석 JSON을 우선.</x:v>
+      </x:c>
+      <x:c r="H701" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I701" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J701" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K701" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="702" ht="18" customHeight="1">
-      <x:c r="A702"/>
-      <x:c r="B702"/>
-      <x:c r="C702"/>
-      <x:c r="D702"/>
-      <x:c r="E702"/>
-      <x:c r="F702"/>
-      <x:c r="G702"/>
-      <x:c r="H702"/>
-      <x:c r="I702"/>
-      <x:c r="J702"/>
-      <x:c r="K702"/>
+      <x:c r="A702" t="str">
+        <x:v>donggeurio20260830_line_0010</x:v>
+      </x:c>
+      <x:c r="B702" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C702" t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="D702" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E702" t="str">
+        <x:v>COLOR</x:v>
+      </x:c>
+      <x:c r="F702" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G702" t="str">
+        <x:v>- WARM tone; contrast/saturation +10~15%. 정확한 temperature 값은 COLOR.WARM_VLOG.TEMPERATURE 정책에서 해결.</x:v>
+      </x:c>
+      <x:c r="H702" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I702" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J702" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K702" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="703" ht="18" customHeight="1">
-      <x:c r="A703"/>
-      <x:c r="B703"/>
-      <x:c r="C703"/>
-      <x:c r="D703"/>
-      <x:c r="E703"/>
-      <x:c r="F703"/>
-      <x:c r="G703"/>
-      <x:c r="H703"/>
-      <x:c r="I703"/>
-      <x:c r="J703"/>
-      <x:c r="K703"/>
+      <x:c r="A703" t="str">
+        <x:v>donggeurio20260830_line_0011</x:v>
+      </x:c>
+      <x:c r="B703" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C703" t="n">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="D703" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E703" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F703" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G703" t="str">
+        <x:v>- S01 중앙 타이틀, S02 하단 보조 텍스트. 레퍼런스 상호·핸들은 복제하지 않고 사용자 프로젝트 메타데이터로 교체.</x:v>
+      </x:c>
+      <x:c r="H703" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I703" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J703" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K703" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="704" ht="18" customHeight="1">
-      <x:c r="A704"/>
-      <x:c r="B704"/>
-      <x:c r="C704"/>
-      <x:c r="D704"/>
-      <x:c r="E704"/>
-      <x:c r="F704"/>
-      <x:c r="G704"/>
-      <x:c r="H704"/>
-      <x:c r="I704"/>
-      <x:c r="J704"/>
-      <x:c r="K704"/>
+      <x:c r="A704" t="str">
+        <x:v>donggeurio20260830_line_0012</x:v>
+      </x:c>
+      <x:c r="B704" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C704" t="n">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="D704" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E704" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F704" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G704" t="str">
+        <x:v>- BEAT_SYNC_MUSIC; 의미 앵커를 훼손하지 않는 범위에서 인접 강한 onset에 컷을 스냅. 플랫폼 음원은 사용자가 추가.</x:v>
+      </x:c>
+      <x:c r="H704" t="str">
+        <x:v>동그리오_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I704" t="str">
+        <x:v>F8C3D8926CE141C84DF9C8077E82B5ABB6A90162A4E8BAF689277EDA85400A71</x:v>
+      </x:c>
+      <x:c r="J704" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K704" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="705" ht="18" customHeight="1">
-      <x:c r="A705"/>
-      <x:c r="B705"/>
-      <x:c r="C705"/>
-      <x:c r="D705"/>
-      <x:c r="E705"/>
-      <x:c r="F705"/>
-      <x:c r="G705"/>
-      <x:c r="H705"/>
-      <x:c r="I705"/>
-      <x:c r="J705"/>
-      <x:c r="K705"/>
+      <x:c r="A705" t="str">
+        <x:v>donggeurio20260830_line_0013</x:v>
+      </x:c>
+      <x:c r="B705" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C705" t="n">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="D705" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E705" t="str">
+        <x:v>PARAMETER_POLICY</x:v>
+      </x:c>
+      <x:c r="F705" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G705" t="str">
+        <x:v>- 미해결 키: COLOR.WARM_VLOG.TEMPERATURE, CAMERA.SLIGHT_ZOOM.DEFAULT, TRANSITION.FADE_OUT.DEFAULT_DURATION_MS.</x:v>
+      </x:c>
+      <x:c r="H705" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I705" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J705" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K705" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="706" ht="18" customHeight="1">
-      <x:c r="A706"/>
-      <x:c r="B706"/>
-      <x:c r="C706"/>
-      <x:c r="D706"/>
-      <x:c r="E706"/>
-      <x:c r="F706"/>
-      <x:c r="G706"/>
-      <x:c r="H706"/>
-      <x:c r="I706"/>
-      <x:c r="J706"/>
-      <x:c r="K706"/>
+      <x:c r="A706" t="str">
+        <x:v>donggeurio20260830_line_0014</x:v>
+      </x:c>
+      <x:c r="B706" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C706" t="n">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="D706" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E706" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F706" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G706" t="str">
+        <x:v>- 7개 슬롯, 컷 경계 단조 증가, 전체 12067±34ms, 액션 앵커 보존, 속도 범위 준수, 레퍼런스 브랜드 미복제.</x:v>
+      </x:c>
+      <x:c r="H706" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I706" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J706" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K706" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="707" ht="18" customHeight="1">
       <x:c r="A707"/>
@@ -32629,7 +33245,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>승인된 두 가이드의 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 랭킹 2위는 공란으로 유지하며 다른 순위를 당겨 채우지 않습니다.</x:v>
+        <x:v>승인된 세 가이드의 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 랭킹 1·2·3위를 유지하며 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -32660,10 +33276,10 @@
         <x:v>챌린지 입력</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>랭킹 1위와 3위만 유지하며 2위는 공란</x:v>
+        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
         <x:v>02_INPUT_GUIDES</x:v>
@@ -32674,10 +33290,10 @@
         <x:v>전체 가이드 템플릿 구간</x:v>
       </x:c>
       <x:c r="B6" s="5" t="n">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
-        <x:v>삭제 대상 제거 후 남은 03_GUIDE_TEMPLATES 데이터 행</x:v>
+        <x:v>버전 이력을 포함한 03_GUIDE_TEMPLATES 데이터 행</x:v>
       </x:c>
       <x:c r="D6" s="2" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -32769,13 +33385,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>5프레임 분석 근거</x:v>
+        <x:v>프레임 분석 실행 구간</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:v>152</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>주술회전 75 + 오츠카레 썸머 77블록을 03 실행 구간에 흡수</x:v>
+        <x:v>기존 152개 블록 + 주술회전 8컷 + 동그리오 7컷의 신규 JSON 근거</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -32783,13 +33399,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>주술회전 v4 실행 구간</x:v>
+        <x:v>주술회전 v5 실행 구간</x:v>
       </x:c>
       <x:c r="B14" t="n">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>F0-F371을 비중첩 세팅/블러/리빌/홀드/루프 단위로 분해한 실행 템플릿</x:v>
+        <x:v>0~14초 SETUP/REVEAL 4쌍의 ACTIVE 8컷 템플릿</x:v>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -32811,13 +33427,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>카페 추천 리뷰 v2 실행 구간</x:v>
+        <x:v>동그리오 v1 실행 구간</x:v>
       </x:c>
       <x:c r="B16" t="n">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>F0-F304를 컷·자막 상태·무자막 gap·엔드카드·루프 프리픽스 기준 23개 비중첩 구간으로 분해</x:v>
+        <x:v>실측 0~12.067초의 훅·메뉴·공간·액션·외관·아웃트로 7컷</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -32863,7 +33479,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>승인된 주술회전·오츠카레 썸머 가이드의 실제 업로드 MP4 정밀 분석을 유지합니다. rank 1과 3을 보존하고 rank 2는 공란으로 둡니다.</x:v>
+        <x:v>승인된 주술회전·동그리오·오츠카레 썸머 가이드를 유지합니다. rank 1·2·3을 보존하고 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -32926,10 +33542,10 @@
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" s="9" t="str">
-        <x:v>uploaded_guide_videos_20260824</x:v>
-      </x:c>
-      <x:c r="B5" s="118" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>uploaded_analysis_json_20260830</x:v>
+      </x:c>
+      <x:c r="B5" s="118" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
         <x:v>jujutsu_transition</x:v>
@@ -32947,7 +33563,7 @@
         <x:v>https://www.youtube.com/shorts/Aa-CGr9-c8E</x:v>
       </x:c>
       <x:c r="H5" s="9" t="str">
-        <x:v>Yc7ZjC0n7oY</x:v>
+        <x:v>Aa-CGr9-c8E</x:v>
       </x:c>
       <x:c r="I5" s="9" t="str">
         <x:v>PASS</x:v>
@@ -32961,50 +33577,73 @@
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="9" t="str">
-        <x:v>uploaded_guide_videos_20260824</x:v>
-      </x:c>
-      <x:c r="B6" s="118" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>uploaded_analysis_json_20260830</x:v>
+      </x:c>
+      <x:c r="B6" s="118" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D6" s="9" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>오츠카레 썸머 챌린지</x:v>
+        <x:v>동그리오 챌린지</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>오츠카레 썸머 챌린지</x:v>
+        <x:v>동그리오 챌린지</x:v>
       </x:c>
       <x:c r="G6" s="30" t="str">
-        <x:v>https://www.youtube.com/shorts/e-dU9yQfmik?si=fGCn4wuBsTEm2Q-p</x:v>
+        <x:v>https://www.youtube.com/shorts/iWyRoIJheV4</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>e-dU9yQfmik</x:v>
+        <x:v>iWyRoIJheV4</x:v>
       </x:c>
       <x:c r="I6" s="9" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="J6" s="63" t="str">
+        <x:v>food</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>정보형</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>uploaded_guide_videos_20260824</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>오츠카레 썸머 챌린지</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>오츠카레 썸머 챌린지</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>https://www.youtube.com/shorts/e-dU9yQfmik?si=fGCn4wuBsTEm2Q-p</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>e-dU9yQfmik</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
         <x:v>challenge</x:v>
       </x:c>
-      <x:c r="K6" t="str">
+      <x:c r="K7" t="str">
         <x:v>챌린지</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7"/>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7"/>
-      <x:c r="J7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -33041,9 +33680,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="Ra9f0d4762c154750"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="Red14ec43976b413a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Rdebae918f4f94596"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="Rc3c8540323df46bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R89123a148bde41bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Rbfb375263a4c4223"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -33080,7 +33719,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="119" t="str">
-        <x:v>실제 편집 가이드 3종 · 원본 스키마 고정형 V2</x:v>
+        <x:v>실제 편집 가이드 3종 · 원본 스키마 고정형 v5.4</x:v>
       </x:c>
       <x:c r="B1" s="31"/>
       <x:c r="C1" s="31"/>
@@ -33107,7 +33746,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="120" t="str">
-        <x:v>최초 템플릿 구조를 유지해 새 시트/새 열을 추가하지 않습니다. 5프레임 분석은 03의 action_pattern·timing_rule에 흡수하고, action_pattern은 동작·카메라·컷·효과·5프레임 근거까지 상세 기록합니다. personalization_rule은 새 사용자 영상에서 실제로 바꿀 수 있는 규칙만 정의하며, 레퍼런스 자막 문구는 고정 재사용하지 않고 LLM이 새 영상 내용에 맞춰 생성합니다.</x:v>
+        <x:v>최초 템플릿 구조를 유지해 새 시트·새 열을 추가하지 않습니다. 주술회전·동그리오의 업로드 JSON 근거를 action_pattern·timing_rule에 흡수하고, 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -34221,7 +34860,7 @@
         <x:v>HOOK_SETUP_A</x:v>
       </x:c>
       <x:c r="J19" s="69" t="str">
-        <x:v>[ACTION] 여성 정면 미디엄 구도. 오른손 손가락 포즈를 얼굴 옆에 고정하고 왼팔/손바닥을 카메라 전방으로 내민다. | [FRAME] 30fps F000-F009 (10f); phase=SETUP_EMPTY; shot=S1_WOMAN_DRINK | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left wrist/palm; camera position locked pre/post; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=SHOT_START@F000; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; next reveal anchor=F12; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F000-F004:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=오른손 손가락 포즈 + 왼손을 카메라 쪽으로 내민 상태; event=NONE; zoom=1; speed=1; MAD=1.572/4.418; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F005-F009:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=오른손 손가락 포즈 + 왼손을 카메라 쪽으로 내민 상태; event=NONE; zoom=1; speed=1; MAD=2.777/8.612; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 정면 미디엄 구도. 오른손 손가락 포즈를 얼굴 옆에 고정하고 왼팔/손바닥을 카메라 전방으로 내민다. | [FRAME] 30fps F000-F009 (10f); phase=SETUP_EMPTY; shot=S1_WOMAN_DRINK | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left wrist/palm; camera position locked pre/post; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=SHOT_START@F000; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; next reveal anchor=F12; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F000-F004:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=오른손 손가락 포즈 + 왼손을 카메라 쪽으로 내민 상태; event=NONE; zoom=1; speed=1; MAD=1.572/4.418; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F005-F009:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=오른손 손가락 포즈 + 왼손을 카메라 쪽으로 내민 상태; event=NONE; zoom=1; speed=1; MAD=2.777/8.612; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K19" s="69" t="str">
         <x:v>30fps; segment=F000-F009; start=0ms; end=333.333ms; duration=10f; event=SHOT_START@F000; hard_cut_in=-1; transition=NONE; transition_frames=0; speed=1; zoom=1; audio_anchor=NO_REQUIRED_EVENT; next reveal anchor=F12</x:v>
@@ -34248,7 +34887,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S19" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T19" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34319,7 +34958,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S20" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T20" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34390,7 +35029,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S21" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T21" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34434,7 +35073,7 @@
         <x:v>RESULT_HOLD_A</x:v>
       </x:c>
       <x:c r="J22" s="69" t="str">
-        <x:v>[ACTION] 상품을 카메라 가까운 전경에 유지하고 오른손 포즈·얼굴·카메라 위치를 크게 바꾸지 않는다. | [FRAME] 30fps F013-F058 (46f); phase=PRODUCT_HOLD; shot=S1_WOMAN_DRINK | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left wrist/palm; camera position locked pre/post; state=PRODUCT_A_LARGE_ICED_DRINK_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain source cadence until hard cut F59; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F010-F014:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=F10-11 FULL_FRAME_VERTICAL_MOTION_BLUR | F12 PRODUCT_A_REVEAL; zoom=1; speed=1; MAD=11.324/29.809; cmd=F10-11:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F12:MATCH_CUT_PRE_POST_TAKE+PRODUCT_A_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F015-F019:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.153/5.43; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F020-F024:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.002/5.201; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F025-F029:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.546/4.754; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F030-F034:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.648/4.412; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F035-F039:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.103/4.143; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F040-F044:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.903/3.612; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F045-F049:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.582/3.735; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F050-F054:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.165/3.814; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F055-F059:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=F59 HARD_CUT S1→S2; zoom=1; speed=1; MAD=14.665/69.427; cmd=F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 상품을 카메라 가까운 전경에 유지하고 오른손 포즈·얼굴·카메라 위치를 크게 바꾸지 않는다. | [FRAME] 30fps F013-F058 (46f); phase=PRODUCT_HOLD; shot=S1_WOMAN_DRINK | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left wrist/palm; camera position locked pre/post; state=PRODUCT_A_LARGE_ICED_DRINK_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain source cadence until hard cut F59; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F010-F014:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=F10-11 FULL_FRAME_VERTICAL_MOTION_BLUR | F12 PRODUCT_A_REVEAL; zoom=1; speed=1; MAD=11.324/29.809; cmd=F10-11:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F12:MATCH_CUT_PRE_POST_TAKE+PRODUCT_A_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F015-F019:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.153/5.43; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F020-F024:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.002/5.201; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F025-F029:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.546/4.754; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F030-F034:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.648/4.412; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F035-F039:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.103/4.143; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F040-F044:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.903/3.612; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F045-F049:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.582/3.735; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F050-F054:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=왼손으로 큰 아이스 음료를 전경에 제시하고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.165/3.814; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F055-F059:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=F59 HARD_CUT S1→S2; zoom=1; speed=1; MAD=14.665/69.427; cmd=F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K22" s="69" t="str">
         <x:v>30fps; segment=F013-F058; start=433.333ms; end=1966.667ms; duration=46f; event=HOLD@NONE; hard_cut_in=-1; transition=NONE; transition_frames=0; speed=1; zoom=1; audio_anchor=NO_REQUIRED_EVENT; maintain source cadence until hard cut F59; 5F_exact=F010-F014:F10-11:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F12:MATCH_CUT_PRE_POST_TAKE+PRODUCT_A_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F055-F059:F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -34461,7 +35100,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S22" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T22" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34499,13 +35138,13 @@
         <x:v>3666.667</x:v>
       </x:c>
       <x:c r="H23" s="69" t="str">
-        <x:v>S2 남성 팔 스윕 세팅</x:v>
+        <x:v>S2 팔 스윕 세팅</x:v>
       </x:c>
       <x:c r="I23" s="69" t="str">
         <x:v>HOOK_SETUP_B</x:v>
       </x:c>
       <x:c r="J23" s="69" t="str">
-        <x:v>[ACTION] F59 하드컷으로 검은 상의 남성 착석 구도 진입. 오른팔/손을 얼굴 앞에서 스윕하며 다른 팔은 옆/전방에 둔다. | [FRAME] 30fps F059-F109 (51f); phase=SETUP_EMPTY; shot=S2_MAN_RED_DRINK | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=sunglasses/face center + forearm/wrist line + seated torso; pre/post crop anchor locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F059; hard_cut_in=59; transition=HARD_CUT_S1_TO_S2/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F59 1.967s; nearest_beat=1.765s Δ+202ms; nearest_onset=1.974s Δ-7ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F055-F059:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=F59 HARD_CUT S1→S2; zoom=1; speed=1; MAD=14.665/69.427; cmd=F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F060-F064:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.206/2.417; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F065-F069:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.247/1.874; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F070-F074:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.216/2.115; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F075-F079:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.186/1.818; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F080-F084:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.691/3.743; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F085-F089:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=2.063/4.081; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F090-F094:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=3.685/5.734; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F095-F099:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=4.282/8.748; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F100-F104:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=6.276/11.329; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F105-F109:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=검은 상의 남성이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=6.69/13.234; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
+        <x:v>[ACTION] F59 하드컷으로 착석 구도 진입. 오른팔/손을 얼굴 앞에서 스윕하며 다른 팔은 옆/전방에 둔다. | [FRAME] 30fps F059-F109 (51f); phase=SETUP_EMPTY; shot=S2_MAN_RED_DRINK | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=sunglasses/face center + forearm/wrist line + seated torso; pre/post crop anchor locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F059; hard_cut_in=59; transition=HARD_CUT_S1_TO_S2/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F59 1.967s; nearest_beat=1.765s Δ+202ms; nearest_onset=1.974s Δ-7ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F055-F059:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=F59 HARD_CUT S1→S2; zoom=1; speed=1; MAD=14.665/69.427; cmd=F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F060-F064:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.206/2.417; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F065-F069:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.247/1.874; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F070-F074:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.216/2.115; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F075-F079:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.186/1.818; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F080-F084:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=1.691/3.743; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F085-F089:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=2.063/4.081; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F090-F094:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=3.685/5.734; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F095-F099:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=4.282/8.748; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F100-F104:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=6.276/11.329; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F105-F109:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 오른팔/손을 얼굴 앞에서 스윕하며 왼팔을 옆으로 유지; event=NONE; zoom=1; speed=1; MAD=6.69/13.234; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K23" s="69" t="str">
         <x:v>30fps; segment=F059-F109; start=1966.667ms; end=3666.667ms; duration=51f; event=HARD_CUT_IN@F059; hard_cut_in=59; transition=HARD_CUT_S1_TO_S2; transition_frames=0; speed=1; zoom=1; audio_anchor=F59 1.967s; nearest_beat=1.765s Δ+202ms; nearest_onset=1.974s Δ-7ms; 5F_exact=F055-F059:F59:HARD_CUT_TO_S2; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -34532,7 +35171,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S23" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T23" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34603,7 +35242,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S24" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T24" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34674,7 +35313,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S25" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T25" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34745,7 +35384,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S26" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T26" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34789,7 +35428,7 @@
         <x:v>RESULT_HOLD_B</x:v>
       </x:c>
       <x:c r="J27" s="69" t="str">
-        <x:v>[ACTION] 붉은 음료를 든 상태로 1.23배 펀치인 구도를 유지하고 손·얼굴 중심 구도를 안정적으로 보여준다. | [FRAME] 30fps F113-F158 (46f); phase=PRODUCT_HOLD_PUNCHIN; shot=S2_MAN_RED_DRINK | [CAMERA] framing=MEDIUM_CLOSE_DIGITAL_PUNCHIN; motion=DIGITAL_PUNCH_IN_HELD; zoom=1.23@(0.50,0.43) main-layer estimated visual center | [SUBJECT] match_anchor=sunglasses/face center + forearm/wrist line + seated torso; pre/post crop anchor locked; state=PRODUCT_B_RED_DRINK_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until hard cut F159; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F110-F114:PUNCH_IN_PRE_REVEAL→REVEAL_ZOOM_BLUR→PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=F110 DIGITAL_PUNCH_IN scale≈1.23 | F111 RADIAL/ZOOM_BLUR | F112 PRODUCT_B_REVEAL; zoom=1.23; speed=1; MAD=29.142/49.473; cmd=F110:ZOOM=1.23; F111:EFFECT=RADIAL_ZOOM_BLUR; F112:MATCH_CUT_PRE_POST_TAKE+PRODUCT_B_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F115-F119:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=6.409/9.653; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F120-F124:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.28/11.069; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F125-F129:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=7.224/11.779; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F130-F134:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=8.28/13.695; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F135-F139:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.35/7.466; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F140-F144:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.54/9.389; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F145-F149:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=8.998/13.009; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F150-F154:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.603/10.963; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F155-F159:PRODUCT_HOLD_PUNCH_IN→SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=F159 HARD_CUT S2→S3; zoom=1.23; speed=1; MAD=19.784/71.002; cmd=F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 붉은 음료를 든 상태로 1.23배 펀치인 구도를 유지하고 손·얼굴 중심 구도를 안정적으로 보여준다. | [FRAME] 30fps F113-F158 (46f); phase=PRODUCT_HOLD_PUNCHIN; shot=S2_MAN_RED_DRINK | [CAMERA] framing=MEDIUM_CLOSE_DIGITAL_PUNCHIN; motion=DIGITAL_PUNCH_IN_HELD; zoom=1.23@(0.50,0.43) main-layer estimated visual center | [SUBJECT] match_anchor=sunglasses/face center + forearm/wrist line + seated torso; pre/post crop anchor locked; state=PRODUCT_B_RED_DRINK_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until hard cut F159; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F110-F114:PUNCH_IN_PRE_REVEAL→REVEAL_ZOOM_BLUR→PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=F110 DIGITAL_PUNCH_IN scale≈1.23 | F111 RADIAL/ZOOM_BLUR | F112 PRODUCT_B_REVEAL; zoom=1.23; speed=1; MAD=29.142/49.473; cmd=F110:ZOOM=1.23; F111:EFFECT=RADIAL_ZOOM_BLUR; F112:MATCH_CUT_PRE_POST_TAKE+PRODUCT_B_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F115-F119:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=6.409/9.653; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F120-F124:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.28/11.069; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F125-F129:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=7.224/11.779; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F130-F134:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=8.28/13.695; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F135-F139:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.35/7.466; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F140-F144:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.54/9.389; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F145-F149:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=8.998/13.009; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F150-F154:PRODUCT_HOLD_PUNCH_IN/MEDIUM_CLOSE_PUNCHIN; action=붉은 음료를 얼굴 앞에 들고 펀치인 구도를 유지; event=NONE; zoom=1.23; speed=1; MAD=5.603/10.963; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F155-F159:PRODUCT_HOLD_PUNCH_IN→SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=F159 HARD_CUT S2→S3; zoom=1.23; speed=1; MAD=19.784/71.002; cmd=F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K27" s="69" t="str">
         <x:v>30fps; segment=F113-F158; start=3766.667ms; end=5300ms; duration=46f; event=HOLD@NONE; hard_cut_in=-1; transition=NONE; transition_frames=0; speed=1; zoom=1.23; audio_anchor=NO_REQUIRED_EVENT; maintain cadence until hard cut F159; 5F_exact=F110-F114:F110:ZOOM=1.23; F111:EFFECT=RADIAL_ZOOM_BLUR; F112:MATCH_CUT_PRE_POST_TAKE+PRODUCT_B_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F155-F159:F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -34816,7 +35455,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S27" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T27" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34854,13 +35493,13 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="H28" s="69" t="str">
-        <x:v>S3 여성 손바닥 세팅</x:v>
+        <x:v>S3 손바닥 세팅</x:v>
       </x:c>
       <x:c r="I28" s="69" t="str">
         <x:v>HOOK_SETUP_C</x:v>
       </x:c>
       <x:c r="J28" s="69" t="str">
-        <x:v>[ACTION] F159 하드컷으로 여성 정면 구도 진입. 오른손 손가락 포즈를 고정하고 왼손 손바닥을 카메라 쪽으로 펼친다. | [FRAME] 30fps F159-F209 (51f); phase=SETUP_EMPTY; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F159; hard_cut_in=159; transition=HARD_CUT_S2_TO_S3/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F159 5.300s; nearest_beat=5.224s Δ+76ms; nearest_onset=5.642s Δ-342ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F155-F159:PRODUCT_HOLD_PUNCH_IN→SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=F159 HARD_CUT S2→S3; zoom=1.23; speed=1; MAD=19.784/71.002; cmd=F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F160-F164:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.079/4.478; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F165-F169:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.068/4.288; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F170-F174:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.047/4.347; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F175-F179:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.942/3.899; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F180-F184:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.689/4.055; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F185-F189:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.934/3.817; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F190-F194:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=3.047/7.97; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F195-F199:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=3.057/6.204; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F200-F204:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.878/4.114; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F205-F209:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=여성이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=5.46/21.06; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
+        <x:v>[ACTION] F159 하드컷으로 정면 구도 진입. 오른손 손가락 포즈를 고정하고 왼손 손바닥을 카메라 쪽으로 펼친다. | [FRAME] 30fps F159-F209 (51f); phase=SETUP_EMPTY; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F159; hard_cut_in=159; transition=HARD_CUT_S2_TO_S3/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F159 5.300s; nearest_beat=5.224s Δ+76ms; nearest_onset=5.642s Δ-342ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F155-F159:PRODUCT_HOLD_PUNCH_IN→SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=F159 HARD_CUT S2→S3; zoom=1.23; speed=1; MAD=19.784/71.002; cmd=F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F160-F164:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.079/4.478; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F165-F169:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.068/4.288; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F170-F174:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=2.047/4.347; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F175-F179:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.942/3.899; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F180-F184:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.689/4.055; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F185-F189:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.934/3.817; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F190-F194:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=3.047/7.97; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F195-F199:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=3.057/6.204; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F200-F204:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=1.878/4.114; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F205-F209:SETUP_EMPTY/MEDIUM_PORTRAIT_FRONT; action=인물이 오른손 손가락 포즈 + 왼손 손바닥을 전경에 펼침; event=NONE; zoom=1; speed=1; MAD=5.46/21.06; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K28" s="69" t="str">
         <x:v>30fps; segment=F159-F209; start=5300ms; end=7000ms; duration=51f; event=HARD_CUT_IN@F159; hard_cut_in=159; transition=HARD_CUT_S2_TO_S3; transition_frames=0; speed=1; zoom=1; audio_anchor=F159 5.300s; nearest_beat=5.224s Δ+76ms; nearest_onset=5.642s Δ-342ms; 5F_exact=F155-F159:F159:HARD_CUT_TO_S3; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -34887,7 +35526,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S28" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T28" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34931,7 +35570,7 @@
         <x:v>TRANSITION_C</x:v>
       </x:c>
       <x:c r="J29" s="69" t="str">
-        <x:v>[ACTION] 메인 영상만 수직 방향 전 프레임 블러로 2프레임 가리고, 상단 PIP는 선명하게 유지한다. | [FRAME] 30fps F210-F211 (2f); phase=REVEAL_BLUR; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=EMPTY→PRODUCT_C_PENDING | [EDIT] type=MOTION_BLUR@F210; hard_cut_in=-1; transition=FULL_FRAME_VERTICAL_MOTION_BLUR_ON_MAIN/2f; blur=F210-211 vertical full-frame motion blur; instant clear F212; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 메인 영상만 수직 방향 전 프레임 블러로 2프레임 가리고, 상단 PIP는 선명하게 유지한다. | [FRAME] 30fps F210-F211 (2f); phase=REVEAL_BLUR; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=EMPTY→PRODUCT_C_PENDING | [EDIT] type=MOTION_BLUR@F210; hard_cut_in=-1; transition=FULL_FRAME_VERTICAL_MOTION_BLUR_ON_MAIN/2f; blur=F210-211 vertical full-frame motion blur; instant clear F212; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K29" s="69" t="str">
         <x:v>30fps; segment=F210-F211; start=7000ms; end=7066.667ms; duration=2f; event=MOTION_BLUR@F210; hard_cut_in=-1; transition=FULL_FRAME_VERTICAL_MOTION_BLUR_ON_MAIN; transition_frames=2; speed=1; zoom=1; audio_anchor=F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; 5F_exact=F210-F214:F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -34958,7 +35597,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S29" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T29" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -34996,13 +35635,13 @@
         <x:v>7100</x:v>
       </x:c>
       <x:c r="H30" s="69" t="str">
-        <x:v>S3 케이크 정확 등장 프레임</x:v>
+        <x:v>S3 디저트 정확 등장 프레임</x:v>
       </x:c>
       <x:c r="I30" s="69" t="str">
         <x:v>REVEAL_C</x:v>
       </x:c>
       <x:c r="J30" s="69" t="str">
-        <x:v>[ACTION] 동일 구도의 상품 있음 후테이크로 매치컷해 케이크 접시를 화면 하단/전경에 즉시 등장시킨다. | [FRAME] 30fps F212-F212 (1f); phase=PRODUCT_REVEAL; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=PRODUCT_C_CAKE_VISIBLE | [EDIT] type=MATCH_CUT_REVEAL@F212; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE/0f; blur=NONE; blur clears on reveal; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC | [SHAKE] OPTIONAL_REUSABLE_SHAKE(trigger=semantic impact/reveal/beat accent only; default=OFF; duration=3-5f; translate_x/y=±1.5~2.5% frame; rotate=±0.5~0.8deg; scale=1.02; alternate direction then damp to 0; never continuous; disable if readability/stability degrades)</x:v>
+        <x:v>[ACTION] 동일 구도의 상품 있음 후테이크로 매치컷해 디저트 접시를 화면 하단/전경에 즉시 등장시킨다. | [FRAME] 30fps F212-F212 (1f); phase=PRODUCT_REVEAL; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=PRODUCT_C_CAKE_VISIBLE | [EDIT] type=MATCH_CUT_REVEAL@F212; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE/0f; blur=NONE; blur clears on reveal; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC | [SHAKE] OPTIONAL_REUSABLE_SHAKE(trigger=semantic impact/reveal/beat accent only; default=OFF; duration=3-5f; translate_x/y=±1.5~2.5% frame; rotate=±0.5~0.8deg; scale=1.02; alternate direction then damp to 0; never continuous; disable if readability/stability degrades)</x:v>
       </x:c>
       <x:c r="K30" s="69" t="str">
         <x:v>30fps; segment=F212-F212; start=7066.667ms; end=7100ms; duration=1f; event=MATCH_CUT_REVEAL@F212; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE; transition_frames=0; speed=1; zoom=1; audio_anchor=F212 7.067s; nearest_beat=6.873s Δ+194ms; nearest_onset=7.082s Δ-15ms; 5F_exact=F210-F214:F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35029,7 +35668,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S30" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T30" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -35067,13 +35706,13 @@
         <x:v>8733.333</x:v>
       </x:c>
       <x:c r="H31" s="69" t="str">
-        <x:v>S3 케이크 결과 홀드</x:v>
+        <x:v>S3 디저트 결과 홀드</x:v>
       </x:c>
       <x:c r="I31" s="69" t="str">
         <x:v>RESULT_HOLD_C</x:v>
       </x:c>
       <x:c r="J31" s="69" t="str">
-        <x:v>[ACTION] 케이크 접시를 전경에 든 상태로 오른손 포즈·얼굴·카메라 프레이밍을 안정적으로 유지한다. | [FRAME] 30fps F213-F261 (49f); phase=PRODUCT_HOLD; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=PRODUCT_C_CAKE_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until hard cut F262; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F215-F219:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=5.596/8.99; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F220-F224:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=4.285/8.324; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F225-F229:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.499/8.36; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F230-F234:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=4.467/6.866; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F235-F239:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.064/4.057; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F240-F244:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.009/5.206; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F245-F249:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.168/4.929; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F250-F254:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.592/7.268; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F255-F259:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=케이크 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.479/2.88; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F260-F264:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=F262 HARD_CUT S3→S4; zoom=1; speed=1; MAD=12.854/62.473; cmd=F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 디저트 접시를 전경에 든 상태로 오른손 포즈·얼굴·카메라 프레이밍을 안정적으로 유지한다. | [FRAME] 30fps F213-F261 (49f); phase=PRODUCT_HOLD; shot=S3_WOMAN_CAKE | [CAMERA] framing=MEDIUM_PORTRAIT_FRONT; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=face/head center + right-hand finger gesture + left open-palm/wrist; camera locked; state=PRODUCT_C_CAKE_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until hard cut F262; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F210-F214:REVEAL_BLUR→PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=F210-211 FULL_FRAME_VERTICAL_MOTION_BLUR | F212 PRODUCT_C_REVEAL; zoom=1; speed=1; MAD=12.827/33.229; cmd=F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F215-F219:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=5.596/8.99; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F220-F224:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=4.285/8.324; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F225-F229:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.499/8.36; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F230-F234:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=4.467/6.866; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F235-F239:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.064/4.057; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F240-F244:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.009/5.206; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F245-F249:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=3.168/4.929; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F250-F254:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=2.592/7.268; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F255-F259:PRODUCT_HOLD/MEDIUM_PORTRAIT_FRONT; action=디저트 접시를 전경에 들고 오른손 포즈 유지; event=NONE; zoom=1; speed=1; MAD=1.479/2.88; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F260-F264:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=F262 HARD_CUT S3→S4; zoom=1; speed=1; MAD=12.854/62.473; cmd=F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K31" s="69" t="str">
         <x:v>30fps; segment=F213-F261; start=7100ms; end=8733.333ms; duration=49f; event=HOLD@NONE; hard_cut_in=-1; transition=NONE; transition_frames=0; speed=1; zoom=1; audio_anchor=NO_REQUIRED_EVENT; maintain cadence until hard cut F262; 5F_exact=F210-F214:F210-211:EFFECT=FULL_FRAME_VERTICAL_MOTION_BLUR; F212:MATCH_CUT_PRE_POST_TAKE+PRODUCT_C_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F260-F264:F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35100,7 +35739,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S31" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T31" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -35138,13 +35777,13 @@
         <x:v>10300</x:v>
       </x:c>
       <x:c r="H32" s="69" t="str">
-        <x:v>S4 남성 양손 제스처 세팅</x:v>
+        <x:v>S4 양손 제스처 세팅</x:v>
       </x:c>
       <x:c r="I32" s="69" t="str">
         <x:v>HOOK_SETUP_D</x:v>
       </x:c>
       <x:c r="J32" s="69" t="str">
-        <x:v>[ACTION] F262 하드컷으로 남성 착석 구도 진입. 두 손을 겹치거나 모아 카메라 전방으로 밀며 공개 동작을 준비한다. | [FRAME] 30fps F262-F308 (47f); phase=SETUP_EMPTY; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F262; hard_cut_in=262; transition=HARD_CUT_S3_TO_S4/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F262 8.733s; nearest_beat=8.545s Δ+188ms; nearest_onset=8.638s Δ+95ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F260-F264:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=F262 HARD_CUT S3→S4; zoom=1; speed=1; MAD=12.854/62.473; cmd=F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F265-F269:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=0.455/0.887; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F270-F274:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=0.947/1.503; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F275-F279:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=1.578/3.511; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F280-F284:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=2.576/4.436; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F285-F289:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=3.712/5.152; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F290-F294:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=3.29/8.329; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F295-F299:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=6.352/9.039; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F300-F304:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=남성이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=4.569/9.056; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F305-F309:SETUP_EMPTY→REVEAL_PROGRESSIVE_BLUR/MEDIUM_WIDE_SEATED; action=손이 펴지는 순간 진행성 블러로 전환; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR; zoom=1; speed=1; MAD=7.43/21.505; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] F262 하드컷으로 착석 구도 진입. 두 손을 겹치거나 모아 카메라 전방으로 밀며 공개 동작을 준비한다. | [FRAME] 30fps F262-F308 (47f); phase=SETUP_EMPTY; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=EMPTY_OR_NOT_YET_VISIBLE | [EDIT] type=HARD_CUT_IN@F262; hard_cut_in=262; transition=HARD_CUT_S3_TO_S4/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F262 8.733s; nearest_beat=8.545s Δ+188ms; nearest_onset=8.638s Δ+95ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F260-F264:PRODUCT_HOLD→SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=F262 HARD_CUT S3→S4; zoom=1; speed=1; MAD=12.854/62.473; cmd=F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F265-F269:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=0.455/0.887; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F270-F274:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=0.947/1.503; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F275-F279:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=1.578/3.511; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F280-F284:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=2.576/4.436; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F285-F289:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=3.712/5.152; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F290-F294:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=3.29/8.329; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F295-F299:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=6.352/9.039; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F300-F304:SETUP_EMPTY/MEDIUM_WIDE_SEATED; action=인물이 두 손을 겹쳐/모아 전방으로 밀어내는 동작; event=NONE; zoom=1; speed=1; MAD=4.569/9.056; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F305-F309:SETUP_EMPTY→REVEAL_PROGRESSIVE_BLUR/MEDIUM_WIDE_SEATED; action=손이 펴지는 순간 진행성 블러로 전환; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR; zoom=1; speed=1; MAD=7.43/21.505; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K32" s="69" t="str">
         <x:v>30fps; segment=F262-F308; start=8733.333ms; end=10300ms; duration=47f; event=HARD_CUT_IN@F262; hard_cut_in=262; transition=HARD_CUT_S3_TO_S4; transition_frames=0; speed=1; zoom=1; audio_anchor=F262 8.733s; nearest_beat=8.545s Δ+188ms; nearest_onset=8.638s Δ+95ms; 5F_exact=F260-F264:F262:HARD_CUT_TO_S4; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F305-F309:F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35171,7 +35810,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S32" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T32" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -35215,7 +35854,7 @@
         <x:v>TRANSITION_D</x:v>
       </x:c>
       <x:c r="J33" s="69" t="str">
-        <x:v>[ACTION] F309에서 블러를 시작하고 F310-311에서 강도를 높여 손이 펼쳐지는 순간과 상품 교체를 가린다. PIP는 영향받지 않는다. | [FRAME] 30fps F309-F311 (3f); phase=PROGRESSIVE_REVEAL_BLUR; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=EMPTY→PRODUCT_D_PENDING | [EDIT] type=PROGRESSIVE_MOTION_BLUR@F309; hard_cut_in=-1; transition=PROGRESSIVE_FULL_FRAME_BLUR_ON_MAIN/3f; blur=F309 mild blur → F310-311 strong full-frame blur; clear at F312; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F309 10.300s nearest_onset=10.310s Δ-10ms; F312 10.400s nearest_onset=10.310s Δ+90ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F305-F309:SETUP_EMPTY→REVEAL_PROGRESSIVE_BLUR/MEDIUM_WIDE_SEATED; action=손이 펴지는 순간 진행성 블러로 전환; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR; zoom=1; speed=1; MAD=7.43/21.505; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] F309에서 블러를 시작하고 F310-311에서 강도를 높여 손이 펼쳐지는 순간과 상품 교체를 가린다. PIP는 영향받지 않는다. | [FRAME] 30fps F309-F311 (3f); phase=PROGRESSIVE_REVEAL_BLUR; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=EMPTY→PRODUCT_D_PENDING | [EDIT] type=PROGRESSIVE_MOTION_BLUR@F309; hard_cut_in=-1; transition=PROGRESSIVE_FULL_FRAME_BLUR_ON_MAIN/3f; blur=F309 mild blur → F310-311 strong full-frame blur; clear at F312; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F309 10.300s nearest_onset=10.310s Δ-10ms; F312 10.400s nearest_onset=10.310s Δ+90ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F305-F309:SETUP_EMPTY→REVEAL_PROGRESSIVE_BLUR/MEDIUM_WIDE_SEATED; action=손이 펴지는 순간 진행성 블러로 전환; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR; zoom=1; speed=1; MAD=7.43/21.505; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K33" s="69" t="str">
         <x:v>30fps; segment=F309-F311; start=10300ms; end=10400ms; duration=3f; event=PROGRESSIVE_MOTION_BLUR@F309; hard_cut_in=-1; transition=PROGRESSIVE_FULL_FRAME_BLUR_ON_MAIN; transition_frames=3; speed=1; zoom=1; audio_anchor=F309 10.300s nearest_onset=10.310s Δ-10ms; F312 10.400s nearest_onset=10.310s Δ+90ms; 5F_exact=F305-F309:F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F310-F314:F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35242,7 +35881,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S33" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T33" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -35280,13 +35919,13 @@
         <x:v>10433.333</x:v>
       </x:c>
       <x:c r="H34" s="69" t="str">
-        <x:v>S4 빵/페이스트리 정확 등장 프레임</x:v>
+        <x:v>S4 베이커리 메뉴 정확 등장 프레임</x:v>
       </x:c>
       <x:c r="I34" s="69" t="str">
         <x:v>REVEAL_D</x:v>
       </x:c>
       <x:c r="J34" s="69" t="str">
-        <x:v>[ACTION] 동일 구도의 후테이크로 매치컷해 빵/페이스트리 접시를 손 아래 전경에 즉시 등장시킨다. | [FRAME] 30fps F312-F312 (1f); phase=PRODUCT_REVEAL; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=PRODUCT_D_PASTRY_VISIBLE | [EDIT] type=MATCH_CUT_REVEAL@F312; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE/0f; blur=NONE; progressive blur clears on reveal; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F312 10.400s; nearest_beat=10.194s Δ+206ms; nearest_onset=10.310s Δ+90ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC | [SHAKE] OPTIONAL_REUSABLE_SHAKE(trigger=semantic impact/reveal/beat accent only; default=OFF; duration=3-5f; translate_x/y=±1.5~2.5% frame; rotate=±0.5~0.8deg; scale=1.02; alternate direction then damp to 0; never continuous; disable if readability/stability degrades)</x:v>
+        <x:v>[ACTION] 동일 구도의 후테이크로 매치컷해 베이커리 메뉴 접시를 손 아래 전경에 즉시 등장시킨다. | [FRAME] 30fps F312-F312 (1f); phase=PRODUCT_REVEAL; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=PRODUCT_D_PASTRY_VISIBLE | [EDIT] type=MATCH_CUT_REVEAL@F312; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE/0f; blur=NONE; progressive blur clears on reveal; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] F312 10.400s; nearest_beat=10.194s Δ+206ms; nearest_onset=10.310s Δ+90ms; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC | [SHAKE] OPTIONAL_REUSABLE_SHAKE(trigger=semantic impact/reveal/beat accent only; default=OFF; duration=3-5f; translate_x/y=±1.5~2.5% frame; rotate=±0.5~0.8deg; scale=1.02; alternate direction then damp to 0; never continuous; disable if readability/stability degrades)</x:v>
       </x:c>
       <x:c r="K34" s="69" t="str">
         <x:v>30fps; segment=F312-F312; start=10400ms; end=10433.333ms; duration=1f; event=MATCH_CUT_REVEAL@F312; hard_cut_in=-1; transition=MATCH_CUT_PRE_POST_TAKE; transition_frames=0; speed=1; zoom=1; audio_anchor=F312 10.400s; nearest_beat=10.194s Δ+206ms; nearest_onset=10.310s Δ+90ms; 5F_exact=F310-F314:F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35313,7 +35952,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S34" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T34" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -35351,13 +35990,13 @@
         <x:v>12066.667</x:v>
       </x:c>
       <x:c r="H35" s="69" t="str">
-        <x:v>S4 빵/페이스트리 결과 홀드</x:v>
+        <x:v>S4 베이커리 메뉴 결과 홀드</x:v>
       </x:c>
       <x:c r="I35" s="69" t="str">
         <x:v>RESULT_HOLD_D</x:v>
       </x:c>
       <x:c r="J35" s="69" t="str">
-        <x:v>[ACTION] 접시와 상품을 화면 하단/전경에 유지하면서 펼친 손과 얼굴 구도를 안정적으로 보여준다. | [FRAME] 30fps F313-F361 (49f); phase=PRODUCT_HOLD; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=PRODUCT_D_PASTRY_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until loop hard cut F362; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F315-F319:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=6.234/8.559; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F320-F324:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=5.232/9.415; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F325-F329:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.612/9.288; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F330-F334:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.779/6.466; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F335-F339:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.551/5.853; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F340-F344:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.858/5.812; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F345-F349:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.174/5.257; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F350-F354:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.829/5.293; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F355-F359:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=빵/페이스트리 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.927/5.128; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F360-F364:PRODUCT_HOLD→LOOP_RESET_SETUP/MEDIUM_PORTRAIT_FRONT_LOOP; action=첫 장면 빈손 포즈로 루프 재시작; event=F362 HARD_CUT/LOOP_RESET S4→S1; zoom=1; speed=1; MAD=14.489/65.692; cmd=F362:HARD_CUT_LOOP_RESET_TO_S1; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
+        <x:v>[ACTION] 접시와 상품을 화면 하단/전경에 유지하면서 펼친 손과 얼굴 구도를 안정적으로 보여준다. | [FRAME] 30fps F313-F361 (49f); phase=PRODUCT_HOLD; shot=S4_MAN_PASTRY | [CAMERA] framing=MEDIUM_WIDE_SEATED; motion=STATIC_FIXED_PHONE; zoom=1@(0.50,0.50) canvas center; no digital zoom | [SUBJECT] match_anchor=head center + both wrist/hand centerline + seated torso; camera locked; state=PRODUCT_D_PASTRY_VISIBLE | [EDIT] type=HOLD@NO_SINGLE_EVENT; hard_cut_in=-1; transition=NONE/0f; blur=NONE; scope=MAIN_VIDEO_ONLY_FOR_ZOOM_BLUR; PIP_EXCLUDED_FROM_MAIN_EFFECTS; layer=MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP | [PIP] bbox=(0.118,0.000,0.444,0.140); behavior=PERSISTENT; SCREEN_FIXED; OPAQUE; NO_BORDER; source-synced VIDEO_PIP; main-layer zoom/blur does not transform PIP | [AUDIO_COLOR] NO_REQUIRED_EVENT; maintain cadence until loop hard cut F362; KEEP_SOURCE_COLOR; no per-cut LUT/grade; maintain exposure/WB continuity | [5F] F310-F314:REVEAL_PROGRESSIVE_BLUR→PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=F309-311 PROGRESSIVE_FULL_FRAME_BLUR | F312 PRODUCT_D_REVEAL; zoom=1; speed=1; MAD=16.702/29.721; cmd=F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F315-F319:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=6.234/8.559; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F320-F324:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=5.232/9.415; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F325-F329:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.612/9.288; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F330-F334:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.779/6.466; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F335-F339:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.551/5.853; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F340-F344:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=3.858/5.812; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F345-F349:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.174/5.257; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F350-F354:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.829/5.293; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F355-F359:PRODUCT_HOLD/MEDIUM_WIDE_SEATED; action=베이커리 메뉴 접시를 전경에 들고 손을 펼친 자세 유지; event=NONE; zoom=1; speed=1; MAD=2.927/5.128; cmd=KEEP_SHOT; speed=1.0; cut=NONE; transition=NONE; text_overlay=NONE; color=KEEP_SOURCE; PIP=SYNC || F360-F364:PRODUCT_HOLD→LOOP_RESET_SETUP/MEDIUM_PORTRAIT_FRONT_LOOP; action=첫 장면 빈손 포즈로 루프 재시작; event=F362 HARD_CUT/LOOP_RESET S4→S1; zoom=1; speed=1; MAD=14.489/65.692; cmd=F362:HARD_CUT_LOOP_RESET_TO_S1; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
       </x:c>
       <x:c r="K35" s="69" t="str">
         <x:v>30fps; segment=F313-F361; start=10433.333ms; end=12066.667ms; duration=49f; event=HOLD@NONE; hard_cut_in=-1; transition=NONE; transition_frames=0; speed=1; zoom=1; audio_anchor=NO_REQUIRED_EVENT; maintain cadence until loop hard cut F362; 5F_exact=F310-F314:F309-311:EFFECT=PROGRESSIVE_FULL_FRAME_BLUR; F312:MATCH_CUT_PRE_POST_TAKE+PRODUCT_D_VISIBLE; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC || F360-F364:F362:HARD_CUT_LOOP_RESET_TO_S1; speed=1.0; dissolve=0; fade=0; text_overlay=NONE; PIP=SYNC</x:v>
@@ -35384,7 +36023,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S35" s="69" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T35" s="69" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$847:$G$870</x:v>
@@ -37033,379 +37672,1043 @@
       </x:c>
     </x:row>
     <x:row r="59" ht="78" customHeight="1">
-      <x:c r="A59"/>
-      <x:c r="B59"/>
-      <x:c r="C59"/>
-      <x:c r="D59"/>
-      <x:c r="E59"/>
-      <x:c r="F59"/>
-      <x:c r="G59"/>
-      <x:c r="H59"/>
-      <x:c r="I59"/>
-      <x:c r="J59"/>
-      <x:c r="K59"/>
+      <x:c r="A59" t="str">
+        <x:v>gts_jujutsu_v5_01</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E59" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G59" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>인물 A 빈손 포즈 훅</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>HOOK_SETUP</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>POSE_HOLD_END_ANCHORED; S02와 신체·손·배경 특징점을 정렬하고 1500ms SFX 직전에 종료</x:v>
+      </x:c>
       <x:c r="L59"/>
-      <x:c r="M59"/>
-      <x:c r="N59"/>
-      <x:c r="O59"/>
-      <x:c r="P59"/>
-      <x:c r="Q59"/>
-      <x:c r="R59"/>
-      <x:c r="S59"/>
-      <x:c r="T59"/>
-      <x:c r="U59"/>
-      <x:c r="V59"/>
-      <x:c r="W59"/>
+      <x:c r="M59" t="str">
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N59" t="str">
+        <x:v>첫 공개 아이템은 실제 대표 메뉴/상품으로 정하고 동일 인물·구도·배경의 S02와 한 쌍으로 촬영</x:v>
+      </x:c>
+      <x:c r="O59" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P59" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q59" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R59" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S59" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T59" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U59" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V59" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W59" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="78" customHeight="1">
-      <x:c r="A60"/>
-      <x:c r="B60"/>
-      <x:c r="C60"/>
-      <x:c r="D60"/>
-      <x:c r="E60"/>
-      <x:c r="F60"/>
-      <x:c r="G60"/>
-      <x:c r="H60"/>
-      <x:c r="I60"/>
-      <x:c r="J60"/>
-      <x:c r="K60"/>
+      <x:c r="A60" t="str">
+        <x:v>gts_jujutsu_v5_02</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D60" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F60" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="G60" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="H60" t="str">
+        <x:v>인물 A 첫 아이템 공개</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>MAGIC_REVEAL</x:v>
+      </x:c>
+      <x:c r="J60" t="str">
+        <x:v>S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
+      </x:c>
+      <x:c r="K60" t="str">
+        <x:v>1500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 디졸브·페이드 금지</x:v>
+      </x:c>
       <x:c r="L60"/>
-      <x:c r="M60"/>
-      <x:c r="N60"/>
-      <x:c r="O60"/>
-      <x:c r="P60"/>
-      <x:c r="Q60"/>
-      <x:c r="R60"/>
-      <x:c r="S60"/>
-      <x:c r="T60"/>
-      <x:c r="U60"/>
-      <x:c r="V60"/>
-      <x:c r="W60"/>
+      <x:c r="M60" t="str">
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N60" t="str">
+        <x:v>S01 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 선택하고 실제 음료/상품만 노출</x:v>
+      </x:c>
+      <x:c r="O60" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P60" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q60" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R60" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S60" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T60" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U60" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V60" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W60" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="78" customHeight="1">
-      <x:c r="A61"/>
-      <x:c r="B61"/>
-      <x:c r="C61"/>
-      <x:c r="D61"/>
-      <x:c r="E61"/>
-      <x:c r="F61"/>
-      <x:c r="G61"/>
-      <x:c r="H61"/>
-      <x:c r="I61"/>
-      <x:c r="J61"/>
-      <x:c r="K61"/>
+      <x:c r="A61" t="str">
+        <x:v>gts_jujutsu_v5_03</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E61" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F61" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="G61" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>인물 B 빈손 포즈 셋업</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>SETUP</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
+      </x:c>
+      <x:c r="K61" t="str">
+        <x:v>POSE_HOLD_END_ANCHORED; S04와 포즈·배경을 정렬하고 5000ms SFX 직전에 종료</x:v>
+      </x:c>
       <x:c r="L61"/>
-      <x:c r="M61"/>
-      <x:c r="N61"/>
-      <x:c r="O61"/>
-      <x:c r="P61"/>
-      <x:c r="Q61"/>
-      <x:c r="R61"/>
-      <x:c r="S61"/>
-      <x:c r="T61"/>
-      <x:c r="U61"/>
-      <x:c r="V61"/>
-      <x:c r="W61"/>
+      <x:c r="M61" t="str">
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N61" t="str">
+        <x:v>두 번째 출연자와 보조 메뉴를 사용하되 S04와 동일 인물·의상·배경 유지</x:v>
+      </x:c>
+      <x:c r="O61" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P61" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q61" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R61" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S61" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T61" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U61" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V61" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W61" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="78" customHeight="1">
-      <x:c r="A62"/>
-      <x:c r="B62"/>
-      <x:c r="C62"/>
-      <x:c r="D62"/>
-      <x:c r="E62"/>
-      <x:c r="F62"/>
-      <x:c r="G62"/>
-      <x:c r="H62"/>
-      <x:c r="I62"/>
-      <x:c r="J62"/>
-      <x:c r="K62"/>
+      <x:c r="A62" t="str">
+        <x:v>gts_jujutsu_v5_04</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F62" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G62" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>인물 B 두 번째 아이템 공개</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>MAGIC_REVEAL</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
+      </x:c>
+      <x:c r="K62" t="str">
+        <x:v>5000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 7000ms HARD_CUT</x:v>
+      </x:c>
       <x:c r="L62"/>
-      <x:c r="M62"/>
-      <x:c r="N62"/>
-      <x:c r="O62"/>
-      <x:c r="P62"/>
-      <x:c r="Q62"/>
-      <x:c r="R62"/>
-      <x:c r="S62"/>
-      <x:c r="T62"/>
-      <x:c r="U62"/>
-      <x:c r="V62"/>
-      <x:c r="W62"/>
+      <x:c r="M62" t="str">
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N62" t="str">
+        <x:v>S03 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 시작점으로 선택</x:v>
+      </x:c>
+      <x:c r="O62" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P62" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q62" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R62" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S62" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T62" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U62" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V62" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W62" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="78" customHeight="1">
-      <x:c r="A63"/>
-      <x:c r="B63"/>
-      <x:c r="C63"/>
-      <x:c r="D63"/>
-      <x:c r="E63"/>
-      <x:c r="F63"/>
-      <x:c r="G63"/>
-      <x:c r="H63"/>
-      <x:c r="I63"/>
-      <x:c r="J63"/>
-      <x:c r="K63"/>
+      <x:c r="A63" t="str">
+        <x:v>gts_jujutsu_v5_05</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F63" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="G63" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>인물 A 새 빈손 포즈 셋업</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>SETUP</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>인물 A가 다시 등장해 제품 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="K63" t="str">
+        <x:v>POSE_HOLD_END_ANCHORED; S06과 정렬하고 8500ms SFX 직전에 종료</x:v>
+      </x:c>
       <x:c r="L63"/>
-      <x:c r="M63"/>
-      <x:c r="N63"/>
-      <x:c r="O63"/>
-      <x:c r="P63"/>
-      <x:c r="Q63"/>
-      <x:c r="R63"/>
-      <x:c r="S63"/>
-      <x:c r="T63"/>
-      <x:c r="U63"/>
-      <x:c r="V63"/>
-      <x:c r="W63"/>
+      <x:c r="M63" t="str">
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N63" t="str">
+        <x:v>세 번째 실제 메뉴의 형태를 고려해 손과 테이블이 가리지 않는 포즈 선택</x:v>
+      </x:c>
+      <x:c r="O63" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P63" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q63" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R63" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S63" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T63" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U63" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V63" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W63" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="78" customHeight="1">
-      <x:c r="A64"/>
-      <x:c r="B64"/>
-      <x:c r="C64"/>
-      <x:c r="D64"/>
-      <x:c r="E64"/>
-      <x:c r="F64"/>
-      <x:c r="G64"/>
-      <x:c r="H64"/>
-      <x:c r="I64"/>
-      <x:c r="J64"/>
-      <x:c r="K64"/>
+      <x:c r="A64" t="str">
+        <x:v>gts_jujutsu_v5_06</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E64" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F64" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>인물 A 제품 공개</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>MAGIC_REVEAL</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>S05와 동일 포즈·구도에서 인물 A가 실제 제품을 든 상태로 시작</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>8500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 아이템 전체가 보이는 결과 홀드</x:v>
+      </x:c>
       <x:c r="L64"/>
-      <x:c r="M64"/>
-      <x:c r="N64"/>
-      <x:c r="O64"/>
-      <x:c r="P64"/>
-      <x:c r="Q64"/>
-      <x:c r="R64"/>
-      <x:c r="S64"/>
-      <x:c r="T64"/>
-      <x:c r="U64"/>
-      <x:c r="V64"/>
-      <x:c r="W64"/>
+      <x:c r="M64" t="str">
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N64" t="str">
+        <x:v>실제 촬영된 제품/대표 상품으로 치환하고 S05 경계의 포즈 일치 우선</x:v>
+      </x:c>
+      <x:c r="O64" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P64" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q64" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R64" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S64" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T64" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U64" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V64" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W64" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="78" customHeight="1">
-      <x:c r="A65"/>
-      <x:c r="B65"/>
-      <x:c r="C65"/>
-      <x:c r="D65"/>
-      <x:c r="E65"/>
-      <x:c r="F65"/>
-      <x:c r="G65"/>
-      <x:c r="H65"/>
-      <x:c r="I65"/>
-      <x:c r="J65"/>
-      <x:c r="K65"/>
+      <x:c r="A65" t="str">
+        <x:v>gts_jujutsu_v5_07</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D65" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E65" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F65" t="n">
+        <x:v>10500</x:v>
+      </x:c>
+      <x:c r="G65" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="H65" t="str">
+        <x:v>인물 B 마지막 빈손 포즈 셋업</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>SETUP</x:v>
+      </x:c>
+      <x:c r="J65" t="str">
+        <x:v>인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
+      </x:c>
+      <x:c r="K65" t="str">
+        <x:v>POSE_HOLD_END_ANCHORED; S08과 정렬하고 12000ms SFX 직전에 종료</x:v>
+      </x:c>
       <x:c r="L65"/>
-      <x:c r="M65"/>
-      <x:c r="N65"/>
-      <x:c r="O65"/>
-      <x:c r="P65"/>
-      <x:c r="Q65"/>
-      <x:c r="R65"/>
-      <x:c r="S65"/>
-      <x:c r="T65"/>
-      <x:c r="U65"/>
-      <x:c r="V65"/>
-      <x:c r="W65"/>
+      <x:c r="M65" t="str">
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N65" t="str">
+        <x:v>네 번째 실제 메뉴를 놓을 위치를 비워 두고 S08과 동일 인물·구도 유지</x:v>
+      </x:c>
+      <x:c r="O65" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P65" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q65" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R65" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S65" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T65" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U65" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V65" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W65" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="78" customHeight="1">
-      <x:c r="A66"/>
-      <x:c r="B66"/>
-      <x:c r="C66"/>
-      <x:c r="D66"/>
-      <x:c r="E66"/>
-      <x:c r="F66"/>
-      <x:c r="G66"/>
-      <x:c r="H66"/>
-      <x:c r="I66"/>
-      <x:c r="J66"/>
-      <x:c r="K66"/>
+      <x:c r="A66" t="str">
+        <x:v>gts_jujutsu_v5_08</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="D66" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E66" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F66" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="G66" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>인물 B 제품 최종 공개</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>MAGIC_REVEAL</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>S07과 동일 포즈·구도에서 실제 제품이 나타난 상태로 전환해 아웃트로 유지</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>12000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 14000ms까지 결과 홀드</x:v>
+      </x:c>
       <x:c r="L66"/>
-      <x:c r="M66"/>
-      <x:c r="N66"/>
-      <x:c r="O66"/>
-      <x:c r="P66"/>
-      <x:c r="Q66"/>
-      <x:c r="R66"/>
-      <x:c r="S66"/>
-      <x:c r="T66"/>
-      <x:c r="U66"/>
-      <x:c r="V66"/>
-      <x:c r="W66"/>
+      <x:c r="M66" t="str">
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N66" t="str">
+        <x:v>실제 촬영된 제품/상품을 명확히 보여주고 추가 전환 없이 종료</x:v>
+      </x:c>
+      <x:c r="O66" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
+      <x:c r="P66" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q66" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R66" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S66" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T66" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+      </x:c>
+      <x:c r="U66" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V66" t="str">
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="W66" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="78" customHeight="1">
-      <x:c r="A67"/>
-      <x:c r="B67"/>
-      <x:c r="C67"/>
-      <x:c r="D67"/>
-      <x:c r="E67"/>
-      <x:c r="F67"/>
-      <x:c r="G67"/>
-      <x:c r="H67"/>
-      <x:c r="I67"/>
-      <x:c r="J67"/>
-      <x:c r="K67"/>
-      <x:c r="L67"/>
-      <x:c r="M67"/>
-      <x:c r="N67"/>
-      <x:c r="O67"/>
-      <x:c r="P67"/>
-      <x:c r="Q67"/>
-      <x:c r="R67"/>
-      <x:c r="S67"/>
-      <x:c r="T67"/>
-      <x:c r="U67"/>
-      <x:c r="V67"/>
-      <x:c r="W67"/>
+      <x:c r="A67" t="str">
+        <x:v>gts_donggeurio_v1_01</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E67" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G67" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>감성 타이틀 훅</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>HOOK</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>실측 0~1033ms; 안정 구간 중심 trim; speed 0.95~1.05; 1033ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L67" t="str">
+        <x:v>{{project.title}}</x:v>
+      </x:c>
+      <x:c r="M67" t="str">
+        <x:v>project.title,store.name</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>레퍼런스 상호·핸들은 복제하지 않고 검증된 프로젝트명/매장명으로 교체</x:v>
+      </x:c>
+      <x:c r="O67" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P67" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q67" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R67" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S67" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T67" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U67" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V67" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W67" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="78" customHeight="1">
-      <x:c r="A68"/>
-      <x:c r="B68"/>
-      <x:c r="C68"/>
-      <x:c r="D68"/>
-      <x:c r="E68"/>
-      <x:c r="F68"/>
-      <x:c r="G68"/>
-      <x:c r="H68"/>
-      <x:c r="I68"/>
-      <x:c r="J68"/>
-      <x:c r="K68"/>
-      <x:c r="L68"/>
-      <x:c r="M68"/>
-      <x:c r="N68"/>
-      <x:c r="O68"/>
-      <x:c r="P68"/>
-      <x:c r="Q68"/>
-      <x:c r="R68"/>
-      <x:c r="S68"/>
-      <x:c r="T68"/>
-      <x:c r="U68"/>
-      <x:c r="V68"/>
-      <x:c r="W68"/>
+      <x:c r="A68" t="str">
+        <x:v>gts_donggeurio_v1_02</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D68" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F68" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="G68" t="n">
+        <x:v>3767</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>메뉴 항공샷 공개</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>REVEAL</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>실측 1033~3767ms; 구성 최적 구간 trim; speed 0.9~1.1; 3767ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L68" t="str">
+        <x:v>{{store.location_or_context}}</x:v>
+      </x:c>
+      <x:c r="M68" t="str">
+        <x:v>store.location,store.context,promo.primary</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>실제 메뉴와 검증된 장소/맥락만 사용하고 숫자·혜택을 임의 생성하지 않음</x:v>
+      </x:c>
+      <x:c r="O68" t="str">
+        <x:v>caption,text_2d,transform</x:v>
+      </x:c>
+      <x:c r="P68" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q68" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R68" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S68" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T68" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U68" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V68" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W68" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="78" customHeight="1">
-      <x:c r="A69"/>
-      <x:c r="B69"/>
-      <x:c r="C69"/>
-      <x:c r="D69"/>
-      <x:c r="E69"/>
-      <x:c r="F69"/>
-      <x:c r="G69"/>
-      <x:c r="H69"/>
-      <x:c r="I69"/>
-      <x:c r="J69"/>
-      <x:c r="K69"/>
+      <x:c r="A69" t="str">
+        <x:v>gts_donggeurio_v1_03</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D69" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E69" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F69" t="n">
+        <x:v>3767</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>카페 공간 팬</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>AMBIENCE</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>실측 3767~4700ms; 모션 중심 trim; speed 0.9~1.35; 소스 팬 보존; 4700ms HARD_CUT</x:v>
+      </x:c>
       <x:c r="L69"/>
-      <x:c r="M69"/>
-      <x:c r="N69"/>
-      <x:c r="O69"/>
-      <x:c r="P69"/>
-      <x:c r="Q69"/>
-      <x:c r="R69"/>
-      <x:c r="S69"/>
-      <x:c r="T69"/>
-      <x:c r="U69"/>
-      <x:c r="V69"/>
-      <x:c r="W69"/>
+      <x:c r="M69" t="str">
+        <x:v>store.interior</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>실제 촬영된 공간 정보량이 높은 구간을 사용하고 긴 팬 전체를 강제 고배속하지 않음</x:v>
+      </x:c>
+      <x:c r="O69" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P69" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q69" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R69" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S69" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T69" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U69" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V69" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W69" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="78" customHeight="1">
-      <x:c r="A70"/>
-      <x:c r="B70"/>
-      <x:c r="C70"/>
-      <x:c r="D70"/>
-      <x:c r="E70"/>
-      <x:c r="F70"/>
-      <x:c r="G70"/>
-      <x:c r="H70"/>
-      <x:c r="I70"/>
-      <x:c r="J70"/>
-      <x:c r="K70"/>
+      <x:c r="A70" t="str">
+        <x:v>gts_donggeurio_v1_04</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D70" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E70" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F70" t="n">
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="G70" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>메뉴 인터랙션 클로즈업</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>ACTION</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>실측 4700~7000ms; ACTION_PEAK를 슬롯 58% 부근에 배치; speed 0.9~1.1; 7000ms HARD_CUT</x:v>
+      </x:c>
       <x:c r="L70"/>
-      <x:c r="M70"/>
-      <x:c r="N70"/>
-      <x:c r="O70"/>
-      <x:c r="P70"/>
-      <x:c r="Q70"/>
-      <x:c r="R70"/>
-      <x:c r="S70"/>
-      <x:c r="T70"/>
-      <x:c r="U70"/>
-      <x:c r="V70"/>
-      <x:c r="W70"/>
+      <x:c r="M70" t="str">
+        <x:v>promo.primary.action</x:v>
+      </x:c>
+      <x:c r="N70" t="str">
+        <x:v>실제 촬영된 섞기·집기·서빙 행동을 우선하며 없는 행동을 생성하지 않음</x:v>
+      </x:c>
+      <x:c r="O70" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P70" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q70" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R70" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S70" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T70" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U70" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V70" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W70" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="78" customHeight="1">
-      <x:c r="A71"/>
-      <x:c r="B71"/>
-      <x:c r="C71"/>
-      <x:c r="D71"/>
-      <x:c r="E71"/>
-      <x:c r="F71"/>
-      <x:c r="G71"/>
-      <x:c r="H71"/>
-      <x:c r="I71"/>
-      <x:c r="J71"/>
-      <x:c r="K71"/>
+      <x:c r="A71" t="str">
+        <x:v>gts_donggeurio_v1_05</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D71" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E71" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F71" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="G71" t="n">
+        <x:v>8333</x:v>
+      </x:c>
+      <x:c r="H71" t="str">
+        <x:v>음식 자르기 액션 하이라이트</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>ACTION_HIGHLIGHT</x:v>
+      </x:c>
+      <x:c r="J71" t="str">
+        <x:v>포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
+      </x:c>
+      <x:c r="K71" t="str">
+        <x:v>실측 7000~8333ms; ACTION_PEAK 중심 trim; speed 0.75~1.0, 0.8 선호; 8333ms HARD_CUT</x:v>
+      </x:c>
       <x:c r="L71"/>
-      <x:c r="M71"/>
-      <x:c r="N71"/>
-      <x:c r="O71"/>
-      <x:c r="P71"/>
-      <x:c r="Q71"/>
-      <x:c r="R71"/>
-      <x:c r="S71"/>
-      <x:c r="T71"/>
-      <x:c r="U71"/>
-      <x:c r="V71"/>
-      <x:c r="W71"/>
+      <x:c r="M71" t="str">
+        <x:v>promo.secondary.action</x:v>
+      </x:c>
+      <x:c r="N71" t="str">
+        <x:v>자르기 장면이 없으면 다른 실제 메뉴 액션으로 대체하고 0.9배 수준까지 완화</x:v>
+      </x:c>
+      <x:c r="O71" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P71" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q71" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R71" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S71" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T71" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U71" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V71" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W71" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="78" customHeight="1">
-      <x:c r="A72"/>
-      <x:c r="B72"/>
-      <x:c r="C72"/>
-      <x:c r="D72"/>
-      <x:c r="E72"/>
-      <x:c r="F72"/>
-      <x:c r="G72"/>
-      <x:c r="H72"/>
-      <x:c r="I72"/>
-      <x:c r="J72"/>
-      <x:c r="K72"/>
+      <x:c r="A72" t="str">
+        <x:v>gts_donggeurio_v1_06</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D72" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E72" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F72" t="n">
+        <x:v>8333</x:v>
+      </x:c>
+      <x:c r="G72" t="n">
+        <x:v>9633</x:v>
+      </x:c>
+      <x:c r="H72" t="str">
+        <x:v>매장 외관·위치 공개</x:v>
+      </x:c>
+      <x:c r="I72" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="J72" t="str">
+        <x:v>매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
+      </x:c>
+      <x:c r="K72" t="str">
+        <x:v>실측 8333~9633ms; 구성 중심 trim; speed 0.9~1.1; 실제 경계는 HARD_CUT 우선</x:v>
+      </x:c>
       <x:c r="L72"/>
-      <x:c r="M72"/>
-      <x:c r="N72"/>
-      <x:c r="O72"/>
-      <x:c r="P72"/>
-      <x:c r="Q72"/>
-      <x:c r="R72"/>
-      <x:c r="S72"/>
-      <x:c r="T72"/>
-      <x:c r="U72"/>
-      <x:c r="V72"/>
-      <x:c r="W72"/>
+      <x:c r="M72" t="str">
+        <x:v>store.name,store.location</x:v>
+      </x:c>
+      <x:c r="N72" t="str">
+        <x:v>검증된 매장 외관/위치만 사용하고 SLIDE_LEFT 느낌은 선택적 악센트로만 취급</x:v>
+      </x:c>
+      <x:c r="O72" t="str">
+        <x:v>caption,text_2d,transform</x:v>
+      </x:c>
+      <x:c r="P72" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q72" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R72" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S72" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T72" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U72" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V72" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W72" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="78" customHeight="1">
-      <x:c r="A73"/>
-      <x:c r="B73"/>
-      <x:c r="C73"/>
-      <x:c r="D73"/>
-      <x:c r="E73"/>
-      <x:c r="F73"/>
-      <x:c r="G73"/>
-      <x:c r="H73"/>
-      <x:c r="I73"/>
-      <x:c r="J73"/>
-      <x:c r="K73"/>
+      <x:c r="A73" t="str">
+        <x:v>gts_donggeurio_v1_07</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D73" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F73" t="n">
+        <x:v>9633</x:v>
+      </x:c>
+      <x:c r="G73" t="n">
+        <x:v>12067</x:v>
+      </x:c>
+      <x:c r="H73" t="str">
+        <x:v>최종 메뉴 액션 아웃트로</x:v>
+      </x:c>
+      <x:c r="I73" t="str">
+        <x:v>OUTRO</x:v>
+      </x:c>
+      <x:c r="J73" t="str">
+        <x:v>비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
+      </x:c>
+      <x:c r="K73" t="str">
+        <x:v>실측 9633~12067ms; ACTION_PEAK를 슬롯 48% 부근에 배치; speed 0.9~1.1; 정책값 해소 시에만 FADE_OUT</x:v>
+      </x:c>
       <x:c r="L73"/>
-      <x:c r="M73"/>
-      <x:c r="N73"/>
-      <x:c r="O73"/>
-      <x:c r="P73"/>
-      <x:c r="Q73"/>
-      <x:c r="R73"/>
-      <x:c r="S73"/>
-      <x:c r="T73"/>
-      <x:c r="U73"/>
-      <x:c r="V73"/>
-      <x:c r="W73"/>
+      <x:c r="M73" t="str">
+        <x:v>promo.primary,promo.secondary</x:v>
+      </x:c>
+      <x:c r="N73" t="str">
+        <x:v>가장 강한 실제 메뉴 액션을 사용하고 레퍼런스 브랜딩은 복제하지 않음</x:v>
+      </x:c>
+      <x:c r="O73" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P73" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q73" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R73" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S73" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T73" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U73" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V73" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W73" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="78" customHeight="1">
       <x:c r="A74"/>

--- a/app/template_knowledge/sources/영상편집DB.xlsx
+++ b/app/template_knowledge/sources/영상편집DB.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R2559efaf5987480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R723ce5923351474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rb7fe763e7bd64973"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R9e0a4e0e15734cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R5efd6aef886f4420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R0fcb1d9fe35340d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R2300e1cb26c44df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R657d1f5689cb45d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R362a401d4c654592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="Ree13d59270e84394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rbd47d9c6a19349cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="Rf769d156e8204fa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R4f30a5f5a4c54b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="Raa4fd192d5334f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R527c86b1bd544b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="R9d863865b0be4850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="Rc6b30e71dd53416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R1878408dda974f0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R0ce19aa02a734138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="Rc28f1779c7f14337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R373a921e9b6b40fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R548f61758e124d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R75ec71b85e8e4f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R8420d084a59141f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R896cb77a1b7d415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R4018a0ae05124f9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -959,7 +959,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>최초 제공 템플릿의 시트·열 구조를 유지합니다. 현재 승인된 세 가이드의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:W 안에서 관리하고, 프레임 분석은 action_pattern·timing_rule에 흡수합니다.</x:v>
+        <x:v>최초 제공 템플릿의 시트·열 구조를 유지합니다. 현재 승인된 네 가이드의 정밀 분석은 03_GUIDE_TEMPLATES 기존 A:W 안에서 관리하고, 프레임 분석은 action_pattern·timing_rule에 흡수합니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -1253,16 +1253,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>실제 가이드 3종</x:v>
+        <x:v>실제 가이드 4종</x:v>
       </x:c>
       <x:c r="B24" s="8" t="str">
-        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
+        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지 · 도마 BAD 챌린지를 실제 레코드로 등록</x:v>
       </x:c>
       <x:c r="C24" s="8" t="str">
         <x:v>02, 03, 12</x:v>
       </x:c>
       <x:c r="D24" s="8" t="str">
-        <x:v>12_SOURCE_GUIDES에 세 가이드의 원문·분석 근거를 보존하고 실행 규칙에 연결</x:v>
+        <x:v>12_SOURCE_GUIDES에 네 가이드의 원문·분석 근거를 보존하고 실행 규칙에 연결</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -27276,134 +27276,354 @@
       </x:c>
     </x:row>
     <x:row r="707" ht="18" customHeight="1">
-      <x:c r="A707"/>
-      <x:c r="B707"/>
-      <x:c r="C707"/>
-      <x:c r="D707"/>
-      <x:c r="E707"/>
-      <x:c r="F707"/>
-      <x:c r="G707"/>
-      <x:c r="H707"/>
-      <x:c r="I707"/>
-      <x:c r="J707"/>
-      <x:c r="K707"/>
+      <x:c r="A707" t="str">
+        <x:v>domabad20260831_line_0001</x:v>
+      </x:c>
+      <x:c r="B707" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C707" t="n">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="D707" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E707" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F707" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G707" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/rUIEHnyoPrU; 11초 STATIC_FULL_SHOT 원테이크, physical_cut_count=0, confidence=0.98, shooting_difficulty: ★★.</x:v>
+      </x:c>
+      <x:c r="H707" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I707" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J707" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K707" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="708" ht="18" customHeight="1">
-      <x:c r="A708"/>
-      <x:c r="B708"/>
-      <x:c r="C708"/>
-      <x:c r="D708"/>
-      <x:c r="E708"/>
-      <x:c r="F708"/>
-      <x:c r="G708"/>
-      <x:c r="H708"/>
-      <x:c r="I708"/>
-      <x:c r="J708"/>
-      <x:c r="K708"/>
+      <x:c r="A708" t="str">
+        <x:v>domabad20260831_line_0002</x:v>
+      </x:c>
+      <x:c r="B708" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C708" t="n">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="D708" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E708" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F708" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G708" t="str">
+        <x:v>- 0~4000ms HOOK_SETUP: 고정 전신 구도에서 자연스러운 준비 동작을 연속 수행.</x:v>
+      </x:c>
+      <x:c r="H708" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I708" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J708" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K708" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="709" ht="18" customHeight="1">
-      <x:c r="A709"/>
-      <x:c r="B709"/>
-      <x:c r="C709"/>
-      <x:c r="D709"/>
-      <x:c r="E709"/>
-      <x:c r="F709"/>
-      <x:c r="G709"/>
-      <x:c r="H709"/>
-      <x:c r="I709"/>
-      <x:c r="J709"/>
-      <x:c r="K709"/>
+      <x:c r="A709" t="str">
+        <x:v>domabad20260831_line_0003</x:v>
+      </x:c>
+      <x:c r="B709" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C709" t="n">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="D709" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E709" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F709" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G709" t="str">
+        <x:v>- 4000~5000ms PRE_DROP_BUILDUP: 드롭 직전 짧은 준비·방향 전환 동작. 경계에서 영상을 분할하지 않음.</x:v>
+      </x:c>
+      <x:c r="H709" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I709" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J709" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K709" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="710" ht="18" customHeight="1">
-      <x:c r="A710"/>
-      <x:c r="B710"/>
-      <x:c r="C710"/>
-      <x:c r="D710"/>
-      <x:c r="E710"/>
-      <x:c r="F710"/>
-      <x:c r="G710"/>
-      <x:c r="H710"/>
-      <x:c r="I710"/>
-      <x:c r="J710"/>
-      <x:c r="K710"/>
+      <x:c r="A710" t="str">
+        <x:v>domabad20260831_line_0004</x:v>
+      </x:c>
+      <x:c r="B710" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C710" t="n">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="D710" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E710" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F710" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G710" t="str">
+        <x:v>- 5000~11000ms CLIMAX_DANCE: 비트 드롭과 동시에 방향을 반전하고 대비되는 안무를 연속 수행.</x:v>
+      </x:c>
+      <x:c r="H710" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I710" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J710" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K710" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="711" ht="18" customHeight="1">
-      <x:c r="A711"/>
-      <x:c r="B711"/>
-      <x:c r="C711"/>
-      <x:c r="D711"/>
-      <x:c r="E711"/>
-      <x:c r="F711"/>
-      <x:c r="G711"/>
-      <x:c r="H711"/>
-      <x:c r="I711"/>
-      <x:c r="J711"/>
-      <x:c r="K711"/>
+      <x:c r="A711" t="str">
+        <x:v>domabad20260831_line_0005</x:v>
+      </x:c>
+      <x:c r="B711" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C711" t="n">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="D711" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E711" t="str">
+        <x:v>CONTINUITY</x:v>
+      </x:c>
+      <x:c r="F711" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G711" t="str">
+        <x:v>- ONE_TAKE, expected_take_count_per_output=1, split/reorder/internal trim/start trim/end trim 모두 금지.</x:v>
+      </x:c>
+      <x:c r="H711" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I711" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J711" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K711" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="712" ht="18" customHeight="1">
-      <x:c r="A712"/>
-      <x:c r="B712"/>
-      <x:c r="C712"/>
-      <x:c r="D712"/>
-      <x:c r="E712"/>
-      <x:c r="F712"/>
-      <x:c r="G712"/>
-      <x:c r="H712"/>
-      <x:c r="I712"/>
-      <x:c r="J712"/>
-      <x:c r="K712"/>
+      <x:c r="A712" t="str">
+        <x:v>domabad20260831_line_0006</x:v>
+      </x:c>
+      <x:c r="B712" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C712" t="n">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="D712" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E712" t="str">
+        <x:v>CAMERA</x:v>
+      </x:c>
+      <x:c r="F712" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G712" t="str">
+        <x:v>- 전체 STATIC_FULL_SHOT. 카메라 이동, 디지털 줌, animated pan/rotation, punch-in 및 transform keyframe 없음.</x:v>
+      </x:c>
+      <x:c r="H712" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I712" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J712" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K712" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="713" ht="18" customHeight="1">
-      <x:c r="A713"/>
-      <x:c r="B713"/>
-      <x:c r="C713"/>
-      <x:c r="D713"/>
-      <x:c r="E713"/>
-      <x:c r="F713"/>
-      <x:c r="G713"/>
-      <x:c r="H713"/>
-      <x:c r="I713"/>
-      <x:c r="J713"/>
-      <x:c r="K713"/>
+      <x:c r="A713" t="str">
+        <x:v>domabad20260831_line_0007</x:v>
+      </x:c>
+      <x:c r="B713" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C713" t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="D713" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E713" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F713" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G713" t="str">
+        <x:v>- 5000ms VISUAL_DROP_REVERSAL과 AUDIO_DROP_HIT 정렬. 외부 음원이 있을 때 audio offset만 조정하고 영상 타임라인은 유지.</x:v>
+      </x:c>
+      <x:c r="H713" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I713" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J713" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K713" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="714" ht="18" customHeight="1">
-      <x:c r="A714"/>
-      <x:c r="B714"/>
-      <x:c r="C714"/>
-      <x:c r="D714"/>
-      <x:c r="E714"/>
-      <x:c r="F714"/>
-      <x:c r="G714"/>
-      <x:c r="H714"/>
-      <x:c r="I714"/>
-      <x:c r="J714"/>
-      <x:c r="K714"/>
+      <x:c r="A714" t="str">
+        <x:v>domabad20260831_line_0008</x:v>
+      </x:c>
+      <x:c r="B714" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C714" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="D714" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E714" t="str">
+        <x:v>CAPTION</x:v>
+      </x:c>
+      <x:c r="F714" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G714" t="str">
+        <x:v>- 레퍼런스 자막 근거 없음. 고정 문구를 복제하지 않고 사용자 영상·홍보 맥락에서 동적으로 생성하며 드롭 앵커를 가리지 않음.</x:v>
+      </x:c>
+      <x:c r="H714" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I714" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J714" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K714" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="715" ht="18" customHeight="1">
-      <x:c r="A715"/>
-      <x:c r="B715"/>
-      <x:c r="C715"/>
-      <x:c r="D715"/>
-      <x:c r="E715"/>
-      <x:c r="F715"/>
-      <x:c r="G715"/>
-      <x:c r="H715"/>
-      <x:c r="I715"/>
-      <x:c r="J715"/>
-      <x:c r="K715"/>
+      <x:c r="A715" t="str">
+        <x:v>domabad20260831_line_0009</x:v>
+      </x:c>
+      <x:c r="B715" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C715" t="n">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="D715" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E715" t="str">
+        <x:v>INPUT_POLICY</x:v>
+      </x:c>
+      <x:c r="F715" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G715" t="str">
+        <x:v>- 단일 연속 사용자 영상 1개만 사용. 사진, B-roll, cutaway, multi-clip montage는 허용하지 않음.</x:v>
+      </x:c>
+      <x:c r="H715" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I715" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J715" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K715" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="716" ht="18" customHeight="1">
-      <x:c r="A716"/>
-      <x:c r="B716"/>
-      <x:c r="C716"/>
-      <x:c r="D716"/>
-      <x:c r="E716"/>
-      <x:c r="F716"/>
-      <x:c r="G716"/>
-      <x:c r="H716"/>
-      <x:c r="I716"/>
-      <x:c r="J716"/>
-      <x:c r="K716"/>
+      <x:c r="A716" t="str">
+        <x:v>domabad20260831_line_0010</x:v>
+      </x:c>
+      <x:c r="B716" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C716" t="n">
+        <x:v>932</x:v>
+      </x:c>
+      <x:c r="D716" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E716" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F716" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G716" t="str">
+        <x:v>- video span=1, split=false, physical transition=0, speed=1.0, reverse=false, freeze=false, image/B-roll=0, reference caption reuse=false.</x:v>
+      </x:c>
+      <x:c r="H716" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I716" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J716" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K716" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="717" ht="18" customHeight="1">
       <x:c r="A717"/>
@@ -33245,7 +33465,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>승인된 세 가이드의 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 랭킹 1·2·3위를 유지하며 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>승인된 네 가이드의 실행 구간과 이후 사용자 영상 레코드를 집계합니다. 랭킹 1·2·3·4위를 유지하며 삭제된 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -33276,10 +33496,10 @@
         <x:v>챌린지 입력</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위</x:v>
+        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위·도마 BAD 4위</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
         <x:v>02_INPUT_GUIDES</x:v>
@@ -33290,7 +33510,7 @@
         <x:v>전체 가이드 템플릿 구간</x:v>
       </x:c>
       <x:c r="B6" s="5" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
         <x:v>버전 이력을 포함한 03_GUIDE_TEMPLATES 데이터 행</x:v>
@@ -33388,10 +33608,10 @@
         <x:v>프레임 분석 실행 구간</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>기존 152개 블록 + 주술회전 8컷 + 동그리오 7컷의 신규 JSON 근거</x:v>
+        <x:v>기존 167개 구간 + 도마 BAD 원테이크의 의미 구간 3개</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -33436,6 +33656,20 @@
         <x:v>실측 0~12.067초의 훅·메뉴·공간·액션·외관·아웃트로 7컷</x:v>
       </x:c>
       <x:c r="D16" t="str">
+        <x:v>03_GUIDE_TEMPLATES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>도마 BAD v1 실행 구간</x:v>
+      </x:c>
+      <x:c r="B17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>0~11초 단일 연속 촬영 안의 SETUP·BUILDUP·CLIMAX 3개 의미 구간</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
       </x:c>
     </x:row>
@@ -33479,7 +33713,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="116" t="str">
-        <x:v>승인된 주술회전·동그리오·오츠카레 썸머 가이드를 유지합니다. rank 1·2·3을 보존하고 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>승인된 주술회전·동그리오·오츠카레 썸머·도마 BAD 가이드를 유지합니다. rank 1·2·3·4를 보존하고 삭제된 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -33646,16 +33880,39 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8"/>
-      <x:c r="C8"/>
-      <x:c r="D8"/>
-      <x:c r="E8"/>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8"/>
-      <x:c r="J8"/>
+      <x:c r="A8" t="str">
+        <x:v>uploaded_analysis_json_20260831</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>도마 BAD 챌린지</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>도마 BAD 챌린지</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>https://www.youtube.com/shorts/rUIEHnyoPrU</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>rUIEHnyoPrU</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>challenge</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>챌린지</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -33680,9 +33937,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="Rc3c8540323df46bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R89123a148bde41bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Rbfb375263a4c4223"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="Rb313eb92af034c28"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="R3686e214b02c4ebe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="Rf8b4b3552e5d4972"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -33719,7 +33976,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="119" t="str">
-        <x:v>실제 편집 가이드 3종 · 원본 스키마 고정형 v5.4</x:v>
+        <x:v>실제 편집 가이드 4종 · 원본 스키마 고정형 v5.4</x:v>
       </x:c>
       <x:c r="B1" s="31"/>
       <x:c r="C1" s="31"/>
@@ -33746,7 +34003,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="120" t="str">
-        <x:v>최초 템플릿 구조를 유지해 새 시트·새 열을 추가하지 않습니다. 주술회전·동그리오의 업로드 JSON 근거를 action_pattern·timing_rule에 흡수하고, 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>최초 템플릿 구조를 유지해 새 시트·새 열을 추가하지 않습니다. 도마 BAD 업로드 JSON의 원테이크 의미 구간을 action_pattern·timing_rule에 흡수하고, 삭제된 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="31"/>
       <x:c r="C2" s="31"/>
@@ -38711,79 +38968,211 @@
       </x:c>
     </x:row>
     <x:row r="74" ht="78" customHeight="1">
-      <x:c r="A74"/>
-      <x:c r="B74"/>
-      <x:c r="C74"/>
-      <x:c r="D74"/>
-      <x:c r="E74"/>
-      <x:c r="F74"/>
-      <x:c r="G74"/>
-      <x:c r="H74"/>
-      <x:c r="I74"/>
-      <x:c r="J74"/>
-      <x:c r="K74"/>
+      <x:c r="A74" t="str">
+        <x:v>gts_doma_bad_v1_01</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G74" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H74" t="str">
+        <x:v>정면 준비 동작 훅</x:v>
+      </x:c>
+      <x:c r="I74" t="str">
+        <x:v>HOOK_SETUP</x:v>
+      </x:c>
+      <x:c r="J74" t="str">
+        <x:v>고정 전신 구도에서 카메라를 바라보며 자연스러운 준비 동작을 이어가고 인물 전체를 프레임 안에 유지</x:v>
+      </x:c>
+      <x:c r="K74" t="str">
+        <x:v>0~4000ms 의미 구간; 원본 영상은 분할하지 않음; speed=1.0; 카메라 이동·디지털 줌·전환 없음</x:v>
+      </x:c>
       <x:c r="L74"/>
-      <x:c r="M74"/>
-      <x:c r="N74"/>
-      <x:c r="O74"/>
-      <x:c r="P74"/>
-      <x:c r="Q74"/>
-      <x:c r="R74"/>
-      <x:c r="S74"/>
-      <x:c r="T74"/>
-      <x:c r="U74"/>
-      <x:c r="V74"/>
-      <x:c r="W74"/>
+      <x:c r="M74" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N74" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O74" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P74" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q74" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R74" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S74" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T74" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U74" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V74" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W74" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="78" customHeight="1">
-      <x:c r="A75"/>
-      <x:c r="B75"/>
-      <x:c r="C75"/>
-      <x:c r="D75"/>
-      <x:c r="E75"/>
-      <x:c r="F75"/>
-      <x:c r="G75"/>
-      <x:c r="H75"/>
-      <x:c r="I75"/>
-      <x:c r="J75"/>
-      <x:c r="K75"/>
+      <x:c r="A75" t="str">
+        <x:v>gts_doma_bad_v1_02</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F75" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G75" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="H75" t="str">
+        <x:v>드롭 직전 준비 동작</x:v>
+      </x:c>
+      <x:c r="I75" t="str">
+        <x:v>PRE_DROP_BUILDUP</x:v>
+      </x:c>
+      <x:c r="J75" t="str">
+        <x:v>같은 고정 전신 구도와 연속 동작을 유지하며 비트 드롭 직전의 짧은 준비·방향 전환 동작 수행</x:v>
+      </x:c>
+      <x:c r="K75" t="str">
+        <x:v>4000~5000ms 의미 구간; 5000ms 행동 반전 앵커를 준비하되 물리 컷을 만들지 않음; speed=1.0</x:v>
+      </x:c>
       <x:c r="L75"/>
-      <x:c r="M75"/>
-      <x:c r="N75"/>
-      <x:c r="O75"/>
-      <x:c r="P75"/>
-      <x:c r="Q75"/>
-      <x:c r="R75"/>
-      <x:c r="S75"/>
-      <x:c r="T75"/>
-      <x:c r="U75"/>
-      <x:c r="V75"/>
-      <x:c r="W75"/>
+      <x:c r="M75" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N75" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O75" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P75" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q75" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R75" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S75" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T75" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U75" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V75" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W75" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="78" customHeight="1">
-      <x:c r="A76"/>
-      <x:c r="B76"/>
-      <x:c r="C76"/>
-      <x:c r="D76"/>
-      <x:c r="E76"/>
-      <x:c r="F76"/>
-      <x:c r="G76"/>
-      <x:c r="H76"/>
-      <x:c r="I76"/>
-      <x:c r="J76"/>
-      <x:c r="K76"/>
+      <x:c r="A76" t="str">
+        <x:v>gts_doma_bad_v1_03</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F76" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G76" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="H76" t="str">
+        <x:v>반전 안무 클라이맥스</x:v>
+      </x:c>
+      <x:c r="I76" t="str">
+        <x:v>CLIMAX_DANCE</x:v>
+      </x:c>
+      <x:c r="J76" t="str">
+        <x:v>비트 드롭과 동시에 몸 또는 이동 방향을 크게 반전한 뒤 대비되는 안무를 끝까지 연속 수행</x:v>
+      </x:c>
+      <x:c r="K76" t="str">
+        <x:v>5000~11000ms 의미 구간; 5000ms 시각 행동 반전과 외부 음원 드롭을 가능할 때 ±1프레임 이내 정렬; 영상 분할 없음</x:v>
+      </x:c>
       <x:c r="L76"/>
-      <x:c r="M76"/>
-      <x:c r="N76"/>
-      <x:c r="O76"/>
-      <x:c r="P76"/>
-      <x:c r="Q76"/>
-      <x:c r="R76"/>
-      <x:c r="S76"/>
-      <x:c r="T76"/>
-      <x:c r="U76"/>
-      <x:c r="V76"/>
-      <x:c r="W76"/>
+      <x:c r="M76" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N76" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O76" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P76" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q76" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R76" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S76" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T76" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U76" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V76" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W76" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="78" customHeight="1">
       <x:c r="A77"/>
